--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122384432</v>
+        <v>122399668</v>
       </c>
       <c r="B2" t="n">
-        <v>74686</v>
+        <v>98175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650422</v>
+        <v>650331</v>
       </c>
       <c r="R2" t="n">
-        <v>6674376</v>
+        <v>6673701</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -748,22 +757,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,24 +786,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -806,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122384481</v>
+        <v>122399626</v>
       </c>
       <c r="B3" t="n">
-        <v>100441</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,27 +820,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650230</v>
+        <v>650382</v>
       </c>
       <c r="R3" t="n">
-        <v>6674064</v>
+        <v>6673643</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -880,22 +883,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122384468</v>
+        <v>122399652</v>
       </c>
       <c r="B4" t="n">
-        <v>91219</v>
+        <v>90779</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,17 +964,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650436</v>
+        <v>650328</v>
       </c>
       <c r="R4" t="n">
-        <v>6674345</v>
+        <v>6673703</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,27 +998,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,24 +1022,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1058,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122384402</v>
+        <v>122399670</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,39 +1052,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1110,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650297</v>
+        <v>650313</v>
       </c>
       <c r="R5" t="n">
-        <v>6674040</v>
+        <v>6673680</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1140,22 +1122,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122384442</v>
+        <v>122399666</v>
       </c>
       <c r="B6" t="n">
-        <v>90744</v>
+        <v>98175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,30 +1176,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650393</v>
+        <v>650369</v>
       </c>
       <c r="R6" t="n">
-        <v>6674157</v>
+        <v>6673665</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1255,22 +1242,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122384412</v>
+        <v>122399627</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,20 +1301,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,16 +1322,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1349,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650399</v>
+        <v>650420</v>
       </c>
       <c r="R7" t="n">
-        <v>6674181</v>
+        <v>6673617</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1379,22 +1368,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122384403</v>
+        <v>122399667</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,39 +1422,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1473,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650237</v>
+        <v>650365</v>
       </c>
       <c r="R8" t="n">
-        <v>6674049</v>
+        <v>6673701</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1503,22 +1492,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,10 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122384454</v>
+        <v>122399671</v>
       </c>
       <c r="B9" t="n">
-        <v>90779</v>
+        <v>100441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,41 +1546,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650440</v>
+        <v>650309</v>
       </c>
       <c r="R9" t="n">
-        <v>6674369</v>
+        <v>6673789</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1618,22 +1608,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,10 +1650,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122384473</v>
+        <v>122399632</v>
       </c>
       <c r="B10" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,50 +1662,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650400</v>
+        <v>650256</v>
       </c>
       <c r="R10" t="n">
-        <v>6674415</v>
+        <v>6673700</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1742,22 +1732,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1784,10 +1774,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122384479</v>
+        <v>122399628</v>
       </c>
       <c r="B11" t="n">
-        <v>100441</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,38 +1790,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650415</v>
+        <v>650379</v>
       </c>
       <c r="R11" t="n">
-        <v>6674370</v>
+        <v>6673641</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1858,22 +1853,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122384466</v>
+        <v>122399644</v>
       </c>
       <c r="B12" t="n">
-        <v>91175</v>
+        <v>57744</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,40 +1911,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650393</v>
+        <v>650328</v>
       </c>
       <c r="R12" t="n">
-        <v>6674366</v>
+        <v>6673703</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1973,22 +1973,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,24 +1997,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2031,7 +2015,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122384369</v>
+        <v>122399633</v>
       </c>
       <c r="B13" t="n">
         <v>57390</v>
@@ -2073,23 +2057,23 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650395</v>
+        <v>650328</v>
       </c>
       <c r="R13" t="n">
-        <v>6674349</v>
+        <v>6673703</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2113,22 +2097,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122384472</v>
+        <v>122399630</v>
       </c>
       <c r="B14" t="n">
-        <v>98175</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2167,50 +2151,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650415</v>
+        <v>650217</v>
       </c>
       <c r="R14" t="n">
-        <v>6674360</v>
+        <v>6673709</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2237,22 +2218,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2279,10 +2260,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122384462</v>
+        <v>122399676</v>
       </c>
       <c r="B15" t="n">
-        <v>90779</v>
+        <v>105290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2291,41 +2272,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650428</v>
+        <v>650299</v>
       </c>
       <c r="R15" t="n">
-        <v>6674388</v>
+        <v>6673755</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2352,22 +2342,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2394,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384406</v>
+        <v>122384432</v>
       </c>
       <c r="B16" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2406,50 +2396,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650115</v>
+        <v>650422</v>
       </c>
       <c r="R16" t="n">
-        <v>6674245</v>
+        <v>6674376</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2481,7 +2462,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2491,7 +2472,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,8 +2481,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2518,10 +2515,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384371</v>
+        <v>122384481</v>
       </c>
       <c r="B17" t="n">
-        <v>57390</v>
+        <v>100441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2530,39 +2527,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2570,13 +2559,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650400</v>
+        <v>650230</v>
       </c>
       <c r="R17" t="n">
-        <v>6674206</v>
+        <v>6674064</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2605,7 +2594,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2615,7 +2604,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,10 +2631,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384373</v>
+        <v>122384468</v>
       </c>
       <c r="B18" t="n">
-        <v>57390</v>
+        <v>91219</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,39 +2643,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2694,10 +2674,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650373</v>
+        <v>650436</v>
       </c>
       <c r="R18" t="n">
-        <v>6674389</v>
+        <v>6674345</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2729,7 +2709,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2739,7 +2719,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2748,8 +2733,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2766,7 +2767,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384366</v>
+        <v>122384402</v>
       </c>
       <c r="B19" t="n">
         <v>57390</v>
@@ -2808,20 +2809,20 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650419</v>
+        <v>650297</v>
       </c>
       <c r="R19" t="n">
-        <v>6674371</v>
+        <v>6674040</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2853,7 +2854,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2863,7 +2864,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2890,10 +2891,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384407</v>
+        <v>122384442</v>
       </c>
       <c r="B20" t="n">
-        <v>57390</v>
+        <v>90744</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2902,39 +2903,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2942,10 +2934,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650101</v>
+        <v>650393</v>
       </c>
       <c r="R20" t="n">
-        <v>6674120</v>
+        <v>6674157</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2977,7 +2969,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2987,7 +2979,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3014,7 +3006,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384404</v>
+        <v>122384412</v>
       </c>
       <c r="B21" t="n">
         <v>57390</v>
@@ -3066,10 +3058,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650195</v>
+        <v>650399</v>
       </c>
       <c r="R21" t="n">
-        <v>6674100</v>
+        <v>6674181</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3101,7 +3093,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3111,7 +3103,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3138,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384470</v>
+        <v>122384403</v>
       </c>
       <c r="B22" t="n">
-        <v>91219</v>
+        <v>57390</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3150,41 +3142,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650388</v>
+        <v>650237</v>
       </c>
       <c r="R22" t="n">
-        <v>6674308</v>
+        <v>6674049</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3216,7 +3217,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3226,7 +3227,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3253,10 +3254,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384480</v>
+        <v>122384454</v>
       </c>
       <c r="B23" t="n">
-        <v>100441</v>
+        <v>90779</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3265,42 +3266,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650316</v>
+        <v>650440</v>
       </c>
       <c r="R23" t="n">
-        <v>6674034</v>
+        <v>6674369</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384484</v>
+        <v>122384473</v>
       </c>
       <c r="B24" t="n">
-        <v>100441</v>
+        <v>98175</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3381,42 +3381,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650407</v>
+        <v>650400</v>
       </c>
       <c r="R24" t="n">
-        <v>6674068</v>
+        <v>6674415</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3448,7 +3456,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3458,7 +3466,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3485,10 +3493,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384395</v>
+        <v>122384479</v>
       </c>
       <c r="B25" t="n">
-        <v>57390</v>
+        <v>100441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3497,50 +3505,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650395</v>
+        <v>650415</v>
       </c>
       <c r="R25" t="n">
-        <v>6674254</v>
+        <v>6674370</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3609,10 +3609,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384465</v>
+        <v>122384369</v>
       </c>
       <c r="B26" t="n">
-        <v>91065</v>
+        <v>57390</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3625,26 +3625,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3652,10 +3661,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650436</v>
+        <v>650395</v>
       </c>
       <c r="R26" t="n">
-        <v>6674342</v>
+        <v>6674349</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3687,7 +3696,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3697,7 +3706,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3724,10 +3733,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384388</v>
+        <v>122384466</v>
       </c>
       <c r="B27" t="n">
-        <v>57390</v>
+        <v>91175</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3736,39 +3745,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650400</v>
+        <v>650393</v>
       </c>
       <c r="R27" t="n">
-        <v>6674425</v>
+        <v>6674366</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3830,8 +3830,24 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3848,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384487</v>
+        <v>122384472</v>
       </c>
       <c r="B28" t="n">
-        <v>105280</v>
+        <v>98175</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3860,29 +3876,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3892,10 +3916,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650442</v>
+        <v>650415</v>
       </c>
       <c r="R28" t="n">
-        <v>6674345</v>
+        <v>6674360</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3927,7 +3951,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,7 +3961,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3964,10 +3988,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384438</v>
+        <v>122384462</v>
       </c>
       <c r="B29" t="n">
-        <v>80602</v>
+        <v>90779</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3980,21 +4004,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4003,14 +4027,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650353</v>
+        <v>650428</v>
       </c>
       <c r="R29" t="n">
-        <v>6674235</v>
+        <v>6674388</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4042,7 +4066,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4052,12 +4076,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4084,7 +4103,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384394</v>
+        <v>122384406</v>
       </c>
       <c r="B30" t="n">
         <v>57390</v>
@@ -4136,10 +4155,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650394</v>
+        <v>650115</v>
       </c>
       <c r="R30" t="n">
-        <v>6674272</v>
+        <v>6674245</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4171,7 +4190,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4181,7 +4200,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4208,10 +4227,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384437</v>
+        <v>122384371</v>
       </c>
       <c r="B31" t="n">
-        <v>80602</v>
+        <v>57390</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4224,26 +4243,35 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4251,13 +4279,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650387</v>
+        <v>650400</v>
       </c>
       <c r="R31" t="n">
-        <v>6674259</v>
+        <v>6674206</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4286,7 +4314,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4296,7 +4324,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4323,10 +4351,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384477</v>
+        <v>122384373</v>
       </c>
       <c r="B32" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4335,50 +4363,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650415</v>
+        <v>650373</v>
       </c>
       <c r="R32" t="n">
-        <v>6674216</v>
+        <v>6674389</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4410,7 +4438,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4420,7 +4448,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4447,7 +4475,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384397</v>
+        <v>122384407</v>
       </c>
       <c r="B33" t="n">
         <v>57390</v>
@@ -4499,10 +4527,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650406</v>
+        <v>650101</v>
       </c>
       <c r="R33" t="n">
-        <v>6674220</v>
+        <v>6674120</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4534,7 +4562,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4544,7 +4572,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4571,10 +4599,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384483</v>
+        <v>122384404</v>
       </c>
       <c r="B34" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4583,31 +4611,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4615,10 +4651,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650238</v>
+        <v>650195</v>
       </c>
       <c r="R34" t="n">
-        <v>6674076</v>
+        <v>6674100</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4650,7 +4686,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4660,7 +4696,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4687,10 +4723,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384464</v>
+        <v>122384470</v>
       </c>
       <c r="B35" t="n">
-        <v>90779</v>
+        <v>91219</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4699,25 +4735,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4726,14 +4762,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650429</v>
+        <v>650388</v>
       </c>
       <c r="R35" t="n">
-        <v>6674188</v>
+        <v>6674308</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4765,7 +4801,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,7 +4811,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4802,7 +4838,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384485</v>
+        <v>122384480</v>
       </c>
       <c r="B36" t="n">
         <v>100441</v>
@@ -4846,10 +4882,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650432</v>
+        <v>650316</v>
       </c>
       <c r="R36" t="n">
-        <v>6674247</v>
+        <v>6674034</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4881,7 +4917,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4891,7 +4927,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4918,7 +4954,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384411</v>
+        <v>122384366</v>
       </c>
       <c r="B37" t="n">
         <v>57390</v>
@@ -4966,14 +5002,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650415</v>
+        <v>650419</v>
       </c>
       <c r="R37" t="n">
-        <v>6674083</v>
+        <v>6674371</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5005,7 +5041,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5015,7 +5051,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5042,10 +5078,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384440</v>
+        <v>122384484</v>
       </c>
       <c r="B38" t="n">
-        <v>80602</v>
+        <v>100441</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5054,30 +5090,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5085,10 +5122,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650077</v>
+        <v>650407</v>
       </c>
       <c r="R38" t="n">
-        <v>6674268</v>
+        <v>6674068</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5120,7 +5157,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5130,7 +5167,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5157,10 +5194,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384476</v>
+        <v>122384395</v>
       </c>
       <c r="B39" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5169,39 +5206,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5209,10 +5246,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650396</v>
+        <v>650395</v>
       </c>
       <c r="R39" t="n">
-        <v>6674252</v>
+        <v>6674254</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5244,7 +5281,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5254,7 +5291,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5281,10 +5318,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384434</v>
+        <v>122384465</v>
       </c>
       <c r="B40" t="n">
-        <v>74686</v>
+        <v>91065</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5293,25 +5330,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5324,10 +5361,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650407</v>
+        <v>650436</v>
       </c>
       <c r="R40" t="n">
-        <v>6674363</v>
+        <v>6674342</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5359,7 +5396,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5369,7 +5406,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5396,7 +5433,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384410</v>
+        <v>122384388</v>
       </c>
       <c r="B41" t="n">
         <v>57390</v>
@@ -5438,20 +5475,20 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650147</v>
+        <v>650400</v>
       </c>
       <c r="R41" t="n">
-        <v>6674088</v>
+        <v>6674425</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5483,7 +5520,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5493,7 +5530,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5520,10 +5557,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384436</v>
+        <v>122384487</v>
       </c>
       <c r="B42" t="n">
-        <v>80602</v>
+        <v>105280</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5532,30 +5569,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5563,10 +5601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650363</v>
+        <v>650442</v>
       </c>
       <c r="R42" t="n">
-        <v>6674334</v>
+        <v>6674345</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5598,7 +5636,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5608,7 +5646,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5635,10 +5673,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384391</v>
+        <v>122384438</v>
       </c>
       <c r="B43" t="n">
-        <v>57390</v>
+        <v>80602</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5651,46 +5689,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650364</v>
+        <v>650353</v>
       </c>
       <c r="R43" t="n">
-        <v>6674383</v>
+        <v>6674235</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5722,7 +5751,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5732,7 +5761,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5759,10 +5793,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384417</v>
+        <v>122384394</v>
       </c>
       <c r="B44" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5775,21 +5809,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5801,23 +5835,23 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650385</v>
+        <v>650394</v>
       </c>
       <c r="R44" t="n">
-        <v>6674365</v>
+        <v>6674272</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5846,7 +5880,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5856,12 +5890,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5888,10 +5917,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384400</v>
+        <v>122384437</v>
       </c>
       <c r="B45" t="n">
-        <v>57390</v>
+        <v>80602</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5904,35 +5933,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5940,10 +5960,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650362</v>
+        <v>650387</v>
       </c>
       <c r="R45" t="n">
-        <v>6674082</v>
+        <v>6674259</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5975,7 +5995,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5985,7 +6005,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6012,10 +6032,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384443</v>
+        <v>122384477</v>
       </c>
       <c r="B46" t="n">
-        <v>90779</v>
+        <v>98175</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6024,41 +6044,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650438</v>
+        <v>650415</v>
       </c>
       <c r="R46" t="n">
-        <v>6674347</v>
+        <v>6674216</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6090,7 +6119,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6100,7 +6129,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6127,10 +6156,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384439</v>
+        <v>122384397</v>
       </c>
       <c r="B47" t="n">
-        <v>80602</v>
+        <v>57390</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6143,26 +6172,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6170,10 +6208,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650238</v>
+        <v>650406</v>
       </c>
       <c r="R47" t="n">
-        <v>6674074</v>
+        <v>6674220</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6205,7 +6243,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6215,12 +6253,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6244,6 +6277,3576 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122384483</v>
+      </c>
+      <c r="B48" t="n">
+        <v>100441</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>650238</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6674076</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122384464</v>
+      </c>
+      <c r="B49" t="n">
+        <v>90779</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>650429</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6674188</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122384485</v>
+      </c>
+      <c r="B50" t="n">
+        <v>100441</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>650432</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6674247</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122384411</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>650415</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6674083</v>
+      </c>
+      <c r="S51" t="n">
+        <v>4</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122384440</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80602</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>650077</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6674268</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122384476</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98175</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>650396</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6674252</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122384434</v>
+      </c>
+      <c r="B54" t="n">
+        <v>74686</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>650407</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6674363</v>
+      </c>
+      <c r="S54" t="n">
+        <v>4</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122384410</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>650147</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6674088</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122384436</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80602</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>650363</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6674334</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122384391</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>650364</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6674383</v>
+      </c>
+      <c r="S57" t="n">
+        <v>4</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122384417</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57527</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>650385</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6674365</v>
+      </c>
+      <c r="S58" t="n">
+        <v>50</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122384400</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>650362</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6674082</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122384443</v>
+      </c>
+      <c r="B60" t="n">
+        <v>90779</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>650438</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6674347</v>
+      </c>
+      <c r="S60" t="n">
+        <v>4</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122384439</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80602</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>650238</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6674074</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122399673</v>
+      </c>
+      <c r="B62" t="n">
+        <v>100441</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>650321</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6673981</v>
+      </c>
+      <c r="S62" t="n">
+        <v>4</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122399656</v>
+      </c>
+      <c r="B63" t="n">
+        <v>94697</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>649935</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6674249</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122399657</v>
+      </c>
+      <c r="B64" t="n">
+        <v>94793</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>210</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>649950</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6674175</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122399658</v>
+      </c>
+      <c r="B65" t="n">
+        <v>94793</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>210</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>649956</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6674194</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122399672</v>
+      </c>
+      <c r="B66" t="n">
+        <v>100441</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>650329</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6673994</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>122399639</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>650031</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6674158</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122399660</v>
+      </c>
+      <c r="B68" t="n">
+        <v>94793</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>210</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>649992</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6674192</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122399649</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80602</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>650383</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6673928</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122399637</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>649994</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6674118</v>
+      </c>
+      <c r="S70" t="n">
+        <v>4</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>122399640</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>650059</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6674144</v>
+      </c>
+      <c r="S71" t="n">
+        <v>4</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>122399655</v>
+      </c>
+      <c r="B72" t="n">
+        <v>94697</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>649962</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6674201</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>122399641</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>650092</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6674138</v>
+      </c>
+      <c r="S73" t="n">
+        <v>4</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>122399642</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>650411</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6674002</v>
+      </c>
+      <c r="S74" t="n">
+        <v>4</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122399645</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57744</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>649902</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6674271</v>
+      </c>
+      <c r="S75" t="n">
+        <v>4</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>122399650</v>
+      </c>
+      <c r="B76" t="n">
+        <v>90744</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>650386</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6673912</v>
+      </c>
+      <c r="S76" t="n">
+        <v>4</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>122399675</v>
+      </c>
+      <c r="B77" t="n">
+        <v>100441</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>650473</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6673911</v>
+      </c>
+      <c r="S77" t="n">
+        <v>4</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399668</v>
+        <v>122399632</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650331</v>
+        <v>650256</v>
       </c>
       <c r="R2" t="n">
-        <v>6673701</v>
+        <v>6673700</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399626</v>
+        <v>122399644</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>57744</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,32 +815,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650382</v>
+        <v>650328</v>
       </c>
       <c r="R3" t="n">
-        <v>6673643</v>
+        <v>6673703</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -898,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399652</v>
+        <v>122399671</v>
       </c>
       <c r="B4" t="n">
-        <v>90779</v>
+        <v>100451</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,30 +931,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650328</v>
+        <v>650309</v>
       </c>
       <c r="R4" t="n">
-        <v>6673703</v>
+        <v>6673789</v>
       </c>
       <c r="S4" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399670</v>
+        <v>122399633</v>
       </c>
       <c r="B5" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,39 +1047,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1092,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650313</v>
+        <v>650328</v>
       </c>
       <c r="R5" t="n">
-        <v>6673680</v>
+        <v>6673703</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399666</v>
+        <v>122399627</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,35 +1171,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1212,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650369</v>
+        <v>650420</v>
       </c>
       <c r="R6" t="n">
-        <v>6673665</v>
+        <v>6673617</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1247,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1257,12 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399627</v>
+        <v>122399668</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,36 +1292,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1338,10 +1332,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650420</v>
+        <v>650331</v>
       </c>
       <c r="R7" t="n">
-        <v>6673617</v>
+        <v>6673701</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1373,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1383,7 +1377,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,7 +1412,7 @@
         <v>122399667</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1534,10 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399671</v>
+        <v>122399630</v>
       </c>
       <c r="B9" t="n">
-        <v>100441</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,27 +1549,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1578,10 +1582,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650309</v>
+        <v>650217</v>
       </c>
       <c r="R9" t="n">
-        <v>6673789</v>
+        <v>6673709</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1623,7 +1627,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,10 +1654,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399632</v>
+        <v>122399652</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>90789</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,35 +1670,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1702,13 +1697,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650256</v>
+        <v>650328</v>
       </c>
       <c r="R10" t="n">
-        <v>6673700</v>
+        <v>6673703</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1737,7 +1732,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1747,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,10 +1769,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399628</v>
+        <v>122399666</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>98185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1786,36 +1781,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1823,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650379</v>
+        <v>650369</v>
       </c>
       <c r="R11" t="n">
-        <v>6673641</v>
+        <v>6673665</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1858,7 +1852,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,7 +1862,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399644</v>
+        <v>122399626</v>
       </c>
       <c r="B12" t="n">
-        <v>57744</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,31 +1910,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650328</v>
+        <v>650382</v>
       </c>
       <c r="R12" t="n">
-        <v>6673703</v>
+        <v>6673643</v>
       </c>
       <c r="S12" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,10 +2015,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399633</v>
+        <v>122399628</v>
       </c>
       <c r="B13" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2027,20 +2027,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2048,16 +2048,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2067,13 +2064,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650328</v>
+        <v>650379</v>
       </c>
       <c r="R13" t="n">
-        <v>6673703</v>
+        <v>6673641</v>
       </c>
       <c r="S13" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2102,7 +2099,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2109,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,10 +2136,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399630</v>
+        <v>122399670</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>98185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,36 +2148,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650217</v>
+        <v>650313</v>
       </c>
       <c r="R14" t="n">
-        <v>6673709</v>
+        <v>6673680</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384432</v>
+        <v>122384437</v>
       </c>
       <c r="B16" t="n">
-        <v>74686</v>
+        <v>80603</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,25 +2396,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2423,14 +2423,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650422</v>
+        <v>650387</v>
       </c>
       <c r="R16" t="n">
-        <v>6674376</v>
+        <v>6674259</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,24 +2481,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2515,10 +2499,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384481</v>
+        <v>122384434</v>
       </c>
       <c r="B17" t="n">
-        <v>100441</v>
+        <v>74686</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2531,38 +2515,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650230</v>
+        <v>650407</v>
       </c>
       <c r="R17" t="n">
-        <v>6674064</v>
+        <v>6674363</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2594,7 +2577,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2604,7 +2587,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2631,10 +2614,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384468</v>
+        <v>122384395</v>
       </c>
       <c r="B18" t="n">
-        <v>91219</v>
+        <v>57390</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2643,41 +2626,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650436</v>
+        <v>650395</v>
       </c>
       <c r="R18" t="n">
-        <v>6674345</v>
+        <v>6674254</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2709,7 +2701,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2719,12 +2711,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,24 +2720,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2767,7 +2738,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384402</v>
+        <v>122384394</v>
       </c>
       <c r="B19" t="n">
         <v>57390</v>
@@ -2819,10 +2790,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650297</v>
+        <v>650394</v>
       </c>
       <c r="R19" t="n">
-        <v>6674040</v>
+        <v>6674272</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2854,7 +2825,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2864,7 +2835,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2894,7 +2865,7 @@
         <v>122384442</v>
       </c>
       <c r="B20" t="n">
-        <v>90744</v>
+        <v>90754</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3006,10 +2977,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384412</v>
+        <v>122384483</v>
       </c>
       <c r="B21" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3018,39 +2989,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3058,10 +3021,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650399</v>
+        <v>650238</v>
       </c>
       <c r="R21" t="n">
-        <v>6674181</v>
+        <v>6674076</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3093,7 +3056,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3103,7 +3066,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3130,7 +3093,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384403</v>
+        <v>122384373</v>
       </c>
       <c r="B22" t="n">
         <v>57390</v>
@@ -3172,20 +3135,20 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650237</v>
+        <v>650373</v>
       </c>
       <c r="R22" t="n">
-        <v>6674049</v>
+        <v>6674389</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3217,7 +3180,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3227,7 +3190,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3254,10 +3217,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384454</v>
+        <v>122384371</v>
       </c>
       <c r="B23" t="n">
-        <v>90779</v>
+        <v>57390</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3270,40 +3233,49 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650440</v>
+        <v>650400</v>
       </c>
       <c r="R23" t="n">
-        <v>6674369</v>
+        <v>6674206</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3332,7 +3304,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3342,7 +3314,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3369,10 +3341,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384473</v>
+        <v>122384369</v>
       </c>
       <c r="B24" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3381,39 +3353,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3421,10 +3393,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650400</v>
+        <v>650395</v>
       </c>
       <c r="R24" t="n">
-        <v>6674415</v>
+        <v>6674349</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3456,7 +3428,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3466,7 +3438,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3493,10 +3465,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384479</v>
+        <v>122384487</v>
       </c>
       <c r="B25" t="n">
-        <v>100441</v>
+        <v>105290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3509,21 +3481,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3537,10 +3509,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650415</v>
+        <v>650442</v>
       </c>
       <c r="R25" t="n">
-        <v>6674370</v>
+        <v>6674345</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3572,7 +3544,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3582,7 +3554,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3609,10 +3581,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384369</v>
+        <v>122384480</v>
       </c>
       <c r="B26" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3621,50 +3593,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650395</v>
+        <v>650316</v>
       </c>
       <c r="R26" t="n">
-        <v>6674349</v>
+        <v>6674034</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3696,7 +3660,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3706,7 +3670,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3733,10 +3697,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384466</v>
+        <v>122384479</v>
       </c>
       <c r="B27" t="n">
-        <v>91175</v>
+        <v>100451</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3749,26 +3713,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4217</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3776,10 +3741,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650393</v>
+        <v>650415</v>
       </c>
       <c r="R27" t="n">
-        <v>6674366</v>
+        <v>6674370</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3811,7 +3776,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3821,7 +3786,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3830,24 +3795,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3864,10 +3813,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384472</v>
+        <v>122384432</v>
       </c>
       <c r="B28" t="n">
-        <v>98175</v>
+        <v>74686</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3876,39 +3825,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3916,10 +3856,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650415</v>
+        <v>650422</v>
       </c>
       <c r="R28" t="n">
-        <v>6674360</v>
+        <v>6674376</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3951,7 +3891,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3961,7 +3901,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3970,8 +3910,24 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3988,10 +3944,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384462</v>
+        <v>122384473</v>
       </c>
       <c r="B29" t="n">
-        <v>90779</v>
+        <v>98185</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4000,30 +3956,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4031,10 +3996,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650428</v>
+        <v>650400</v>
       </c>
       <c r="R29" t="n">
-        <v>6674388</v>
+        <v>6674415</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4066,7 +4031,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4076,7 +4041,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4103,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384406</v>
+        <v>122384477</v>
       </c>
       <c r="B30" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4115,39 +4080,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4155,10 +4120,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650115</v>
+        <v>650415</v>
       </c>
       <c r="R30" t="n">
-        <v>6674245</v>
+        <v>6674216</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4190,7 +4155,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4200,7 +4165,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4227,10 +4192,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384371</v>
+        <v>122384481</v>
       </c>
       <c r="B31" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4239,39 +4204,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4279,13 +4236,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650400</v>
+        <v>650230</v>
       </c>
       <c r="R31" t="n">
-        <v>6674206</v>
+        <v>6674064</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4314,7 +4271,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4324,7 +4281,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4351,10 +4308,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384373</v>
+        <v>122384417</v>
       </c>
       <c r="B32" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4367,21 +4324,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4393,7 +4350,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4403,13 +4360,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650373</v>
+        <v>650385</v>
       </c>
       <c r="R32" t="n">
-        <v>6674389</v>
+        <v>6674365</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4438,7 +4395,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4448,7 +4405,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4475,7 +4437,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384407</v>
+        <v>122384411</v>
       </c>
       <c r="B33" t="n">
         <v>57390</v>
@@ -4517,7 +4479,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4527,10 +4489,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650101</v>
+        <v>650415</v>
       </c>
       <c r="R33" t="n">
-        <v>6674120</v>
+        <v>6674083</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4562,7 +4524,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4572,7 +4534,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4599,7 +4561,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384404</v>
+        <v>122384402</v>
       </c>
       <c r="B34" t="n">
         <v>57390</v>
@@ -4641,7 +4603,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4651,10 +4613,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650195</v>
+        <v>650297</v>
       </c>
       <c r="R34" t="n">
-        <v>6674100</v>
+        <v>6674040</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4686,7 +4648,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4696,7 +4658,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4723,10 +4685,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384470</v>
+        <v>122384468</v>
       </c>
       <c r="B35" t="n">
-        <v>91219</v>
+        <v>91229</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4766,10 +4728,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650388</v>
+        <v>650436</v>
       </c>
       <c r="R35" t="n">
-        <v>6674308</v>
+        <v>6674345</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4801,7 +4763,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4811,7 +4773,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4820,8 +4787,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4838,10 +4821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384480</v>
+        <v>122384397</v>
       </c>
       <c r="B36" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4850,31 +4833,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4882,10 +4873,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650316</v>
+        <v>650406</v>
       </c>
       <c r="R36" t="n">
-        <v>6674034</v>
+        <v>6674220</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4917,7 +4908,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4927,7 +4918,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4954,10 +4945,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384366</v>
+        <v>122384462</v>
       </c>
       <c r="B37" t="n">
-        <v>57390</v>
+        <v>90789</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4970,35 +4961,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5006,10 +4988,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650419</v>
+        <v>650428</v>
       </c>
       <c r="R37" t="n">
-        <v>6674371</v>
+        <v>6674388</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5041,7 +5023,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5051,7 +5033,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5078,10 +5060,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384484</v>
+        <v>122384400</v>
       </c>
       <c r="B38" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5090,31 +5072,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5122,10 +5112,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650407</v>
+        <v>650362</v>
       </c>
       <c r="R38" t="n">
-        <v>6674068</v>
+        <v>6674082</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5157,7 +5147,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5167,7 +5157,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5194,7 +5184,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384395</v>
+        <v>122384404</v>
       </c>
       <c r="B39" t="n">
         <v>57390</v>
@@ -5246,10 +5236,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650395</v>
+        <v>650195</v>
       </c>
       <c r="R39" t="n">
-        <v>6674254</v>
+        <v>6674100</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5281,7 +5271,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5291,7 +5281,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5318,10 +5308,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384465</v>
+        <v>122384484</v>
       </c>
       <c r="B40" t="n">
-        <v>91065</v>
+        <v>100451</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5330,41 +5320,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650436</v>
+        <v>650407</v>
       </c>
       <c r="R40" t="n">
-        <v>6674342</v>
+        <v>6674068</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5396,7 +5387,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5406,7 +5397,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5433,10 +5424,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384388</v>
+        <v>122384465</v>
       </c>
       <c r="B41" t="n">
-        <v>57390</v>
+        <v>91075</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5449,35 +5440,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5485,10 +5467,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650400</v>
+        <v>650436</v>
       </c>
       <c r="R41" t="n">
-        <v>6674425</v>
+        <v>6674342</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5520,7 +5502,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5530,7 +5512,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5557,10 +5539,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384487</v>
+        <v>122384440</v>
       </c>
       <c r="B42" t="n">
-        <v>105280</v>
+        <v>80603</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5569,42 +5551,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650442</v>
+        <v>650077</v>
       </c>
       <c r="R42" t="n">
-        <v>6674345</v>
+        <v>6674268</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5636,7 +5617,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5646,7 +5627,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5673,10 +5654,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384438</v>
+        <v>122384485</v>
       </c>
       <c r="B43" t="n">
-        <v>80602</v>
+        <v>100451</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5685,30 +5666,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5716,10 +5698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650353</v>
+        <v>650432</v>
       </c>
       <c r="R43" t="n">
-        <v>6674235</v>
+        <v>6674247</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5751,7 +5733,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5761,12 +5743,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5793,7 +5770,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384394</v>
+        <v>122384407</v>
       </c>
       <c r="B44" t="n">
         <v>57390</v>
@@ -5845,10 +5822,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650394</v>
+        <v>650101</v>
       </c>
       <c r="R44" t="n">
-        <v>6674272</v>
+        <v>6674120</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5880,7 +5857,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5890,7 +5867,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5917,10 +5894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384437</v>
+        <v>122384391</v>
       </c>
       <c r="B45" t="n">
-        <v>80602</v>
+        <v>57390</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5933,37 +5910,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650387</v>
+        <v>650364</v>
       </c>
       <c r="R45" t="n">
-        <v>6674259</v>
+        <v>6674383</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5995,7 +5981,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6005,7 +5991,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6032,10 +6018,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384477</v>
+        <v>122384439</v>
       </c>
       <c r="B46" t="n">
-        <v>98175</v>
+        <v>80603</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6044,39 +6030,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6084,10 +6061,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650415</v>
+        <v>650238</v>
       </c>
       <c r="R46" t="n">
-        <v>6674216</v>
+        <v>6674074</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6119,7 +6096,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6129,7 +6106,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6156,7 +6138,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384397</v>
+        <v>122384406</v>
       </c>
       <c r="B47" t="n">
         <v>57390</v>
@@ -6208,10 +6190,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650406</v>
+        <v>650115</v>
       </c>
       <c r="R47" t="n">
-        <v>6674220</v>
+        <v>6674245</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6243,7 +6225,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6253,7 +6235,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6280,10 +6262,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384483</v>
+        <v>122384476</v>
       </c>
       <c r="B48" t="n">
-        <v>100441</v>
+        <v>98185</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6292,29 +6274,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -6324,10 +6314,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650238</v>
+        <v>650396</v>
       </c>
       <c r="R48" t="n">
-        <v>6674076</v>
+        <v>6674252</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6359,7 +6349,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6369,7 +6359,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6396,10 +6386,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384464</v>
+        <v>122384470</v>
       </c>
       <c r="B49" t="n">
-        <v>90779</v>
+        <v>91229</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6408,25 +6398,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6435,14 +6425,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650429</v>
+        <v>650388</v>
       </c>
       <c r="R49" t="n">
-        <v>6674188</v>
+        <v>6674308</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6474,7 +6464,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6484,7 +6474,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6511,10 +6501,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384485</v>
+        <v>122384366</v>
       </c>
       <c r="B50" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6523,42 +6513,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650432</v>
+        <v>650419</v>
       </c>
       <c r="R50" t="n">
-        <v>6674247</v>
+        <v>6674371</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6590,7 +6588,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6600,7 +6598,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6627,7 +6625,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384411</v>
+        <v>122384403</v>
       </c>
       <c r="B51" t="n">
         <v>57390</v>
@@ -6679,10 +6677,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650415</v>
+        <v>650237</v>
       </c>
       <c r="R51" t="n">
-        <v>6674083</v>
+        <v>6674049</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6714,7 +6712,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6724,7 +6722,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6751,10 +6749,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384440</v>
+        <v>122384412</v>
       </c>
       <c r="B52" t="n">
-        <v>80602</v>
+        <v>57390</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6767,26 +6765,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6794,10 +6801,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650077</v>
+        <v>650399</v>
       </c>
       <c r="R52" t="n">
-        <v>6674268</v>
+        <v>6674181</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6829,7 +6836,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6839,7 +6846,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6866,10 +6873,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384476</v>
+        <v>122384388</v>
       </c>
       <c r="B53" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6878,50 +6885,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650396</v>
+        <v>650400</v>
       </c>
       <c r="R53" t="n">
-        <v>6674252</v>
+        <v>6674425</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6953,7 +6960,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6963,7 +6970,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6990,10 +6997,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384434</v>
+        <v>122384443</v>
       </c>
       <c r="B54" t="n">
-        <v>74686</v>
+        <v>90789</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7002,25 +7009,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7033,10 +7040,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650407</v>
+        <v>650438</v>
       </c>
       <c r="R54" t="n">
-        <v>6674363</v>
+        <v>6674347</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7068,7 +7075,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7078,7 +7085,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7105,10 +7112,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384410</v>
+        <v>122384472</v>
       </c>
       <c r="B55" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7117,50 +7124,50 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650147</v>
+        <v>650415</v>
       </c>
       <c r="R55" t="n">
-        <v>6674088</v>
+        <v>6674360</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7192,7 +7199,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7202,7 +7209,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7229,10 +7236,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384436</v>
+        <v>122384438</v>
       </c>
       <c r="B56" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7268,14 +7275,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650363</v>
+        <v>650353</v>
       </c>
       <c r="R56" t="n">
-        <v>6674334</v>
+        <v>6674235</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7307,7 +7314,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7317,7 +7324,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7344,10 +7356,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384391</v>
+        <v>122384454</v>
       </c>
       <c r="B57" t="n">
-        <v>57390</v>
+        <v>90789</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7360,35 +7372,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7396,10 +7399,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650364</v>
+        <v>650440</v>
       </c>
       <c r="R57" t="n">
-        <v>6674383</v>
+        <v>6674369</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7431,7 +7434,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7441,7 +7444,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7468,10 +7471,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384417</v>
+        <v>122384436</v>
       </c>
       <c r="B58" t="n">
-        <v>57527</v>
+        <v>80603</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7484,35 +7487,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7520,13 +7514,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650385</v>
+        <v>650363</v>
       </c>
       <c r="R58" t="n">
-        <v>6674365</v>
+        <v>6674334</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7555,7 +7549,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7565,12 +7559,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7597,10 +7586,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384400</v>
+        <v>122384466</v>
       </c>
       <c r="B59" t="n">
-        <v>57390</v>
+        <v>91185</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7609,50 +7598,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650362</v>
+        <v>650393</v>
       </c>
       <c r="R59" t="n">
-        <v>6674082</v>
+        <v>6674366</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7684,7 +7664,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7694,7 +7674,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7703,8 +7683,24 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7721,10 +7717,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384443</v>
+        <v>122384464</v>
       </c>
       <c r="B60" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7760,14 +7756,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650438</v>
+        <v>650429</v>
       </c>
       <c r="R60" t="n">
-        <v>6674347</v>
+        <v>6674188</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7799,7 +7795,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7809,7 +7805,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7836,10 +7832,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384439</v>
+        <v>122384410</v>
       </c>
       <c r="B61" t="n">
-        <v>80602</v>
+        <v>57390</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7852,26 +7848,35 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7879,10 +7884,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650238</v>
+        <v>650147</v>
       </c>
       <c r="R61" t="n">
-        <v>6674074</v>
+        <v>6674088</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7914,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7924,12 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,10 +7956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399673</v>
+        <v>122399658</v>
       </c>
       <c r="B62" t="n">
-        <v>100441</v>
+        <v>94803</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7972,21 +7972,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>650321</v>
+        <v>649956</v>
       </c>
       <c r="R62" t="n">
-        <v>6673981</v>
+        <v>6674194</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8072,10 +8072,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399656</v>
+        <v>122399642</v>
       </c>
       <c r="B63" t="n">
-        <v>94697</v>
+        <v>57390</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8084,31 +8084,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8116,10 +8124,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649935</v>
+        <v>650411</v>
       </c>
       <c r="R63" t="n">
-        <v>6674249</v>
+        <v>6674002</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8151,7 +8159,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8161,7 +8169,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8188,10 +8196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399657</v>
+        <v>122399673</v>
       </c>
       <c r="B64" t="n">
-        <v>94793</v>
+        <v>100451</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8204,21 +8212,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8232,10 +8240,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649950</v>
+        <v>650321</v>
       </c>
       <c r="R64" t="n">
-        <v>6674175</v>
+        <v>6673981</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8267,7 +8275,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8277,7 +8285,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8304,10 +8312,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399658</v>
+        <v>122399675</v>
       </c>
       <c r="B65" t="n">
-        <v>94793</v>
+        <v>100451</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8320,21 +8328,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8348,10 +8356,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649956</v>
+        <v>650473</v>
       </c>
       <c r="R65" t="n">
-        <v>6674194</v>
+        <v>6673911</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8383,7 +8391,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8393,7 +8401,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8423,7 +8431,7 @@
         <v>122399672</v>
       </c>
       <c r="B66" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8536,10 +8544,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399639</v>
+        <v>122399656</v>
       </c>
       <c r="B67" t="n">
-        <v>57390</v>
+        <v>94707</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8548,39 +8556,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8588,10 +8588,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>650031</v>
+        <v>649935</v>
       </c>
       <c r="R67" t="n">
-        <v>6674158</v>
+        <v>6674249</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8660,10 +8660,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399660</v>
+        <v>122399650</v>
       </c>
       <c r="B68" t="n">
-        <v>94793</v>
+        <v>90754</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8676,27 +8676,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8704,10 +8703,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>649992</v>
+        <v>650386</v>
       </c>
       <c r="R68" t="n">
-        <v>6674192</v>
+        <v>6673912</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8739,7 +8738,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8749,7 +8748,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8776,10 +8775,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399649</v>
+        <v>122399639</v>
       </c>
       <c r="B69" t="n">
-        <v>80602</v>
+        <v>57390</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8792,26 +8791,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8819,10 +8827,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650383</v>
+        <v>650031</v>
       </c>
       <c r="R69" t="n">
-        <v>6673928</v>
+        <v>6674158</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8854,7 +8862,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8864,7 +8872,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8891,7 +8899,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399637</v>
+        <v>122399640</v>
       </c>
       <c r="B70" t="n">
         <v>57390</v>
@@ -8943,10 +8951,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>649994</v>
+        <v>650059</v>
       </c>
       <c r="R70" t="n">
-        <v>6674118</v>
+        <v>6674144</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8978,7 +8986,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8988,7 +8996,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9015,10 +9023,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399640</v>
+        <v>122399649</v>
       </c>
       <c r="B71" t="n">
-        <v>57390</v>
+        <v>80603</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9031,35 +9039,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9067,10 +9066,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650059</v>
+        <v>650383</v>
       </c>
       <c r="R71" t="n">
-        <v>6674144</v>
+        <v>6673928</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9102,7 +9101,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9112,7 +9111,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9139,10 +9138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399655</v>
+        <v>122399637</v>
       </c>
       <c r="B72" t="n">
-        <v>94697</v>
+        <v>57390</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9151,31 +9150,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9183,10 +9190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>649962</v>
+        <v>649994</v>
       </c>
       <c r="R72" t="n">
-        <v>6674201</v>
+        <v>6674118</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9218,7 +9225,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9228,7 +9235,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9379,10 +9386,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399642</v>
+        <v>122399645</v>
       </c>
       <c r="B74" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9391,20 +9398,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9412,18 +9419,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9431,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>650411</v>
+        <v>649902</v>
       </c>
       <c r="R74" t="n">
-        <v>6674002</v>
+        <v>6674271</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9466,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9476,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9499,18 +9498,22 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr"/>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399645</v>
+        <v>122399660</v>
       </c>
       <c r="B75" t="n">
-        <v>57744</v>
+        <v>94803</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9519,27 +9522,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>210</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9547,10 +9550,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649902</v>
+        <v>649992</v>
       </c>
       <c r="R75" t="n">
-        <v>6674271</v>
+        <v>6674192</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9582,7 +9585,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9592,7 +9595,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9619,14 +9622,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399650</v>
+        <v>122399657</v>
       </c>
       <c r="B76" t="n">
-        <v>90744</v>
+        <v>94803</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9635,26 +9638,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9662,10 +9666,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>650386</v>
+        <v>649950</v>
       </c>
       <c r="R76" t="n">
-        <v>6673912</v>
+        <v>6674175</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9697,7 +9701,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9707,7 +9711,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9734,14 +9738,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122399675</v>
+        <v>122399655</v>
       </c>
       <c r="B77" t="n">
-        <v>100441</v>
+        <v>94707</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9750,21 +9754,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9778,10 +9782,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>650473</v>
+        <v>649962</v>
       </c>
       <c r="R77" t="n">
-        <v>6673911</v>
+        <v>6674201</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9813,7 +9817,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9823,7 +9827,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399632</v>
+        <v>122399670</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650256</v>
+        <v>650313</v>
       </c>
       <c r="R2" t="n">
-        <v>6673700</v>
+        <v>6673680</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399671</v>
+        <v>122399626</v>
       </c>
       <c r="B4" t="n">
-        <v>100451</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,27 +935,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650309</v>
+        <v>650382</v>
       </c>
       <c r="R4" t="n">
-        <v>6673789</v>
+        <v>6673643</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -998,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399633</v>
+        <v>122399630</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,20 +1052,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,16 +1073,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1087,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650328</v>
+        <v>650217</v>
       </c>
       <c r="R5" t="n">
-        <v>6673703</v>
+        <v>6673709</v>
       </c>
       <c r="S5" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1280,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399668</v>
+        <v>122399671</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>100451</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,37 +1294,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1332,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650331</v>
+        <v>650309</v>
       </c>
       <c r="R7" t="n">
-        <v>6673701</v>
+        <v>6673789</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1367,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,12 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399667</v>
+        <v>122399633</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,39 +1410,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1461,13 +1450,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650365</v>
+        <v>650328</v>
       </c>
       <c r="R8" t="n">
-        <v>6673701</v>
+        <v>6673703</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1506,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,10 +1522,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399630</v>
+        <v>122399667</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,36 +1534,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1582,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650217</v>
+        <v>650365</v>
       </c>
       <c r="R9" t="n">
-        <v>6673709</v>
+        <v>6673701</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1617,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1627,7 +1619,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399652</v>
+        <v>122399632</v>
       </c>
       <c r="B10" t="n">
-        <v>90789</v>
+        <v>57390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1670,26 +1662,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1697,13 +1698,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650328</v>
+        <v>650256</v>
       </c>
       <c r="R10" t="n">
-        <v>6673703</v>
+        <v>6673700</v>
       </c>
       <c r="S10" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1732,7 +1733,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1742,7 +1743,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1894,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399626</v>
+        <v>122399652</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>90789</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,36 +1907,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1943,13 +1938,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650382</v>
+        <v>650328</v>
       </c>
       <c r="R12" t="n">
-        <v>6673643</v>
+        <v>6673703</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1978,7 +1973,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1988,7 +1983,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2136,7 +2131,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399670</v>
+        <v>122399668</v>
       </c>
       <c r="B14" t="n">
         <v>98185</v>
@@ -2171,7 +2166,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650313</v>
+        <v>650331</v>
       </c>
       <c r="R14" t="n">
-        <v>6673680</v>
+        <v>6673701</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2223,7 +2218,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2228,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384437</v>
+        <v>122384464</v>
       </c>
       <c r="B16" t="n">
-        <v>80603</v>
+        <v>90789</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650387</v>
+        <v>650429</v>
       </c>
       <c r="R16" t="n">
-        <v>6674259</v>
+        <v>6674188</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2499,10 +2499,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384434</v>
+        <v>122384369</v>
       </c>
       <c r="B17" t="n">
-        <v>74686</v>
+        <v>57390</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2511,30 +2511,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2542,10 +2551,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650407</v>
+        <v>650395</v>
       </c>
       <c r="R17" t="n">
-        <v>6674363</v>
+        <v>6674349</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2577,7 +2586,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2587,7 +2596,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2614,7 +2623,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384395</v>
+        <v>122384394</v>
       </c>
       <c r="B18" t="n">
         <v>57390</v>
@@ -2656,7 +2665,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2666,10 +2675,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650395</v>
+        <v>650394</v>
       </c>
       <c r="R18" t="n">
-        <v>6674254</v>
+        <v>6674272</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2701,7 +2710,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2711,7 +2720,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2738,10 +2747,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384394</v>
+        <v>122384485</v>
       </c>
       <c r="B19" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2750,39 +2759,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2790,10 +2791,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650394</v>
+        <v>650432</v>
       </c>
       <c r="R19" t="n">
-        <v>6674272</v>
+        <v>6674247</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2825,7 +2826,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2835,7 +2836,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2862,10 +2863,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384442</v>
+        <v>122384462</v>
       </c>
       <c r="B20" t="n">
-        <v>90754</v>
+        <v>90789</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2874,25 +2875,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2901,14 +2902,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650393</v>
+        <v>650428</v>
       </c>
       <c r="R20" t="n">
-        <v>6674157</v>
+        <v>6674388</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2940,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2950,7 +2951,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2977,10 +2978,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384483</v>
+        <v>122384411</v>
       </c>
       <c r="B21" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2989,31 +2990,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3021,10 +3030,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650238</v>
+        <v>650415</v>
       </c>
       <c r="R21" t="n">
-        <v>6674076</v>
+        <v>6674083</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3056,7 +3065,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3066,7 +3075,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3093,7 +3102,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384373</v>
+        <v>122384412</v>
       </c>
       <c r="B22" t="n">
         <v>57390</v>
@@ -3135,20 +3144,20 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650373</v>
+        <v>650399</v>
       </c>
       <c r="R22" t="n">
-        <v>6674389</v>
+        <v>6674181</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3180,7 +3189,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3190,7 +3199,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3217,10 +3226,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384371</v>
+        <v>122384439</v>
       </c>
       <c r="B23" t="n">
-        <v>57390</v>
+        <v>80603</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3233,35 +3242,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650400</v>
+        <v>650238</v>
       </c>
       <c r="R23" t="n">
-        <v>6674206</v>
+        <v>6674074</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3314,7 +3314,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3341,10 +3346,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384369</v>
+        <v>122384434</v>
       </c>
       <c r="B24" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3353,39 +3358,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3393,10 +3389,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650395</v>
+        <v>650407</v>
       </c>
       <c r="R24" t="n">
-        <v>6674349</v>
+        <v>6674363</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3428,7 +3424,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3438,7 +3434,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3465,10 +3461,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384487</v>
+        <v>122384436</v>
       </c>
       <c r="B25" t="n">
-        <v>105290</v>
+        <v>80603</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3477,31 +3473,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3509,10 +3504,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650442</v>
+        <v>650363</v>
       </c>
       <c r="R25" t="n">
-        <v>6674345</v>
+        <v>6674334</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3544,7 +3539,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3554,7 +3549,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3581,10 +3576,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384480</v>
+        <v>122384454</v>
       </c>
       <c r="B26" t="n">
-        <v>100451</v>
+        <v>90789</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3593,42 +3588,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650316</v>
+        <v>650440</v>
       </c>
       <c r="R26" t="n">
-        <v>6674034</v>
+        <v>6674369</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3660,7 +3654,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3670,7 +3664,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3697,7 +3691,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384479</v>
+        <v>122384483</v>
       </c>
       <c r="B27" t="n">
         <v>100451</v>
@@ -3737,14 +3731,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650415</v>
+        <v>650238</v>
       </c>
       <c r="R27" t="n">
-        <v>6674370</v>
+        <v>6674076</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3776,7 +3770,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3786,7 +3780,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3813,10 +3807,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384432</v>
+        <v>122384395</v>
       </c>
       <c r="B28" t="n">
-        <v>74686</v>
+        <v>57390</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3825,41 +3819,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650422</v>
+        <v>650395</v>
       </c>
       <c r="R28" t="n">
-        <v>6674376</v>
+        <v>6674254</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3891,7 +3894,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3901,7 +3904,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3910,24 +3913,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3944,10 +3931,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384473</v>
+        <v>122384397</v>
       </c>
       <c r="B29" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3956,50 +3943,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650400</v>
+        <v>650406</v>
       </c>
       <c r="R29" t="n">
-        <v>6674415</v>
+        <v>6674220</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4031,7 +4018,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4041,7 +4028,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4068,10 +4055,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384477</v>
+        <v>122384373</v>
       </c>
       <c r="B30" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4080,50 +4067,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650415</v>
+        <v>650373</v>
       </c>
       <c r="R30" t="n">
-        <v>6674216</v>
+        <v>6674389</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4155,7 +4142,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4165,7 +4152,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4192,10 +4179,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384481</v>
+        <v>122384400</v>
       </c>
       <c r="B31" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4204,31 +4191,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4236,10 +4231,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650230</v>
+        <v>650362</v>
       </c>
       <c r="R31" t="n">
-        <v>6674064</v>
+        <v>6674082</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4271,7 +4266,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4281,7 +4276,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4308,10 +4303,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384417</v>
+        <v>122384465</v>
       </c>
       <c r="B32" t="n">
-        <v>57527</v>
+        <v>91075</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4324,35 +4319,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4360,13 +4346,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650385</v>
+        <v>650436</v>
       </c>
       <c r="R32" t="n">
-        <v>6674365</v>
+        <v>6674342</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4395,7 +4381,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4405,12 +4391,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4437,10 +4418,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384411</v>
+        <v>122384440</v>
       </c>
       <c r="B33" t="n">
-        <v>57390</v>
+        <v>80603</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4453,35 +4434,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4489,10 +4461,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650415</v>
+        <v>650077</v>
       </c>
       <c r="R33" t="n">
-        <v>6674083</v>
+        <v>6674268</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4524,7 +4496,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4534,7 +4506,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4685,10 +4657,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384468</v>
+        <v>122384480</v>
       </c>
       <c r="B35" t="n">
-        <v>91229</v>
+        <v>100451</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4697,41 +4669,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650436</v>
+        <v>650316</v>
       </c>
       <c r="R35" t="n">
-        <v>6674345</v>
+        <v>6674034</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4763,7 +4736,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4773,12 +4746,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4787,24 +4755,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4821,10 +4773,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384397</v>
+        <v>122384417</v>
       </c>
       <c r="B36" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4837,21 +4789,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4863,23 +4815,23 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650406</v>
+        <v>650385</v>
       </c>
       <c r="R36" t="n">
-        <v>6674220</v>
+        <v>6674365</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4908,7 +4860,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4918,7 +4870,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4945,10 +4902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384462</v>
+        <v>122384484</v>
       </c>
       <c r="B37" t="n">
-        <v>90789</v>
+        <v>100451</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4957,41 +4914,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650428</v>
+        <v>650407</v>
       </c>
       <c r="R37" t="n">
-        <v>6674388</v>
+        <v>6674068</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5023,7 +4981,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5033,7 +4991,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5060,10 +5018,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384400</v>
+        <v>122384442</v>
       </c>
       <c r="B38" t="n">
-        <v>57390</v>
+        <v>90754</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5072,39 +5030,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5112,10 +5061,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650362</v>
+        <v>650393</v>
       </c>
       <c r="R38" t="n">
-        <v>6674082</v>
+        <v>6674157</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5147,7 +5096,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5157,7 +5106,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5184,10 +5133,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384404</v>
+        <v>122384437</v>
       </c>
       <c r="B39" t="n">
-        <v>57390</v>
+        <v>80603</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5200,35 +5149,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5236,10 +5176,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650195</v>
+        <v>650387</v>
       </c>
       <c r="R39" t="n">
-        <v>6674100</v>
+        <v>6674259</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5271,7 +5211,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5281,7 +5221,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5308,7 +5248,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384484</v>
+        <v>122384481</v>
       </c>
       <c r="B40" t="n">
         <v>100451</v>
@@ -5352,10 +5292,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650407</v>
+        <v>650230</v>
       </c>
       <c r="R40" t="n">
-        <v>6674068</v>
+        <v>6674064</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5387,7 +5327,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5397,7 +5337,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5424,10 +5364,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384465</v>
+        <v>122384366</v>
       </c>
       <c r="B41" t="n">
-        <v>91075</v>
+        <v>57390</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5440,26 +5380,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5467,10 +5416,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650436</v>
+        <v>650419</v>
       </c>
       <c r="R41" t="n">
-        <v>6674342</v>
+        <v>6674371</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5502,7 +5451,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5512,7 +5461,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5539,10 +5488,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384440</v>
+        <v>122384476</v>
       </c>
       <c r="B42" t="n">
-        <v>80603</v>
+        <v>98185</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5551,30 +5500,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5582,10 +5540,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650077</v>
+        <v>650396</v>
       </c>
       <c r="R42" t="n">
-        <v>6674268</v>
+        <v>6674252</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5617,7 +5575,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5627,7 +5585,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5654,10 +5612,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384485</v>
+        <v>122384443</v>
       </c>
       <c r="B43" t="n">
-        <v>100451</v>
+        <v>90789</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5666,42 +5624,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650432</v>
+        <v>650438</v>
       </c>
       <c r="R43" t="n">
-        <v>6674247</v>
+        <v>6674347</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5733,7 +5690,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5743,7 +5700,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5770,7 +5727,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384407</v>
+        <v>122384371</v>
       </c>
       <c r="B44" t="n">
         <v>57390</v>
@@ -5812,7 +5769,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5822,13 +5779,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650101</v>
+        <v>650400</v>
       </c>
       <c r="R44" t="n">
-        <v>6674120</v>
+        <v>6674206</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5857,7 +5814,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5867,7 +5824,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5894,7 +5851,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384391</v>
+        <v>122384388</v>
       </c>
       <c r="B45" t="n">
         <v>57390</v>
@@ -5936,7 +5893,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5946,10 +5903,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650364</v>
+        <v>650400</v>
       </c>
       <c r="R45" t="n">
-        <v>6674383</v>
+        <v>6674425</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5981,7 +5938,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5991,7 +5948,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6018,10 +5975,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384439</v>
+        <v>122384470</v>
       </c>
       <c r="B46" t="n">
-        <v>80603</v>
+        <v>91229</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6030,25 +5987,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6057,14 +6014,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650238</v>
+        <v>650388</v>
       </c>
       <c r="R46" t="n">
-        <v>6674074</v>
+        <v>6674308</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6096,7 +6053,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6106,12 +6063,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6138,10 +6090,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384406</v>
+        <v>122384477</v>
       </c>
       <c r="B47" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6150,39 +6102,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6190,10 +6142,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650115</v>
+        <v>650415</v>
       </c>
       <c r="R47" t="n">
-        <v>6674245</v>
+        <v>6674216</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6225,7 +6177,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6235,7 +6187,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6262,10 +6214,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384476</v>
+        <v>122384407</v>
       </c>
       <c r="B48" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6274,39 +6226,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6314,10 +6266,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650396</v>
+        <v>650101</v>
       </c>
       <c r="R48" t="n">
-        <v>6674252</v>
+        <v>6674120</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6349,7 +6301,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6359,7 +6311,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6386,10 +6338,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384470</v>
+        <v>122384438</v>
       </c>
       <c r="B49" t="n">
-        <v>91229</v>
+        <v>80603</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6398,25 +6350,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>1049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6425,14 +6377,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650388</v>
+        <v>650353</v>
       </c>
       <c r="R49" t="n">
-        <v>6674308</v>
+        <v>6674235</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6464,7 +6416,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6474,7 +6426,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6501,10 +6458,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384366</v>
+        <v>122384432</v>
       </c>
       <c r="B50" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6513,39 +6470,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6553,10 +6501,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650419</v>
+        <v>650422</v>
       </c>
       <c r="R50" t="n">
-        <v>6674371</v>
+        <v>6674376</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6588,7 +6536,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6598,7 +6546,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6607,8 +6555,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6625,7 +6589,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384403</v>
+        <v>122384410</v>
       </c>
       <c r="B51" t="n">
         <v>57390</v>
@@ -6677,10 +6641,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650237</v>
+        <v>650147</v>
       </c>
       <c r="R51" t="n">
-        <v>6674049</v>
+        <v>6674088</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6712,7 +6676,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6722,7 +6686,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6749,10 +6713,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384412</v>
+        <v>122384487</v>
       </c>
       <c r="B52" t="n">
-        <v>57390</v>
+        <v>105290</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6761,50 +6725,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650399</v>
+        <v>650442</v>
       </c>
       <c r="R52" t="n">
-        <v>6674181</v>
+        <v>6674345</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6836,7 +6792,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6846,7 +6802,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6873,7 +6829,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384388</v>
+        <v>122384406</v>
       </c>
       <c r="B53" t="n">
         <v>57390</v>
@@ -6921,14 +6877,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650400</v>
+        <v>650115</v>
       </c>
       <c r="R53" t="n">
-        <v>6674425</v>
+        <v>6674245</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6960,7 +6916,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6970,7 +6926,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6997,10 +6953,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384443</v>
+        <v>122384404</v>
       </c>
       <c r="B54" t="n">
-        <v>90789</v>
+        <v>57390</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7013,37 +6969,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650438</v>
+        <v>650195</v>
       </c>
       <c r="R54" t="n">
-        <v>6674347</v>
+        <v>6674100</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7075,7 +7040,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7085,7 +7050,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7112,10 +7077,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384472</v>
+        <v>122384468</v>
       </c>
       <c r="B55" t="n">
-        <v>98185</v>
+        <v>91229</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7128,35 +7093,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7164,10 +7120,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650415</v>
+        <v>650436</v>
       </c>
       <c r="R55" t="n">
-        <v>6674360</v>
+        <v>6674345</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7199,7 +7155,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7209,7 +7165,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7218,8 +7179,24 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7236,10 +7213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384438</v>
+        <v>122384403</v>
       </c>
       <c r="B56" t="n">
-        <v>80603</v>
+        <v>57390</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7252,26 +7229,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7279,10 +7265,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650353</v>
+        <v>650237</v>
       </c>
       <c r="R56" t="n">
-        <v>6674235</v>
+        <v>6674049</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7314,7 +7300,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7324,12 +7310,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7356,10 +7337,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384454</v>
+        <v>122384466</v>
       </c>
       <c r="B57" t="n">
-        <v>90789</v>
+        <v>91185</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7368,25 +7349,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7399,10 +7380,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650440</v>
+        <v>650393</v>
       </c>
       <c r="R57" t="n">
-        <v>6674369</v>
+        <v>6674366</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7434,7 +7415,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7444,7 +7425,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7453,8 +7434,24 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7471,10 +7468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384436</v>
+        <v>122384391</v>
       </c>
       <c r="B58" t="n">
-        <v>80603</v>
+        <v>57390</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7487,26 +7484,35 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7514,10 +7520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650363</v>
+        <v>650364</v>
       </c>
       <c r="R58" t="n">
-        <v>6674334</v>
+        <v>6674383</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7549,7 +7555,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7559,7 +7565,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7586,10 +7592,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384466</v>
+        <v>122384473</v>
       </c>
       <c r="B59" t="n">
-        <v>91185</v>
+        <v>98185</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7598,30 +7604,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7629,10 +7644,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650393</v>
+        <v>650400</v>
       </c>
       <c r="R59" t="n">
-        <v>6674366</v>
+        <v>6674415</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7664,7 +7679,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7674,7 +7689,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7683,24 +7698,8 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7717,10 +7716,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384464</v>
+        <v>122384472</v>
       </c>
       <c r="B60" t="n">
-        <v>90789</v>
+        <v>98185</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7729,41 +7728,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650429</v>
+        <v>650415</v>
       </c>
       <c r="R60" t="n">
-        <v>6674188</v>
+        <v>6674360</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7795,7 +7803,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7805,7 +7813,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7832,10 +7840,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384410</v>
+        <v>122384479</v>
       </c>
       <c r="B61" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7844,50 +7852,42 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650147</v>
+        <v>650415</v>
       </c>
       <c r="R61" t="n">
-        <v>6674088</v>
+        <v>6674370</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,10 +7956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399658</v>
+        <v>122399642</v>
       </c>
       <c r="B62" t="n">
-        <v>94803</v>
+        <v>57390</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7968,31 +7968,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8000,10 +8008,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649956</v>
+        <v>650411</v>
       </c>
       <c r="R62" t="n">
-        <v>6674194</v>
+        <v>6674002</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8035,7 +8043,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8045,7 +8053,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8072,7 +8080,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399642</v>
+        <v>122399641</v>
       </c>
       <c r="B63" t="n">
         <v>57390</v>
@@ -8124,10 +8132,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>650411</v>
+        <v>650092</v>
       </c>
       <c r="R63" t="n">
-        <v>6674002</v>
+        <v>6674138</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8159,7 +8167,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8169,7 +8177,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8196,7 +8204,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399673</v>
+        <v>122399672</v>
       </c>
       <c r="B64" t="n">
         <v>100451</v>
@@ -8240,10 +8248,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650321</v>
+        <v>650329</v>
       </c>
       <c r="R64" t="n">
-        <v>6673981</v>
+        <v>6673994</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8275,7 +8283,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8285,7 +8293,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8428,10 +8436,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399672</v>
+        <v>122399656</v>
       </c>
       <c r="B66" t="n">
-        <v>100451</v>
+        <v>94707</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8444,21 +8452,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8472,10 +8480,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>650329</v>
+        <v>649935</v>
       </c>
       <c r="R66" t="n">
-        <v>6673994</v>
+        <v>6674249</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8507,7 +8515,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8517,7 +8525,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8544,10 +8552,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399656</v>
+        <v>122399637</v>
       </c>
       <c r="B67" t="n">
-        <v>94707</v>
+        <v>57390</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8556,31 +8564,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8588,10 +8604,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649935</v>
+        <v>649994</v>
       </c>
       <c r="R67" t="n">
-        <v>6674249</v>
+        <v>6674118</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8623,7 +8639,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8633,7 +8649,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8660,10 +8676,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399650</v>
+        <v>122399640</v>
       </c>
       <c r="B68" t="n">
-        <v>90754</v>
+        <v>57390</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8672,30 +8688,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8703,10 +8728,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650386</v>
+        <v>650059</v>
       </c>
       <c r="R68" t="n">
-        <v>6673912</v>
+        <v>6674144</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8738,7 +8763,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8748,7 +8773,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8775,10 +8800,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399639</v>
+        <v>122399673</v>
       </c>
       <c r="B69" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8787,39 +8812,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8827,10 +8844,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650031</v>
+        <v>650321</v>
       </c>
       <c r="R69" t="n">
-        <v>6674158</v>
+        <v>6673981</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8862,7 +8879,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8872,7 +8889,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8899,10 +8916,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399640</v>
+        <v>122399649</v>
       </c>
       <c r="B70" t="n">
-        <v>57390</v>
+        <v>80603</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8915,35 +8932,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8951,10 +8959,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>650059</v>
+        <v>650383</v>
       </c>
       <c r="R70" t="n">
-        <v>6674144</v>
+        <v>6673928</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8986,7 +8994,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8996,7 +9004,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9023,10 +9031,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399649</v>
+        <v>122399650</v>
       </c>
       <c r="B71" t="n">
-        <v>80603</v>
+        <v>90754</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9035,25 +9043,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9066,10 +9074,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650383</v>
+        <v>650386</v>
       </c>
       <c r="R71" t="n">
-        <v>6673928</v>
+        <v>6673912</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9101,7 +9109,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9111,7 +9119,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9138,10 +9146,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399637</v>
+        <v>122399658</v>
       </c>
       <c r="B72" t="n">
-        <v>57390</v>
+        <v>94803</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9150,39 +9158,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9190,10 +9190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>649994</v>
+        <v>649956</v>
       </c>
       <c r="R72" t="n">
-        <v>6674118</v>
+        <v>6674194</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9262,7 +9262,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399641</v>
+        <v>122399639</v>
       </c>
       <c r="B73" t="n">
         <v>57390</v>
@@ -9304,7 +9304,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650092</v>
+        <v>650031</v>
       </c>
       <c r="R73" t="n">
-        <v>6674138</v>
+        <v>6674158</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9386,14 +9386,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399645</v>
+        <v>122399657</v>
       </c>
       <c r="B74" t="n">
-        <v>57744</v>
+        <v>94803</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9402,27 +9402,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>210</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649902</v>
+        <v>649950</v>
       </c>
       <c r="R74" t="n">
-        <v>6674271</v>
+        <v>6674175</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9498,11 +9498,7 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9622,14 +9618,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399657</v>
+        <v>122399645</v>
       </c>
       <c r="B76" t="n">
-        <v>94803</v>
+        <v>57744</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9638,27 +9634,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9666,10 +9662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>649950</v>
+        <v>649902</v>
       </c>
       <c r="R76" t="n">
-        <v>6674175</v>
+        <v>6674271</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9701,7 +9697,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9711,7 +9707,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9734,7 +9730,11 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -1895,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399652</v>
+        <v>122399628</v>
       </c>
       <c r="B12" t="n">
-        <v>90789</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,30 +1907,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1938,13 +1944,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650328</v>
+        <v>650379</v>
       </c>
       <c r="R12" t="n">
-        <v>6673703</v>
+        <v>6673641</v>
       </c>
       <c r="S12" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1973,7 +1979,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1983,7 +1989,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2010,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399628</v>
+        <v>122399652</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>90789</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2022,36 +2028,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650379</v>
+        <v>650328</v>
       </c>
       <c r="R13" t="n">
-        <v>6673641</v>
+        <v>6673703</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -6090,10 +6090,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384477</v>
+        <v>122384407</v>
       </c>
       <c r="B47" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6102,39 +6102,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650415</v>
+        <v>650101</v>
       </c>
       <c r="R47" t="n">
-        <v>6674216</v>
+        <v>6674120</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6214,10 +6214,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384407</v>
+        <v>122384477</v>
       </c>
       <c r="B48" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6226,39 +6226,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650101</v>
+        <v>650415</v>
       </c>
       <c r="R48" t="n">
-        <v>6674120</v>
+        <v>6674216</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399670</v>
+        <v>122399652</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>90801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650313</v>
+        <v>650328</v>
       </c>
       <c r="R2" t="n">
-        <v>6673680</v>
+        <v>6673703</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399644</v>
+        <v>122399666</v>
       </c>
       <c r="B3" t="n">
-        <v>57744</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650328</v>
+        <v>650369</v>
       </c>
       <c r="R3" t="n">
-        <v>6673703</v>
+        <v>6673665</v>
       </c>
       <c r="S3" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399626</v>
+        <v>122399633</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,34 +927,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -968,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650382</v>
+        <v>650328</v>
       </c>
       <c r="R4" t="n">
-        <v>6673643</v>
+        <v>6673703</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399630</v>
+        <v>122399632</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,20 +1051,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,13 +1072,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1089,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650217</v>
+        <v>650256</v>
       </c>
       <c r="R5" t="n">
-        <v>6673709</v>
+        <v>6673700</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1124,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1285,7 +1287,7 @@
         <v>122399671</v>
       </c>
       <c r="B7" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1398,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399633</v>
+        <v>122399628</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,20 +1412,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1431,16 +1433,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1450,13 +1449,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650328</v>
+        <v>650379</v>
       </c>
       <c r="R8" t="n">
-        <v>6673703</v>
+        <v>6673641</v>
       </c>
       <c r="S8" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399667</v>
+        <v>122399644</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>57749</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,39 +1533,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1574,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650365</v>
+        <v>650328</v>
       </c>
       <c r="R9" t="n">
-        <v>6673701</v>
+        <v>6673703</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1609,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1619,7 +1614,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399632</v>
+        <v>122399626</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,37 +1653,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1698,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650256</v>
+        <v>650382</v>
       </c>
       <c r="R10" t="n">
-        <v>6673700</v>
+        <v>6673643</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1733,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1743,7 +1735,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399666</v>
+        <v>122399667</v>
       </c>
       <c r="B11" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1805,10 +1797,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1818,10 +1814,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650369</v>
+        <v>650365</v>
       </c>
       <c r="R11" t="n">
-        <v>6673665</v>
+        <v>6673701</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1853,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,12 +1859,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,7 +1886,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399628</v>
+        <v>122399630</v>
       </c>
       <c r="B12" t="n">
         <v>5193</v>
@@ -1934,7 +1925,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1944,10 +1935,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650379</v>
+        <v>650217</v>
       </c>
       <c r="R12" t="n">
-        <v>6673641</v>
+        <v>6673709</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1979,7 +1970,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1989,7 +1980,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,10 +2007,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399652</v>
+        <v>122399668</v>
       </c>
       <c r="B13" t="n">
-        <v>90789</v>
+        <v>98197</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,30 +2019,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650328</v>
+        <v>650331</v>
       </c>
       <c r="R13" t="n">
-        <v>6673703</v>
+        <v>6673701</v>
       </c>
       <c r="S13" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2104,7 +2104,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2131,10 +2136,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399668</v>
+        <v>122399670</v>
       </c>
       <c r="B14" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2166,7 +2171,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2183,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650331</v>
+        <v>650313</v>
       </c>
       <c r="R14" t="n">
-        <v>6673701</v>
+        <v>6673680</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2218,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2228,12 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,7 +2263,7 @@
         <v>122399676</v>
       </c>
       <c r="B15" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384464</v>
+        <v>122384371</v>
       </c>
       <c r="B16" t="n">
-        <v>90789</v>
+        <v>57395</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2400,26 +2400,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2427,13 +2436,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650429</v>
+        <v>650400</v>
       </c>
       <c r="R16" t="n">
-        <v>6674188</v>
+        <v>6674206</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2462,7 +2471,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,7 +2481,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2499,10 +2508,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384369</v>
+        <v>122384407</v>
       </c>
       <c r="B17" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2541,20 +2550,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650395</v>
+        <v>650101</v>
       </c>
       <c r="R17" t="n">
-        <v>6674349</v>
+        <v>6674120</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2586,7 +2595,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2596,7 +2605,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2623,10 +2632,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384394</v>
+        <v>122384454</v>
       </c>
       <c r="B18" t="n">
-        <v>57390</v>
+        <v>90801</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2639,46 +2648,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650394</v>
+        <v>650440</v>
       </c>
       <c r="R18" t="n">
-        <v>6674272</v>
+        <v>6674369</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384485</v>
+        <v>122384432</v>
       </c>
       <c r="B19" t="n">
-        <v>100451</v>
+        <v>74691</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2763,38 +2763,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650432</v>
+        <v>650422</v>
       </c>
       <c r="R19" t="n">
-        <v>6674247</v>
+        <v>6674376</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2826,7 +2825,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2836,7 +2835,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2845,8 +2844,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2863,10 +2878,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384462</v>
+        <v>122384470</v>
       </c>
       <c r="B20" t="n">
-        <v>90789</v>
+        <v>91241</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2875,25 +2890,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2906,10 +2921,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650428</v>
+        <v>650388</v>
       </c>
       <c r="R20" t="n">
-        <v>6674388</v>
+        <v>6674308</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2941,7 +2956,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,7 +2966,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2978,10 +2993,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384411</v>
+        <v>122384440</v>
       </c>
       <c r="B21" t="n">
-        <v>57390</v>
+        <v>80608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2994,35 +3009,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3030,10 +3036,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650415</v>
+        <v>650077</v>
       </c>
       <c r="R21" t="n">
-        <v>6674083</v>
+        <v>6674268</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3065,7 +3071,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3075,7 +3081,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3102,10 +3108,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384412</v>
+        <v>122384466</v>
       </c>
       <c r="B22" t="n">
-        <v>57390</v>
+        <v>91197</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3114,50 +3120,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650399</v>
+        <v>650393</v>
       </c>
       <c r="R22" t="n">
-        <v>6674181</v>
+        <v>6674366</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3189,7 +3186,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3199,7 +3196,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3208,8 +3205,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3226,10 +3239,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384439</v>
+        <v>122384434</v>
       </c>
       <c r="B23" t="n">
-        <v>80603</v>
+        <v>74691</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3238,25 +3251,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3265,14 +3278,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650238</v>
+        <v>650407</v>
       </c>
       <c r="R23" t="n">
-        <v>6674074</v>
+        <v>6674363</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3304,7 +3317,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3314,12 +3327,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3346,10 +3354,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384434</v>
+        <v>122384479</v>
       </c>
       <c r="B24" t="n">
-        <v>74686</v>
+        <v>100463</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3362,26 +3370,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3389,10 +3398,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650407</v>
+        <v>650415</v>
       </c>
       <c r="R24" t="n">
-        <v>6674363</v>
+        <v>6674370</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3424,7 +3433,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3434,7 +3443,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3461,10 +3470,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384436</v>
+        <v>122384473</v>
       </c>
       <c r="B25" t="n">
-        <v>80603</v>
+        <v>98197</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3473,30 +3482,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3504,10 +3522,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650363</v>
+        <v>650400</v>
       </c>
       <c r="R25" t="n">
-        <v>6674334</v>
+        <v>6674415</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3539,7 +3557,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3549,7 +3567,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3576,10 +3594,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384454</v>
+        <v>122384484</v>
       </c>
       <c r="B26" t="n">
-        <v>90789</v>
+        <v>100463</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3588,41 +3606,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650440</v>
+        <v>650407</v>
       </c>
       <c r="R26" t="n">
-        <v>6674369</v>
+        <v>6674068</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3654,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3664,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3691,10 +3710,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384483</v>
+        <v>122384442</v>
       </c>
       <c r="B27" t="n">
-        <v>100451</v>
+        <v>90766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3707,27 +3726,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3735,10 +3753,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650238</v>
+        <v>650393</v>
       </c>
       <c r="R27" t="n">
-        <v>6674076</v>
+        <v>6674157</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3770,7 +3788,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3780,7 +3798,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3807,10 +3825,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384395</v>
+        <v>122384483</v>
       </c>
       <c r="B28" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3819,39 +3837,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3859,10 +3869,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650395</v>
+        <v>650238</v>
       </c>
       <c r="R28" t="n">
-        <v>6674254</v>
+        <v>6674076</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3894,7 +3904,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3904,7 +3914,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3931,10 +3941,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384397</v>
+        <v>122384373</v>
       </c>
       <c r="B29" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3979,14 +3989,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650406</v>
+        <v>650373</v>
       </c>
       <c r="R29" t="n">
-        <v>6674220</v>
+        <v>6674389</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4018,7 +4028,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4028,7 +4038,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4055,10 +4065,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384373</v>
+        <v>122384394</v>
       </c>
       <c r="B30" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4103,14 +4113,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650373</v>
+        <v>650394</v>
       </c>
       <c r="R30" t="n">
-        <v>6674389</v>
+        <v>6674272</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4142,7 +4152,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4152,7 +4162,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4179,10 +4189,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384400</v>
+        <v>122384462</v>
       </c>
       <c r="B31" t="n">
-        <v>57390</v>
+        <v>90801</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4195,46 +4205,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650362</v>
+        <v>650428</v>
       </c>
       <c r="R31" t="n">
-        <v>6674082</v>
+        <v>6674388</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4266,7 +4267,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4276,7 +4277,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4303,10 +4304,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384465</v>
+        <v>122384477</v>
       </c>
       <c r="B32" t="n">
-        <v>91075</v>
+        <v>98197</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4315,41 +4316,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650436</v>
+        <v>650415</v>
       </c>
       <c r="R32" t="n">
-        <v>6674342</v>
+        <v>6674216</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4381,7 +4391,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4391,7 +4401,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4418,10 +4428,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384440</v>
+        <v>122384468</v>
       </c>
       <c r="B33" t="n">
-        <v>80603</v>
+        <v>91241</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4430,25 +4440,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4457,14 +4467,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650077</v>
+        <v>650436</v>
       </c>
       <c r="R33" t="n">
-        <v>6674268</v>
+        <v>6674345</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4496,7 +4506,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4506,7 +4516,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4515,8 +4530,24 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4533,10 +4564,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384402</v>
+        <v>122384406</v>
       </c>
       <c r="B34" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4585,10 +4616,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650297</v>
+        <v>650115</v>
       </c>
       <c r="R34" t="n">
-        <v>6674040</v>
+        <v>6674245</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4620,7 +4651,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4630,7 +4661,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4657,10 +4688,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384480</v>
+        <v>122384404</v>
       </c>
       <c r="B35" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4669,31 +4700,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4701,10 +4740,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650316</v>
+        <v>650195</v>
       </c>
       <c r="R35" t="n">
-        <v>6674034</v>
+        <v>6674100</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4736,7 +4775,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4746,7 +4785,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4773,10 +4812,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384417</v>
+        <v>122384391</v>
       </c>
       <c r="B36" t="n">
-        <v>57527</v>
+        <v>57395</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4789,21 +4828,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4815,7 +4854,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4825,13 +4864,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650385</v>
+        <v>650364</v>
       </c>
       <c r="R36" t="n">
-        <v>6674365</v>
+        <v>6674383</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4860,7 +4899,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4870,12 +4909,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4902,10 +4936,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384484</v>
+        <v>122384411</v>
       </c>
       <c r="B37" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4914,31 +4948,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4946,10 +4988,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650407</v>
+        <v>650415</v>
       </c>
       <c r="R37" t="n">
-        <v>6674068</v>
+        <v>6674083</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4981,7 +5023,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4991,7 +5033,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5018,10 +5060,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384442</v>
+        <v>122384410</v>
       </c>
       <c r="B38" t="n">
-        <v>90754</v>
+        <v>57395</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5030,30 +5072,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5061,10 +5112,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650393</v>
+        <v>650147</v>
       </c>
       <c r="R38" t="n">
-        <v>6674157</v>
+        <v>6674088</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5096,7 +5147,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5106,7 +5157,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5133,10 +5184,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384437</v>
+        <v>122384400</v>
       </c>
       <c r="B39" t="n">
-        <v>80603</v>
+        <v>57395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5149,26 +5200,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5176,10 +5236,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650387</v>
+        <v>650362</v>
       </c>
       <c r="R39" t="n">
-        <v>6674259</v>
+        <v>6674082</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5211,7 +5271,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5221,7 +5281,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5248,10 +5308,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384481</v>
+        <v>122384472</v>
       </c>
       <c r="B40" t="n">
-        <v>100451</v>
+        <v>98197</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5260,42 +5320,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650230</v>
+        <v>650415</v>
       </c>
       <c r="R40" t="n">
-        <v>6674064</v>
+        <v>6674360</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5327,7 +5395,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5337,7 +5405,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5364,10 +5432,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384366</v>
+        <v>122384487</v>
       </c>
       <c r="B41" t="n">
-        <v>57390</v>
+        <v>105303</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5376,39 +5444,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5416,10 +5476,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650419</v>
+        <v>650442</v>
       </c>
       <c r="R41" t="n">
-        <v>6674371</v>
+        <v>6674345</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5451,7 +5511,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5461,7 +5521,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5488,10 +5548,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384476</v>
+        <v>122384439</v>
       </c>
       <c r="B42" t="n">
-        <v>98185</v>
+        <v>80608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5500,39 +5560,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5540,10 +5591,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650396</v>
+        <v>650238</v>
       </c>
       <c r="R42" t="n">
-        <v>6674252</v>
+        <v>6674074</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5575,7 +5626,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5585,7 +5636,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5612,10 +5668,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384443</v>
+        <v>122384366</v>
       </c>
       <c r="B43" t="n">
-        <v>90789</v>
+        <v>57395</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5628,26 +5684,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5655,10 +5720,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650438</v>
+        <v>650419</v>
       </c>
       <c r="R43" t="n">
-        <v>6674347</v>
+        <v>6674371</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5690,7 +5755,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5700,7 +5765,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5727,10 +5792,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384371</v>
+        <v>122384388</v>
       </c>
       <c r="B44" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5769,23 +5834,23 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
         <v>650400</v>
       </c>
       <c r="R44" t="n">
-        <v>6674206</v>
+        <v>6674425</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5814,7 +5879,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5824,7 +5889,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5851,10 +5916,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384388</v>
+        <v>122384438</v>
       </c>
       <c r="B45" t="n">
-        <v>57390</v>
+        <v>80608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5867,46 +5932,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650400</v>
+        <v>650353</v>
       </c>
       <c r="R45" t="n">
-        <v>6674425</v>
+        <v>6674235</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5938,7 +5994,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5948,7 +6004,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5975,10 +6036,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384470</v>
+        <v>122384402</v>
       </c>
       <c r="B46" t="n">
-        <v>91229</v>
+        <v>57395</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5987,41 +6048,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650388</v>
+        <v>650297</v>
       </c>
       <c r="R46" t="n">
-        <v>6674308</v>
+        <v>6674040</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6053,7 +6123,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6063,7 +6133,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6090,10 +6160,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384407</v>
+        <v>122384397</v>
       </c>
       <c r="B47" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6142,10 +6212,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650101</v>
+        <v>650406</v>
       </c>
       <c r="R47" t="n">
-        <v>6674120</v>
+        <v>6674220</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6177,7 +6247,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6187,7 +6257,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6214,10 +6284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384477</v>
+        <v>122384403</v>
       </c>
       <c r="B48" t="n">
-        <v>98185</v>
+        <v>57395</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6226,39 +6296,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6266,10 +6336,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650415</v>
+        <v>650237</v>
       </c>
       <c r="R48" t="n">
-        <v>6674216</v>
+        <v>6674049</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6301,7 +6371,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6311,7 +6381,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6338,10 +6408,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384438</v>
+        <v>122384417</v>
       </c>
       <c r="B49" t="n">
-        <v>80603</v>
+        <v>57532</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6354,40 +6424,49 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650353</v>
+        <v>650385</v>
       </c>
       <c r="R49" t="n">
-        <v>6674235</v>
+        <v>6674365</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6416,7 +6495,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6426,12 +6505,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Riklig mängd.</t>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6458,10 +6537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384432</v>
+        <v>122384436</v>
       </c>
       <c r="B50" t="n">
-        <v>74686</v>
+        <v>80608</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6470,25 +6549,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6501,10 +6580,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650422</v>
+        <v>650363</v>
       </c>
       <c r="R50" t="n">
-        <v>6674376</v>
+        <v>6674334</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6536,7 +6615,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6546,7 +6625,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6555,24 +6634,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6589,10 +6652,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384410</v>
+        <v>122384485</v>
       </c>
       <c r="B51" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6601,39 +6664,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6641,10 +6696,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650147</v>
+        <v>650432</v>
       </c>
       <c r="R51" t="n">
-        <v>6674088</v>
+        <v>6674247</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6676,7 +6731,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6686,7 +6741,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6713,10 +6768,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384487</v>
+        <v>122384443</v>
       </c>
       <c r="B52" t="n">
-        <v>105290</v>
+        <v>90801</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6725,31 +6780,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6757,10 +6811,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650442</v>
+        <v>650438</v>
       </c>
       <c r="R52" t="n">
-        <v>6674345</v>
+        <v>6674347</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6792,7 +6846,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6802,7 +6856,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,10 +6883,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384406</v>
+        <v>122384464</v>
       </c>
       <c r="B53" t="n">
-        <v>57390</v>
+        <v>90801</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6845,35 +6899,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6881,10 +6926,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650115</v>
+        <v>650429</v>
       </c>
       <c r="R53" t="n">
-        <v>6674245</v>
+        <v>6674188</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6916,7 +6961,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6926,7 +6971,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6953,10 +6998,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384404</v>
+        <v>122384476</v>
       </c>
       <c r="B54" t="n">
-        <v>57390</v>
+        <v>98197</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6965,39 +7010,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7005,10 +7050,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650195</v>
+        <v>650396</v>
       </c>
       <c r="R54" t="n">
-        <v>6674100</v>
+        <v>6674252</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7040,7 +7085,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7050,7 +7095,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7077,10 +7122,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384468</v>
+        <v>122384465</v>
       </c>
       <c r="B55" t="n">
-        <v>91229</v>
+        <v>91087</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7089,25 +7134,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7123,7 +7168,7 @@
         <v>650436</v>
       </c>
       <c r="R55" t="n">
-        <v>6674345</v>
+        <v>6674342</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7155,7 +7200,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7165,12 +7210,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7179,24 +7219,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7213,10 +7237,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384403</v>
+        <v>122384395</v>
       </c>
       <c r="B56" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7265,10 +7289,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650237</v>
+        <v>650395</v>
       </c>
       <c r="R56" t="n">
-        <v>6674049</v>
+        <v>6674254</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7300,7 +7324,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7310,7 +7334,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7337,10 +7361,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384466</v>
+        <v>122384481</v>
       </c>
       <c r="B57" t="n">
-        <v>91185</v>
+        <v>100463</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7353,37 +7377,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4217</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650393</v>
+        <v>650230</v>
       </c>
       <c r="R57" t="n">
-        <v>6674366</v>
+        <v>6674064</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7415,7 +7440,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7425,7 +7450,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7434,24 +7459,8 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7468,10 +7477,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384391</v>
+        <v>122384412</v>
       </c>
       <c r="B58" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7516,14 +7525,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650364</v>
+        <v>650399</v>
       </c>
       <c r="R58" t="n">
-        <v>6674383</v>
+        <v>6674181</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7555,7 +7564,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7565,7 +7574,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7592,10 +7601,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384473</v>
+        <v>122384437</v>
       </c>
       <c r="B59" t="n">
-        <v>98185</v>
+        <v>80608</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7604,50 +7613,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650400</v>
+        <v>650387</v>
       </c>
       <c r="R59" t="n">
-        <v>6674415</v>
+        <v>6674259</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7716,10 +7716,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384472</v>
+        <v>122384480</v>
       </c>
       <c r="B60" t="n">
-        <v>98185</v>
+        <v>100463</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7728,50 +7728,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650415</v>
+        <v>650316</v>
       </c>
       <c r="R60" t="n">
-        <v>6674360</v>
+        <v>6674034</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7803,7 +7795,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7813,7 +7805,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7840,10 +7832,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384479</v>
+        <v>122384369</v>
       </c>
       <c r="B61" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7852,31 +7844,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650415</v>
+        <v>650395</v>
       </c>
       <c r="R61" t="n">
-        <v>6674370</v>
+        <v>6674349</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7959,7 +7959,7 @@
         <v>122399642</v>
       </c>
       <c r="B62" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8080,10 +8080,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399641</v>
+        <v>122399675</v>
       </c>
       <c r="B63" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8092,39 +8092,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8132,10 +8124,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>650092</v>
+        <v>650473</v>
       </c>
       <c r="R63" t="n">
-        <v>6674138</v>
+        <v>6673911</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8167,7 +8159,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8177,7 +8169,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8207,7 +8199,7 @@
         <v>122399672</v>
       </c>
       <c r="B64" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8320,10 +8312,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399675</v>
+        <v>122399649</v>
       </c>
       <c r="B65" t="n">
-        <v>100451</v>
+        <v>80608</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8332,31 +8324,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8364,10 +8355,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650473</v>
+        <v>650383</v>
       </c>
       <c r="R65" t="n">
-        <v>6673911</v>
+        <v>6673928</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8399,7 +8390,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8409,7 +8400,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8436,10 +8427,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399656</v>
+        <v>122399650</v>
       </c>
       <c r="B66" t="n">
-        <v>94707</v>
+        <v>90766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8452,27 +8443,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8480,10 +8470,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>649935</v>
+        <v>650386</v>
       </c>
       <c r="R66" t="n">
-        <v>6674249</v>
+        <v>6673912</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8515,7 +8505,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8525,7 +8515,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8555,7 +8545,7 @@
         <v>122399637</v>
       </c>
       <c r="B67" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8676,10 +8666,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399640</v>
+        <v>122399673</v>
       </c>
       <c r="B68" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8688,39 +8678,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8728,10 +8710,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650059</v>
+        <v>650321</v>
       </c>
       <c r="R68" t="n">
-        <v>6674144</v>
+        <v>6673981</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8763,7 +8745,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8773,7 +8755,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8800,10 +8782,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399673</v>
+        <v>122399656</v>
       </c>
       <c r="B69" t="n">
-        <v>100451</v>
+        <v>94719</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8816,21 +8798,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8844,10 +8826,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650321</v>
+        <v>649935</v>
       </c>
       <c r="R69" t="n">
-        <v>6673981</v>
+        <v>6674249</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8879,7 +8861,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8889,7 +8871,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8916,10 +8898,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399649</v>
+        <v>122399640</v>
       </c>
       <c r="B70" t="n">
-        <v>80603</v>
+        <v>57395</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8932,26 +8914,35 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8959,10 +8950,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>650383</v>
+        <v>650059</v>
       </c>
       <c r="R70" t="n">
-        <v>6673928</v>
+        <v>6674144</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8994,7 +8985,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9004,7 +8995,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9031,10 +9022,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399650</v>
+        <v>122399639</v>
       </c>
       <c r="B71" t="n">
-        <v>90754</v>
+        <v>57395</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9043,30 +9034,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9074,10 +9074,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650386</v>
+        <v>650031</v>
       </c>
       <c r="R71" t="n">
-        <v>6673912</v>
+        <v>6674158</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9146,10 +9146,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399658</v>
+        <v>122399641</v>
       </c>
       <c r="B72" t="n">
-        <v>94803</v>
+        <v>57395</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9158,31 +9158,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9190,10 +9198,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>649956</v>
+        <v>650092</v>
       </c>
       <c r="R72" t="n">
-        <v>6674194</v>
+        <v>6674138</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9225,7 +9233,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9235,7 +9243,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9262,10 +9270,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399639</v>
+        <v>122399658</v>
       </c>
       <c r="B73" t="n">
-        <v>57390</v>
+        <v>94815</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9274,39 +9282,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650031</v>
+        <v>649956</v>
       </c>
       <c r="R73" t="n">
-        <v>6674158</v>
+        <v>6674194</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9386,10 +9386,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399657</v>
+        <v>122399655</v>
       </c>
       <c r="B74" t="n">
-        <v>94803</v>
+        <v>94719</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9402,21 +9402,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649950</v>
+        <v>649962</v>
       </c>
       <c r="R74" t="n">
-        <v>6674175</v>
+        <v>6674201</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,14 +9502,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399660</v>
+        <v>122399645</v>
       </c>
       <c r="B75" t="n">
-        <v>94803</v>
+        <v>57749</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9518,27 +9518,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649992</v>
+        <v>649902</v>
       </c>
       <c r="R75" t="n">
-        <v>6674192</v>
+        <v>6674271</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9614,18 +9614,22 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399645</v>
+        <v>122399660</v>
       </c>
       <c r="B76" t="n">
-        <v>57744</v>
+        <v>94815</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9634,27 +9638,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>210</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9662,10 +9666,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>649902</v>
+        <v>649992</v>
       </c>
       <c r="R76" t="n">
-        <v>6674271</v>
+        <v>6674192</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9697,7 +9701,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9707,7 +9711,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9730,18 +9734,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122399655</v>
+        <v>122399657</v>
       </c>
       <c r="B77" t="n">
-        <v>94707</v>
+        <v>94815</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9782,10 +9782,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>649962</v>
+        <v>649950</v>
       </c>
       <c r="R77" t="n">
-        <v>6674201</v>
+        <v>6674175</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399652</v>
+        <v>122399667</v>
       </c>
       <c r="B2" t="n">
-        <v>90801</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650328</v>
+        <v>650365</v>
       </c>
       <c r="R2" t="n">
-        <v>6673703</v>
+        <v>6673701</v>
       </c>
       <c r="S2" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399666</v>
+        <v>122399668</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,10 +834,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -838,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650369</v>
+        <v>650331</v>
       </c>
       <c r="R3" t="n">
-        <v>6673665</v>
+        <v>6673701</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst!</t>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399633</v>
+        <v>122399627</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,20 +940,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,16 +961,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -967,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650328</v>
+        <v>650420</v>
       </c>
       <c r="R4" t="n">
-        <v>6673703</v>
+        <v>6673617</v>
       </c>
       <c r="S4" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1049,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399632</v>
+        <v>122399633</v>
       </c>
       <c r="B5" t="n">
         <v>57395</v>
@@ -1081,7 +1091,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1091,13 +1101,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650256</v>
+        <v>650328</v>
       </c>
       <c r="R5" t="n">
-        <v>6673700</v>
+        <v>6673703</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1136,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1146,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399627</v>
+        <v>122399671</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>100468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,32 +1189,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1212,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650420</v>
+        <v>650309</v>
       </c>
       <c r="R6" t="n">
-        <v>6673617</v>
+        <v>6673789</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1247,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1257,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399671</v>
+        <v>122399632</v>
       </c>
       <c r="B7" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,31 +1301,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1328,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650309</v>
+        <v>650256</v>
       </c>
       <c r="R7" t="n">
-        <v>6673789</v>
+        <v>6673700</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1363,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1413,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399628</v>
+        <v>122399644</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>57749</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,16 +1429,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1433,15 +1446,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1449,13 +1461,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650379</v>
+        <v>650328</v>
       </c>
       <c r="R8" t="n">
-        <v>6673641</v>
+        <v>6673703</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,7 +1496,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1506,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,10 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399644</v>
+        <v>122399666</v>
       </c>
       <c r="B9" t="n">
-        <v>57749</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,35 +1545,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1569,13 +1581,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650328</v>
+        <v>650369</v>
       </c>
       <c r="R9" t="n">
-        <v>6673703</v>
+        <v>6673665</v>
       </c>
       <c r="S9" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1604,7 +1616,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,7 +1626,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,10 +1658,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399626</v>
+        <v>122399652</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>90808</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,36 +1670,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1690,13 +1701,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650382</v>
+        <v>650328</v>
       </c>
       <c r="R10" t="n">
-        <v>6673643</v>
+        <v>6673703</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1725,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,7 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399667</v>
+        <v>122399630</v>
       </c>
       <c r="B11" t="n">
-        <v>98197</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1774,39 +1785,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1814,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650365</v>
+        <v>650217</v>
       </c>
       <c r="R11" t="n">
-        <v>6673701</v>
+        <v>6673709</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1849,7 +1857,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,7 +1867,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,7 +1894,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399630</v>
+        <v>122399628</v>
       </c>
       <c r="B12" t="n">
         <v>5193</v>
@@ -1925,7 +1933,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1935,10 +1943,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650217</v>
+        <v>650379</v>
       </c>
       <c r="R12" t="n">
-        <v>6673709</v>
+        <v>6673641</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1970,7 +1978,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1980,7 +1988,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2007,10 +2015,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399668</v>
+        <v>122399670</v>
       </c>
       <c r="B13" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2042,7 +2050,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2059,10 +2067,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650331</v>
+        <v>650313</v>
       </c>
       <c r="R13" t="n">
-        <v>6673701</v>
+        <v>6673680</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2094,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2104,12 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399670</v>
+        <v>122399626</v>
       </c>
       <c r="B14" t="n">
-        <v>98197</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,39 +2151,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650313</v>
+        <v>650382</v>
       </c>
       <c r="R14" t="n">
-        <v>6673680</v>
+        <v>6673643</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,7 +2263,7 @@
         <v>122399676</v>
       </c>
       <c r="B15" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384371</v>
+        <v>122384470</v>
       </c>
       <c r="B16" t="n">
-        <v>57395</v>
+        <v>91246</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,53 +2396,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650400</v>
+        <v>650388</v>
       </c>
       <c r="R16" t="n">
-        <v>6674206</v>
+        <v>6674308</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2471,7 +2462,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2481,7 +2472,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,10 +2499,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384407</v>
+        <v>122384479</v>
       </c>
       <c r="B17" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2520,50 +2511,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650101</v>
+        <v>650415</v>
       </c>
       <c r="R17" t="n">
-        <v>6674120</v>
+        <v>6674370</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2595,7 +2578,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2605,7 +2588,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2632,10 +2615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384454</v>
+        <v>122384411</v>
       </c>
       <c r="B18" t="n">
-        <v>90801</v>
+        <v>57395</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2648,37 +2631,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650440</v>
+        <v>650415</v>
       </c>
       <c r="R18" t="n">
-        <v>6674369</v>
+        <v>6674083</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2710,7 +2702,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2720,7 +2712,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2747,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384432</v>
+        <v>122384477</v>
       </c>
       <c r="B19" t="n">
-        <v>74691</v>
+        <v>98202</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2759,41 +2751,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650422</v>
+        <v>650415</v>
       </c>
       <c r="R19" t="n">
-        <v>6674376</v>
+        <v>6674216</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2825,7 +2826,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2835,7 +2836,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2844,24 +2845,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2878,10 +2863,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384470</v>
+        <v>122384468</v>
       </c>
       <c r="B20" t="n">
-        <v>91241</v>
+        <v>91246</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2921,10 +2906,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650388</v>
+        <v>650436</v>
       </c>
       <c r="R20" t="n">
-        <v>6674308</v>
+        <v>6674345</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2956,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2966,7 +2951,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2975,8 +2965,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2993,10 +2999,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384440</v>
+        <v>122384404</v>
       </c>
       <c r="B21" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3009,26 +3015,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3036,10 +3051,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650077</v>
+        <v>650195</v>
       </c>
       <c r="R21" t="n">
-        <v>6674268</v>
+        <v>6674100</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3071,7 +3086,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3081,7 +3096,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3108,10 +3123,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384466</v>
+        <v>122384487</v>
       </c>
       <c r="B22" t="n">
-        <v>91197</v>
+        <v>105308</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3124,26 +3139,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4217</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3151,10 +3167,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650393</v>
+        <v>650442</v>
       </c>
       <c r="R22" t="n">
-        <v>6674366</v>
+        <v>6674345</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3186,7 +3202,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3196,7 +3212,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3205,24 +3221,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3239,10 +3239,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384434</v>
+        <v>122384440</v>
       </c>
       <c r="B23" t="n">
-        <v>74691</v>
+        <v>80608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3251,25 +3251,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3278,14 +3278,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650407</v>
+        <v>650077</v>
       </c>
       <c r="R23" t="n">
-        <v>6674363</v>
+        <v>6674268</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384479</v>
+        <v>122384454</v>
       </c>
       <c r="B24" t="n">
-        <v>100463</v>
+        <v>90808</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3366,31 +3366,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3398,10 +3397,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650415</v>
+        <v>650440</v>
       </c>
       <c r="R24" t="n">
-        <v>6674370</v>
+        <v>6674369</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3433,7 +3432,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3443,7 +3442,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3470,10 +3469,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384473</v>
+        <v>122384417</v>
       </c>
       <c r="B25" t="n">
-        <v>98197</v>
+        <v>57532</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3482,39 +3481,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3522,13 +3521,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650400</v>
+        <v>650385</v>
       </c>
       <c r="R25" t="n">
-        <v>6674415</v>
+        <v>6674365</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3557,7 +3556,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3567,7 +3566,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3594,10 +3598,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384484</v>
+        <v>122384481</v>
       </c>
       <c r="B26" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3638,10 +3642,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650407</v>
+        <v>650230</v>
       </c>
       <c r="R26" t="n">
-        <v>6674068</v>
+        <v>6674064</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3673,7 +3677,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3687,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3710,10 +3714,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384442</v>
+        <v>122384434</v>
       </c>
       <c r="B27" t="n">
-        <v>90766</v>
+        <v>74691</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3726,21 +3730,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3749,14 +3753,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650393</v>
+        <v>650407</v>
       </c>
       <c r="R27" t="n">
-        <v>6674157</v>
+        <v>6674363</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3788,7 +3792,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3798,7 +3802,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3825,10 +3829,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384483</v>
+        <v>122384442</v>
       </c>
       <c r="B28" t="n">
-        <v>100463</v>
+        <v>90773</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3841,27 +3845,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3869,10 +3872,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650238</v>
+        <v>650393</v>
       </c>
       <c r="R28" t="n">
-        <v>6674076</v>
+        <v>6674157</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3904,7 +3907,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3914,7 +3917,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3941,7 +3944,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384373</v>
+        <v>122384412</v>
       </c>
       <c r="B29" t="n">
         <v>57395</v>
@@ -3983,20 +3986,20 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650373</v>
+        <v>650399</v>
       </c>
       <c r="R29" t="n">
-        <v>6674389</v>
+        <v>6674181</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4028,7 +4031,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4038,7 +4041,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4065,7 +4068,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384394</v>
+        <v>122384388</v>
       </c>
       <c r="B30" t="n">
         <v>57395</v>
@@ -4113,14 +4116,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650394</v>
+        <v>650400</v>
       </c>
       <c r="R30" t="n">
-        <v>6674272</v>
+        <v>6674425</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4152,7 +4155,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4162,7 +4165,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4189,10 +4192,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384462</v>
+        <v>122384366</v>
       </c>
       <c r="B31" t="n">
-        <v>90801</v>
+        <v>57395</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4205,26 +4208,35 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4232,10 +4244,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650428</v>
+        <v>650419</v>
       </c>
       <c r="R31" t="n">
-        <v>6674388</v>
+        <v>6674371</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4267,7 +4279,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4277,7 +4289,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4304,10 +4316,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384477</v>
+        <v>122384476</v>
       </c>
       <c r="B32" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4339,7 +4351,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4356,10 +4368,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650415</v>
+        <v>650396</v>
       </c>
       <c r="R32" t="n">
-        <v>6674216</v>
+        <v>6674252</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4391,7 +4403,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4401,7 +4413,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4428,10 +4440,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384468</v>
+        <v>122384483</v>
       </c>
       <c r="B33" t="n">
-        <v>91241</v>
+        <v>100468</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4440,41 +4452,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650436</v>
+        <v>650238</v>
       </c>
       <c r="R33" t="n">
-        <v>6674345</v>
+        <v>6674076</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4506,7 +4519,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4516,12 +4529,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4530,24 +4538,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4688,7 +4680,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384404</v>
+        <v>122384403</v>
       </c>
       <c r="B35" t="n">
         <v>57395</v>
@@ -4740,10 +4732,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650195</v>
+        <v>650237</v>
       </c>
       <c r="R35" t="n">
-        <v>6674100</v>
+        <v>6674049</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4775,7 +4767,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4785,7 +4777,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4812,10 +4804,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384391</v>
+        <v>122384437</v>
       </c>
       <c r="B36" t="n">
-        <v>57395</v>
+        <v>80608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4828,46 +4820,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650364</v>
+        <v>650387</v>
       </c>
       <c r="R36" t="n">
-        <v>6674383</v>
+        <v>6674259</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4899,7 +4882,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4909,7 +4892,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4936,10 +4919,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384411</v>
+        <v>122384472</v>
       </c>
       <c r="B37" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4948,50 +4931,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
         <v>650415</v>
       </c>
       <c r="R37" t="n">
-        <v>6674083</v>
+        <v>6674360</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5023,7 +5006,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5033,7 +5016,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5060,7 +5043,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384410</v>
+        <v>122384371</v>
       </c>
       <c r="B38" t="n">
         <v>57395</v>
@@ -5102,7 +5085,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5112,13 +5095,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650147</v>
+        <v>650400</v>
       </c>
       <c r="R38" t="n">
-        <v>6674088</v>
+        <v>6674206</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5147,7 +5130,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5157,7 +5140,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5184,10 +5167,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384400</v>
+        <v>122384464</v>
       </c>
       <c r="B39" t="n">
-        <v>57395</v>
+        <v>90808</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5200,35 +5183,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5236,10 +5210,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650362</v>
+        <v>650429</v>
       </c>
       <c r="R39" t="n">
-        <v>6674082</v>
+        <v>6674188</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5271,7 +5245,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5281,7 +5255,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5308,10 +5282,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384472</v>
+        <v>122384397</v>
       </c>
       <c r="B40" t="n">
-        <v>98197</v>
+        <v>57395</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5320,50 +5294,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650415</v>
+        <v>650406</v>
       </c>
       <c r="R40" t="n">
-        <v>6674360</v>
+        <v>6674220</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5395,7 +5369,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5405,7 +5379,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5432,10 +5406,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384487</v>
+        <v>122384480</v>
       </c>
       <c r="B41" t="n">
-        <v>105303</v>
+        <v>100468</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5448,21 +5422,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5472,14 +5446,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650442</v>
+        <v>650316</v>
       </c>
       <c r="R41" t="n">
-        <v>6674345</v>
+        <v>6674034</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5511,7 +5485,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5521,7 +5495,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5548,10 +5522,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384439</v>
+        <v>122384410</v>
       </c>
       <c r="B42" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5564,26 +5538,35 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5591,10 +5574,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650238</v>
+        <v>650147</v>
       </c>
       <c r="R42" t="n">
-        <v>6674074</v>
+        <v>6674088</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5626,7 +5609,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5636,12 +5619,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5668,10 +5646,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384366</v>
+        <v>122384473</v>
       </c>
       <c r="B43" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5680,39 +5658,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5720,10 +5698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650419</v>
+        <v>650400</v>
       </c>
       <c r="R43" t="n">
-        <v>6674371</v>
+        <v>6674415</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5755,7 +5733,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5765,7 +5743,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5792,10 +5770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384388</v>
+        <v>122384485</v>
       </c>
       <c r="B44" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5804,50 +5782,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650400</v>
+        <v>650432</v>
       </c>
       <c r="R44" t="n">
-        <v>6674425</v>
+        <v>6674247</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5879,7 +5849,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5889,7 +5859,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5916,10 +5886,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384438</v>
+        <v>122384402</v>
       </c>
       <c r="B45" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5932,26 +5902,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5959,10 +5938,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650353</v>
+        <v>650297</v>
       </c>
       <c r="R45" t="n">
-        <v>6674235</v>
+        <v>6674040</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5994,7 +5973,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6004,12 +5983,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6036,10 +6010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384402</v>
+        <v>122384462</v>
       </c>
       <c r="B46" t="n">
-        <v>57395</v>
+        <v>90808</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6052,46 +6026,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650297</v>
+        <v>650428</v>
       </c>
       <c r="R46" t="n">
-        <v>6674040</v>
+        <v>6674388</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6123,7 +6088,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6133,7 +6098,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6160,7 +6125,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384397</v>
+        <v>122384373</v>
       </c>
       <c r="B47" t="n">
         <v>57395</v>
@@ -6208,14 +6173,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650406</v>
+        <v>650373</v>
       </c>
       <c r="R47" t="n">
-        <v>6674220</v>
+        <v>6674389</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6247,7 +6212,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6257,7 +6222,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6284,7 +6249,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384403</v>
+        <v>122384395</v>
       </c>
       <c r="B48" t="n">
         <v>57395</v>
@@ -6336,10 +6301,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650237</v>
+        <v>650395</v>
       </c>
       <c r="R48" t="n">
-        <v>6674049</v>
+        <v>6674254</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6371,7 +6336,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6381,7 +6346,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6408,10 +6373,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384417</v>
+        <v>122384369</v>
       </c>
       <c r="B49" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6424,21 +6389,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6450,7 +6415,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6460,13 +6425,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650385</v>
+        <v>650395</v>
       </c>
       <c r="R49" t="n">
-        <v>6674365</v>
+        <v>6674349</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6495,7 +6460,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6505,12 +6470,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6537,10 +6497,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384436</v>
+        <v>122384394</v>
       </c>
       <c r="B50" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6553,37 +6513,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650363</v>
+        <v>650394</v>
       </c>
       <c r="R50" t="n">
-        <v>6674334</v>
+        <v>6674272</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6615,7 +6584,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6625,7 +6594,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6652,10 +6621,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384485</v>
+        <v>122384407</v>
       </c>
       <c r="B51" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6664,31 +6633,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6696,10 +6673,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650432</v>
+        <v>650101</v>
       </c>
       <c r="R51" t="n">
-        <v>6674247</v>
+        <v>6674120</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6731,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6741,7 +6718,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6768,10 +6745,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384443</v>
+        <v>122384438</v>
       </c>
       <c r="B52" t="n">
-        <v>90801</v>
+        <v>80608</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6784,21 +6761,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6807,14 +6784,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650438</v>
+        <v>650353</v>
       </c>
       <c r="R52" t="n">
-        <v>6674347</v>
+        <v>6674235</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6846,7 +6823,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6856,7 +6833,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6883,10 +6865,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384464</v>
+        <v>122384484</v>
       </c>
       <c r="B53" t="n">
-        <v>90801</v>
+        <v>100468</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6895,30 +6877,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6926,10 +6909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650429</v>
+        <v>650407</v>
       </c>
       <c r="R53" t="n">
-        <v>6674188</v>
+        <v>6674068</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6961,7 +6944,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6971,7 +6954,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6998,10 +6981,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384476</v>
+        <v>122384466</v>
       </c>
       <c r="B54" t="n">
-        <v>98197</v>
+        <v>91202</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7010,50 +6993,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650396</v>
+        <v>650393</v>
       </c>
       <c r="R54" t="n">
-        <v>6674252</v>
+        <v>6674366</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7085,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7095,7 +7069,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7104,8 +7078,24 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7122,10 +7112,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384465</v>
+        <v>122384432</v>
       </c>
       <c r="B55" t="n">
-        <v>91087</v>
+        <v>74691</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7134,25 +7124,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7165,10 +7155,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650436</v>
+        <v>650422</v>
       </c>
       <c r="R55" t="n">
-        <v>6674342</v>
+        <v>6674376</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7200,7 +7190,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7210,7 +7200,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7219,8 +7209,24 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7237,10 +7243,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384395</v>
+        <v>122384439</v>
       </c>
       <c r="B56" t="n">
-        <v>57395</v>
+        <v>80608</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7253,35 +7259,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7289,10 +7286,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650395</v>
+        <v>650238</v>
       </c>
       <c r="R56" t="n">
-        <v>6674254</v>
+        <v>6674074</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7324,7 +7321,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7334,7 +7331,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7361,10 +7363,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384481</v>
+        <v>122384443</v>
       </c>
       <c r="B57" t="n">
-        <v>100463</v>
+        <v>90808</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7373,42 +7375,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650230</v>
+        <v>650438</v>
       </c>
       <c r="R57" t="n">
-        <v>6674064</v>
+        <v>6674347</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7440,7 +7441,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7450,7 +7451,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7477,7 +7478,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384412</v>
+        <v>122384391</v>
       </c>
       <c r="B58" t="n">
         <v>57395</v>
@@ -7525,14 +7526,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650399</v>
+        <v>650364</v>
       </c>
       <c r="R58" t="n">
-        <v>6674181</v>
+        <v>6674383</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7564,7 +7565,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7574,7 +7575,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7601,10 +7602,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384437</v>
+        <v>122384400</v>
       </c>
       <c r="B59" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7617,26 +7618,35 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7644,10 +7654,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650387</v>
+        <v>650362</v>
       </c>
       <c r="R59" t="n">
-        <v>6674259</v>
+        <v>6674082</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7679,7 +7689,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7689,7 +7699,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7716,10 +7726,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384480</v>
+        <v>122384436</v>
       </c>
       <c r="B60" t="n">
-        <v>100463</v>
+        <v>80608</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7728,42 +7738,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650316</v>
+        <v>650363</v>
       </c>
       <c r="R60" t="n">
-        <v>6674034</v>
+        <v>6674334</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7795,7 +7804,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7805,7 +7814,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7832,10 +7841,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384369</v>
+        <v>122384465</v>
       </c>
       <c r="B61" t="n">
-        <v>57395</v>
+        <v>91092</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7848,35 +7857,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650395</v>
+        <v>650436</v>
       </c>
       <c r="R61" t="n">
-        <v>6674349</v>
+        <v>6674342</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,7 +7956,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399642</v>
+        <v>122399639</v>
       </c>
       <c r="B62" t="n">
         <v>57395</v>
@@ -7998,7 +7998,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8008,10 +8008,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>650411</v>
+        <v>650031</v>
       </c>
       <c r="R62" t="n">
-        <v>6674002</v>
+        <v>6674158</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8080,10 +8080,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399675</v>
+        <v>122399637</v>
       </c>
       <c r="B63" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8092,31 +8092,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8124,10 +8132,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>650473</v>
+        <v>649994</v>
       </c>
       <c r="R63" t="n">
-        <v>6673911</v>
+        <v>6674118</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8159,7 +8167,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8169,7 +8177,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8199,7 +8207,7 @@
         <v>122399672</v>
       </c>
       <c r="B64" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8312,10 +8320,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399649</v>
+        <v>122399658</v>
       </c>
       <c r="B65" t="n">
-        <v>80608</v>
+        <v>94820</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8324,30 +8332,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1049</v>
+        <v>210</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8355,10 +8364,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650383</v>
+        <v>649956</v>
       </c>
       <c r="R65" t="n">
-        <v>6673928</v>
+        <v>6674194</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8390,7 +8399,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8400,7 +8409,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8430,7 +8439,7 @@
         <v>122399650</v>
       </c>
       <c r="B66" t="n">
-        <v>90766</v>
+        <v>90773</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8542,10 +8551,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399637</v>
+        <v>122399649</v>
       </c>
       <c r="B67" t="n">
-        <v>57395</v>
+        <v>80608</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8558,35 +8567,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649994</v>
+        <v>650383</v>
       </c>
       <c r="R67" t="n">
-        <v>6674118</v>
+        <v>6673928</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8666,10 +8666,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399673</v>
+        <v>122399640</v>
       </c>
       <c r="B68" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8678,31 +8678,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8710,10 +8718,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650321</v>
+        <v>650059</v>
       </c>
       <c r="R68" t="n">
-        <v>6673981</v>
+        <v>6674144</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8745,7 +8753,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8755,7 +8763,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8782,10 +8790,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399656</v>
+        <v>122399642</v>
       </c>
       <c r="B69" t="n">
-        <v>94719</v>
+        <v>57395</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8794,31 +8802,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8826,10 +8842,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>649935</v>
+        <v>650411</v>
       </c>
       <c r="R69" t="n">
-        <v>6674249</v>
+        <v>6674002</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8861,7 +8877,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8871,7 +8887,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8898,10 +8914,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399640</v>
+        <v>122399675</v>
       </c>
       <c r="B70" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8910,39 +8926,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8950,10 +8958,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>650059</v>
+        <v>650473</v>
       </c>
       <c r="R70" t="n">
-        <v>6674144</v>
+        <v>6673911</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8985,7 +8993,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8995,7 +9003,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9022,10 +9030,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399639</v>
+        <v>122399656</v>
       </c>
       <c r="B71" t="n">
-        <v>57395</v>
+        <v>94724</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9034,39 +9042,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9074,10 +9074,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650031</v>
+        <v>649935</v>
       </c>
       <c r="R71" t="n">
-        <v>6674158</v>
+        <v>6674249</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9146,10 +9146,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399641</v>
+        <v>122399673</v>
       </c>
       <c r="B72" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9158,39 +9158,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9198,10 +9190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>650092</v>
+        <v>650321</v>
       </c>
       <c r="R72" t="n">
-        <v>6674138</v>
+        <v>6673981</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9233,7 +9225,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9243,7 +9235,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9270,10 +9262,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399658</v>
+        <v>122399641</v>
       </c>
       <c r="B73" t="n">
-        <v>94815</v>
+        <v>57395</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9282,31 +9274,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>649956</v>
+        <v>650092</v>
       </c>
       <c r="R73" t="n">
-        <v>6674194</v>
+        <v>6674138</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9386,10 +9386,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399655</v>
+        <v>122399657</v>
       </c>
       <c r="B74" t="n">
-        <v>94719</v>
+        <v>94820</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9402,21 +9402,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649962</v>
+        <v>649950</v>
       </c>
       <c r="R74" t="n">
-        <v>6674201</v>
+        <v>6674175</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,14 +9502,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399645</v>
+        <v>122399660</v>
       </c>
       <c r="B75" t="n">
-        <v>57749</v>
+        <v>94820</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9518,27 +9518,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>210</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649902</v>
+        <v>649992</v>
       </c>
       <c r="R75" t="n">
-        <v>6674271</v>
+        <v>6674192</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9614,22 +9614,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399660</v>
+        <v>122399645</v>
       </c>
       <c r="B76" t="n">
-        <v>94815</v>
+        <v>57749</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9638,27 +9634,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9666,10 +9662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>649992</v>
+        <v>649902</v>
       </c>
       <c r="R76" t="n">
-        <v>6674192</v>
+        <v>6674271</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9701,7 +9697,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9711,7 +9707,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9734,14 +9730,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122399657</v>
+        <v>122399655</v>
       </c>
       <c r="B77" t="n">
-        <v>94815</v>
+        <v>94724</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9782,10 +9782,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>649950</v>
+        <v>649962</v>
       </c>
       <c r="R77" t="n">
-        <v>6674175</v>
+        <v>6674201</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -1289,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399632</v>
+        <v>122399644</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,20 +1301,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1329,11 +1329,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1341,13 +1337,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650256</v>
+        <v>650328</v>
       </c>
       <c r="R7" t="n">
-        <v>6673700</v>
+        <v>6673703</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1382,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399644</v>
+        <v>122399632</v>
       </c>
       <c r="B8" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,20 +1421,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1453,7 +1449,11 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1461,13 +1461,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650328</v>
+        <v>650256</v>
       </c>
       <c r="R8" t="n">
-        <v>6673703</v>
+        <v>6673700</v>
       </c>
       <c r="S8" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384487</v>
+        <v>122384440</v>
       </c>
       <c r="B22" t="n">
-        <v>105308</v>
+        <v>80608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3135,42 +3135,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650442</v>
+        <v>650077</v>
       </c>
       <c r="R22" t="n">
-        <v>6674345</v>
+        <v>6674268</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3202,7 +3201,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3212,7 +3211,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3239,10 +3238,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384440</v>
+        <v>122384454</v>
       </c>
       <c r="B23" t="n">
-        <v>80608</v>
+        <v>90808</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3255,21 +3254,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3278,14 +3277,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650077</v>
+        <v>650440</v>
       </c>
       <c r="R23" t="n">
-        <v>6674268</v>
+        <v>6674369</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3317,7 +3316,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3327,7 +3326,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3354,10 +3353,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384454</v>
+        <v>122384417</v>
       </c>
       <c r="B24" t="n">
-        <v>90808</v>
+        <v>57532</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3370,26 +3369,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3397,13 +3405,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650440</v>
+        <v>650385</v>
       </c>
       <c r="R24" t="n">
-        <v>6674369</v>
+        <v>6674365</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3432,7 +3440,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3442,7 +3450,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3469,10 +3482,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384417</v>
+        <v>122384487</v>
       </c>
       <c r="B25" t="n">
-        <v>57532</v>
+        <v>105308</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3481,39 +3494,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3521,13 +3526,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650385</v>
+        <v>650442</v>
       </c>
       <c r="R25" t="n">
-        <v>6674365</v>
+        <v>6674345</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3556,7 +3561,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3566,12 +3571,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3714,10 +3714,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384434</v>
+        <v>122384442</v>
       </c>
       <c r="B27" t="n">
-        <v>74691</v>
+        <v>90773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,21 +3730,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3753,14 +3753,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650407</v>
+        <v>650393</v>
       </c>
       <c r="R27" t="n">
-        <v>6674363</v>
+        <v>6674157</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384442</v>
+        <v>122384434</v>
       </c>
       <c r="B28" t="n">
-        <v>90773</v>
+        <v>74691</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3845,21 +3845,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3868,14 +3868,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650393</v>
+        <v>650407</v>
       </c>
       <c r="R28" t="n">
-        <v>6674157</v>
+        <v>6674363</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384485</v>
+        <v>122384402</v>
       </c>
       <c r="B44" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5782,31 +5782,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5814,10 +5822,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650432</v>
+        <v>650297</v>
       </c>
       <c r="R44" t="n">
-        <v>6674247</v>
+        <v>6674040</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5849,7 +5857,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5859,7 +5867,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5886,10 +5894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384402</v>
+        <v>122384485</v>
       </c>
       <c r="B45" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5898,39 +5906,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650297</v>
+        <v>650432</v>
       </c>
       <c r="R45" t="n">
-        <v>6674040</v>
+        <v>6674247</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -2863,10 +2863,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384468</v>
+        <v>122384404</v>
       </c>
       <c r="B20" t="n">
-        <v>91246</v>
+        <v>57395</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2875,41 +2875,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650436</v>
+        <v>650195</v>
       </c>
       <c r="R20" t="n">
-        <v>6674345</v>
+        <v>6674100</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2941,7 +2950,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,12 +2960,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2965,24 +2969,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2999,10 +2987,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384404</v>
+        <v>122384468</v>
       </c>
       <c r="B21" t="n">
-        <v>57395</v>
+        <v>91246</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3011,50 +2999,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650195</v>
+        <v>650436</v>
       </c>
       <c r="R21" t="n">
-        <v>6674100</v>
+        <v>6674345</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3086,7 +3065,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3096,7 +3075,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3105,8 +3089,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384440</v>
+        <v>122384487</v>
       </c>
       <c r="B22" t="n">
-        <v>80608</v>
+        <v>105308</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3135,41 +3135,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650077</v>
+        <v>650442</v>
       </c>
       <c r="R22" t="n">
-        <v>6674268</v>
+        <v>6674345</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3201,7 +3202,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3211,7 +3212,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3238,10 +3239,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384454</v>
+        <v>122384440</v>
       </c>
       <c r="B23" t="n">
-        <v>90808</v>
+        <v>80608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3254,21 +3255,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3277,14 +3278,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650440</v>
+        <v>650077</v>
       </c>
       <c r="R23" t="n">
-        <v>6674369</v>
+        <v>6674268</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3316,7 +3317,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3326,7 +3327,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3353,10 +3354,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384417</v>
+        <v>122384454</v>
       </c>
       <c r="B24" t="n">
-        <v>57532</v>
+        <v>90808</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3369,35 +3370,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3405,13 +3397,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650385</v>
+        <v>650440</v>
       </c>
       <c r="R24" t="n">
-        <v>6674365</v>
+        <v>6674369</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3440,7 +3432,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3450,12 +3442,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3482,10 +3469,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384487</v>
+        <v>122384417</v>
       </c>
       <c r="B25" t="n">
-        <v>105308</v>
+        <v>57532</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3494,31 +3481,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3526,13 +3521,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650442</v>
+        <v>650385</v>
       </c>
       <c r="R25" t="n">
-        <v>6674345</v>
+        <v>6674365</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3561,7 +3556,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3571,7 +3566,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3714,10 +3714,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384442</v>
+        <v>122384434</v>
       </c>
       <c r="B27" t="n">
-        <v>90773</v>
+        <v>74691</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,21 +3730,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3753,14 +3753,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650393</v>
+        <v>650407</v>
       </c>
       <c r="R27" t="n">
-        <v>6674157</v>
+        <v>6674363</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384434</v>
+        <v>122384442</v>
       </c>
       <c r="B28" t="n">
-        <v>74691</v>
+        <v>90773</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3845,21 +3845,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3868,14 +3868,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650407</v>
+        <v>650393</v>
       </c>
       <c r="R28" t="n">
-        <v>6674363</v>
+        <v>6674157</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384402</v>
+        <v>122384485</v>
       </c>
       <c r="B44" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5782,39 +5782,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5822,10 +5814,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650297</v>
+        <v>650432</v>
       </c>
       <c r="R44" t="n">
-        <v>6674040</v>
+        <v>6674247</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5857,7 +5849,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5867,7 +5859,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5894,10 +5886,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384485</v>
+        <v>122384402</v>
       </c>
       <c r="B45" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5906,31 +5898,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650432</v>
+        <v>650297</v>
       </c>
       <c r="R45" t="n">
-        <v>6674247</v>
+        <v>6674040</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399667</v>
+        <v>122399671</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>100477</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650365</v>
+        <v>650309</v>
       </c>
       <c r="R2" t="n">
-        <v>6673701</v>
+        <v>6673789</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399668</v>
+        <v>122399626</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,39 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650331</v>
+        <v>650382</v>
       </c>
       <c r="R3" t="n">
-        <v>6673701</v>
+        <v>6673643</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -886,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399627</v>
+        <v>122399644</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>57749</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,16 +918,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -961,15 +930,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -977,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650420</v>
+        <v>650328</v>
       </c>
       <c r="R4" t="n">
-        <v>6673617</v>
+        <v>6673703</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,11 +1035,6 @@
       <c r="E5" t="n">
         <v>100049</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1173,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399671</v>
+        <v>122399628</v>
       </c>
       <c r="B6" t="n">
-        <v>100468</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,27 +1152,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>105930</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1217,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650309</v>
+        <v>650379</v>
       </c>
       <c r="R6" t="n">
-        <v>6673789</v>
+        <v>6673641</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1252,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399644</v>
+        <v>122399666</v>
       </c>
       <c r="B7" t="n">
-        <v>57749</v>
+        <v>98211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,35 +1264,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1337,13 +1295,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650328</v>
+        <v>650369</v>
       </c>
       <c r="R7" t="n">
-        <v>6673703</v>
+        <v>6673665</v>
       </c>
       <c r="S7" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,7 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399632</v>
+        <v>122399652</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,35 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1461,13 +1410,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650256</v>
+        <v>650328</v>
       </c>
       <c r="R8" t="n">
-        <v>6673700</v>
+        <v>6673703</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1506,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399666</v>
+        <v>122399630</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,35 +1494,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>105930</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1581,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650369</v>
+        <v>650217</v>
       </c>
       <c r="R9" t="n">
-        <v>6673665</v>
+        <v>6673709</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1616,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1626,12 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399652</v>
+        <v>122399632</v>
       </c>
       <c r="B10" t="n">
-        <v>90808</v>
+        <v>57395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,26 +1614,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1701,13 +1645,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650328</v>
+        <v>650256</v>
       </c>
       <c r="R10" t="n">
-        <v>6673703</v>
+        <v>6673700</v>
       </c>
       <c r="S10" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1736,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,7 +1717,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399630</v>
+        <v>122399627</v>
       </c>
       <c r="B11" t="n">
         <v>5193</v>
@@ -1790,11 +1734,6 @@
       </c>
       <c r="E11" t="n">
         <v>105930</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1812,7 +1751,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1822,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650217</v>
+        <v>650420</v>
       </c>
       <c r="R11" t="n">
-        <v>6673709</v>
+        <v>6673617</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1857,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1867,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399628</v>
+        <v>122399667</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>98211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,36 +1845,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1943,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650379</v>
+        <v>650365</v>
       </c>
       <c r="R12" t="n">
-        <v>6673641</v>
+        <v>6673701</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1978,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1988,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399670</v>
+        <v>122399668</v>
       </c>
       <c r="B13" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,11 +1970,6 @@
       <c r="E13" t="n">
         <v>220787</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2050,7 +1982,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2067,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650313</v>
+        <v>650331</v>
       </c>
       <c r="R13" t="n">
-        <v>6673680</v>
+        <v>6673701</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2102,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2044,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399626</v>
+        <v>122399670</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>98211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,36 +2088,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650382</v>
+        <v>650313</v>
       </c>
       <c r="R14" t="n">
-        <v>6673643</v>
+        <v>6673680</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2223,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2168,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,7 +2198,7 @@
         <v>122399676</v>
       </c>
       <c r="B15" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2277,11 +2212,6 @@
       </c>
       <c r="E15" t="n">
         <v>221144</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2384,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384470</v>
+        <v>122384432</v>
       </c>
       <c r="B16" t="n">
-        <v>91246</v>
+        <v>74692</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,25 +2326,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6426</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650388</v>
+        <v>650422</v>
       </c>
       <c r="R16" t="n">
-        <v>6674308</v>
+        <v>6674376</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2462,7 +2387,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,7 +2397,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,8 +2406,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2499,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384479</v>
+        <v>122384403</v>
       </c>
       <c r="B17" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2511,42 +2447,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650415</v>
+        <v>650237</v>
       </c>
       <c r="R17" t="n">
-        <v>6674370</v>
+        <v>6674049</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2578,7 +2517,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2588,7 +2527,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,10 +2554,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384411</v>
+        <v>122384442</v>
       </c>
       <c r="B18" t="n">
-        <v>57395</v>
+        <v>90778</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2627,39 +2566,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2667,10 +2592,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650415</v>
+        <v>650393</v>
       </c>
       <c r="R18" t="n">
-        <v>6674083</v>
+        <v>6674157</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2702,7 +2627,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2712,7 +2637,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,10 +2664,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384477</v>
+        <v>122384366</v>
       </c>
       <c r="B19" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2751,50 +2676,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650415</v>
+        <v>650419</v>
       </c>
       <c r="R19" t="n">
-        <v>6674216</v>
+        <v>6674371</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2826,7 +2746,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2836,7 +2756,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2863,10 +2783,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384404</v>
+        <v>122384487</v>
       </c>
       <c r="B20" t="n">
-        <v>57395</v>
+        <v>105317</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2875,50 +2795,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650195</v>
+        <v>650442</v>
       </c>
       <c r="R20" t="n">
-        <v>6674100</v>
+        <v>6674345</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2950,7 +2857,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2960,7 +2867,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2987,10 +2894,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384468</v>
+        <v>122384395</v>
       </c>
       <c r="B21" t="n">
-        <v>91246</v>
+        <v>57395</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2999,41 +2906,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650436</v>
+        <v>650395</v>
       </c>
       <c r="R21" t="n">
-        <v>6674345</v>
+        <v>6674254</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3065,7 +2976,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3075,12 +2986,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3089,24 +2995,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3123,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384487</v>
+        <v>122384369</v>
       </c>
       <c r="B22" t="n">
-        <v>105308</v>
+        <v>57395</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3135,31 +3025,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3167,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650442</v>
+        <v>650395</v>
       </c>
       <c r="R22" t="n">
-        <v>6674345</v>
+        <v>6674349</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3202,7 +3095,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3212,7 +3105,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3239,10 +3132,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384440</v>
+        <v>122384485</v>
       </c>
       <c r="B23" t="n">
-        <v>80608</v>
+        <v>100477</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3251,30 +3144,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3282,10 +3171,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650077</v>
+        <v>650432</v>
       </c>
       <c r="R23" t="n">
-        <v>6674268</v>
+        <v>6674247</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3317,7 +3206,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3327,7 +3216,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3354,10 +3243,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384454</v>
+        <v>122384470</v>
       </c>
       <c r="B24" t="n">
-        <v>90808</v>
+        <v>91251</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3366,25 +3255,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>1209</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3397,10 +3281,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650440</v>
+        <v>650388</v>
       </c>
       <c r="R24" t="n">
-        <v>6674369</v>
+        <v>6674308</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3432,7 +3316,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3442,7 +3326,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3469,10 +3353,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384417</v>
+        <v>122384439</v>
       </c>
       <c r="B25" t="n">
-        <v>57532</v>
+        <v>80609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3485,49 +3369,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>1049</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650385</v>
+        <v>650238</v>
       </c>
       <c r="R25" t="n">
-        <v>6674365</v>
+        <v>6674074</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3556,7 +3426,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3566,12 +3436,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3598,10 +3468,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384481</v>
+        <v>122384484</v>
       </c>
       <c r="B26" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3615,11 +3485,6 @@
       </c>
       <c r="E26" t="n">
         <v>222498</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3642,10 +3507,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650230</v>
+        <v>650407</v>
       </c>
       <c r="R26" t="n">
-        <v>6674064</v>
+        <v>6674068</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3677,7 +3542,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3687,7 +3552,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3714,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384434</v>
+        <v>122384391</v>
       </c>
       <c r="B27" t="n">
-        <v>74691</v>
+        <v>57395</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3726,30 +3591,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3757,10 +3626,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650407</v>
+        <v>650364</v>
       </c>
       <c r="R27" t="n">
-        <v>6674363</v>
+        <v>6674383</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3792,7 +3661,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3802,7 +3671,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3829,10 +3698,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384442</v>
+        <v>122384406</v>
       </c>
       <c r="B28" t="n">
-        <v>90773</v>
+        <v>57395</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3841,30 +3710,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3872,10 +3745,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650393</v>
+        <v>650115</v>
       </c>
       <c r="R28" t="n">
-        <v>6674157</v>
+        <v>6674245</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3907,7 +3780,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3917,7 +3790,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,10 +3817,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384412</v>
+        <v>122384468</v>
       </c>
       <c r="B29" t="n">
-        <v>57395</v>
+        <v>91251</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3956,50 +3829,36 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1209</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650399</v>
+        <v>650436</v>
       </c>
       <c r="R29" t="n">
-        <v>6674181</v>
+        <v>6674345</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4031,7 +3890,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4041,7 +3900,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4050,8 +3914,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4068,10 +3943,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384388</v>
+        <v>122384464</v>
       </c>
       <c r="B30" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4084,46 +3959,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650400</v>
+        <v>650429</v>
       </c>
       <c r="R30" t="n">
-        <v>6674425</v>
+        <v>6674188</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4155,7 +4016,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4165,7 +4026,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4192,7 +4053,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384366</v>
+        <v>122384373</v>
       </c>
       <c r="B31" t="n">
         <v>57395</v>
@@ -4209,11 +4070,6 @@
       </c>
       <c r="E31" t="n">
         <v>100049</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4234,7 +4090,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4244,10 +4100,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650419</v>
+        <v>650373</v>
       </c>
       <c r="R31" t="n">
-        <v>6674371</v>
+        <v>6674389</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4279,7 +4135,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4289,7 +4145,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4316,10 +4172,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384476</v>
+        <v>122384437</v>
       </c>
       <c r="B32" t="n">
-        <v>98202</v>
+        <v>80609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4328,39 +4184,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>1049</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4368,10 +4210,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650396</v>
+        <v>650387</v>
       </c>
       <c r="R32" t="n">
-        <v>6674252</v>
+        <v>6674259</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4403,7 +4245,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4413,7 +4255,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4440,10 +4282,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384483</v>
+        <v>122384402</v>
       </c>
       <c r="B33" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4452,31 +4294,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4484,10 +4329,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650238</v>
+        <v>650297</v>
       </c>
       <c r="R33" t="n">
-        <v>6674076</v>
+        <v>6674040</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4519,7 +4364,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4529,7 +4374,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4556,7 +4401,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384406</v>
+        <v>122384410</v>
       </c>
       <c r="B34" t="n">
         <v>57395</v>
@@ -4573,11 +4418,6 @@
       </c>
       <c r="E34" t="n">
         <v>100049</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4598,7 +4438,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4608,10 +4448,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650115</v>
+        <v>650147</v>
       </c>
       <c r="R34" t="n">
-        <v>6674245</v>
+        <v>6674088</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4643,7 +4483,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4653,7 +4493,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4680,7 +4520,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384403</v>
+        <v>122384400</v>
       </c>
       <c r="B35" t="n">
         <v>57395</v>
@@ -4697,11 +4537,6 @@
       </c>
       <c r="E35" t="n">
         <v>100049</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4722,7 +4557,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4732,10 +4567,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650237</v>
+        <v>650362</v>
       </c>
       <c r="R35" t="n">
-        <v>6674049</v>
+        <v>6674082</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4767,7 +4602,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4777,7 +4612,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4804,10 +4639,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384437</v>
+        <v>122384388</v>
       </c>
       <c r="B36" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4820,37 +4655,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650387</v>
+        <v>650400</v>
       </c>
       <c r="R36" t="n">
-        <v>6674259</v>
+        <v>6674425</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4882,7 +4721,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4892,7 +4731,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4919,10 +4758,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384472</v>
+        <v>122384404</v>
       </c>
       <c r="B37" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4931,50 +4770,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650415</v>
+        <v>650195</v>
       </c>
       <c r="R37" t="n">
-        <v>6674360</v>
+        <v>6674100</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5006,7 +4840,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5016,7 +4850,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5043,10 +4877,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384371</v>
+        <v>122384480</v>
       </c>
       <c r="B38" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5055,39 +4889,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5095,13 +4916,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650400</v>
+        <v>650316</v>
       </c>
       <c r="R38" t="n">
-        <v>6674206</v>
+        <v>6674034</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5130,7 +4951,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5140,7 +4961,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5167,10 +4988,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384464</v>
+        <v>122384479</v>
       </c>
       <c r="B39" t="n">
-        <v>90808</v>
+        <v>100477</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5179,41 +5000,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650429</v>
+        <v>650415</v>
       </c>
       <c r="R39" t="n">
-        <v>6674188</v>
+        <v>6674370</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5245,7 +5062,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5255,7 +5072,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5282,10 +5099,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384397</v>
+        <v>122384462</v>
       </c>
       <c r="B40" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5298,46 +5115,32 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650406</v>
+        <v>650428</v>
       </c>
       <c r="R40" t="n">
-        <v>6674220</v>
+        <v>6674388</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5369,7 +5172,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5379,7 +5182,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5406,10 +5209,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384480</v>
+        <v>122384476</v>
       </c>
       <c r="B41" t="n">
-        <v>100468</v>
+        <v>98211</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5418,29 +5221,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5450,10 +5256,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650316</v>
+        <v>650396</v>
       </c>
       <c r="R41" t="n">
-        <v>6674034</v>
+        <v>6674252</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5485,7 +5291,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5495,7 +5301,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5522,7 +5328,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384410</v>
+        <v>122384411</v>
       </c>
       <c r="B42" t="n">
         <v>57395</v>
@@ -5539,11 +5345,6 @@
       </c>
       <c r="E42" t="n">
         <v>100049</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5574,10 +5375,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650147</v>
+        <v>650415</v>
       </c>
       <c r="R42" t="n">
-        <v>6674088</v>
+        <v>6674083</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5609,7 +5410,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5619,7 +5420,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5646,10 +5447,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384473</v>
+        <v>122384436</v>
       </c>
       <c r="B43" t="n">
-        <v>98202</v>
+        <v>80609</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5658,39 +5459,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>1049</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5698,10 +5485,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650400</v>
+        <v>650363</v>
       </c>
       <c r="R43" t="n">
-        <v>6674415</v>
+        <v>6674334</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5733,7 +5520,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5743,7 +5530,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5770,10 +5557,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384485</v>
+        <v>122384473</v>
       </c>
       <c r="B44" t="n">
-        <v>100468</v>
+        <v>98211</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5782,42 +5569,45 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650432</v>
+        <v>650400</v>
       </c>
       <c r="R44" t="n">
-        <v>6674247</v>
+        <v>6674415</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5849,7 +5639,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5859,7 +5649,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5886,10 +5676,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384402</v>
+        <v>122384472</v>
       </c>
       <c r="B45" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5898,50 +5688,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650297</v>
+        <v>650415</v>
       </c>
       <c r="R45" t="n">
-        <v>6674040</v>
+        <v>6674360</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5973,7 +5758,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5983,7 +5768,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6010,10 +5795,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384462</v>
+        <v>122384481</v>
       </c>
       <c r="B46" t="n">
-        <v>90808</v>
+        <v>100477</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6022,41 +5807,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650428</v>
+        <v>650230</v>
       </c>
       <c r="R46" t="n">
-        <v>6674388</v>
+        <v>6674064</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6088,7 +5869,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6098,7 +5879,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6125,10 +5906,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384373</v>
+        <v>122384443</v>
       </c>
       <c r="B47" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6141,35 +5922,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6177,10 +5944,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650373</v>
+        <v>650438</v>
       </c>
       <c r="R47" t="n">
-        <v>6674389</v>
+        <v>6674347</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6212,7 +5979,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6222,7 +5989,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6249,7 +6016,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384395</v>
+        <v>122384371</v>
       </c>
       <c r="B48" t="n">
         <v>57395</v>
@@ -6266,11 +6033,6 @@
       </c>
       <c r="E48" t="n">
         <v>100049</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6291,7 +6053,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6301,13 +6063,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650395</v>
+        <v>650400</v>
       </c>
       <c r="R48" t="n">
-        <v>6674254</v>
+        <v>6674206</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6336,7 +6098,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6346,7 +6108,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6373,7 +6135,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384369</v>
+        <v>122384407</v>
       </c>
       <c r="B49" t="n">
         <v>57395</v>
@@ -6390,11 +6152,6 @@
       </c>
       <c r="E49" t="n">
         <v>100049</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6415,20 +6172,20 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650395</v>
+        <v>650101</v>
       </c>
       <c r="R49" t="n">
-        <v>6674349</v>
+        <v>6674120</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6460,7 +6217,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6470,7 +6227,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6497,10 +6254,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384394</v>
+        <v>122384465</v>
       </c>
       <c r="B50" t="n">
-        <v>57395</v>
+        <v>91097</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6513,46 +6270,32 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>658</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650394</v>
+        <v>650436</v>
       </c>
       <c r="R50" t="n">
-        <v>6674272</v>
+        <v>6674342</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6584,7 +6327,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6594,7 +6337,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,10 +6364,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384407</v>
+        <v>122384440</v>
       </c>
       <c r="B51" t="n">
-        <v>57395</v>
+        <v>80609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6637,35 +6380,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1049</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6673,10 +6402,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650101</v>
+        <v>650077</v>
       </c>
       <c r="R51" t="n">
-        <v>6674120</v>
+        <v>6674268</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6708,7 +6437,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6718,7 +6447,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6745,10 +6474,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384438</v>
+        <v>122384417</v>
       </c>
       <c r="B52" t="n">
-        <v>80608</v>
+        <v>57532</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6761,40 +6490,44 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650353</v>
+        <v>650385</v>
       </c>
       <c r="R52" t="n">
-        <v>6674235</v>
+        <v>6674365</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6823,7 +6556,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6833,12 +6566,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Riklig mängd.</t>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6865,10 +6598,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384484</v>
+        <v>122384438</v>
       </c>
       <c r="B53" t="n">
-        <v>100468</v>
+        <v>80609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6877,31 +6610,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>1049</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6909,10 +6636,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650407</v>
+        <v>650353</v>
       </c>
       <c r="R53" t="n">
-        <v>6674068</v>
+        <v>6674235</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6944,7 +6671,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6954,7 +6681,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6984,7 +6716,7 @@
         <v>122384466</v>
       </c>
       <c r="B54" t="n">
-        <v>91202</v>
+        <v>91207</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6998,11 +6730,6 @@
       </c>
       <c r="E54" t="n">
         <v>4217</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Blodticka</t>
-        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -7082,11 +6809,6 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AK54" t="inlineStr">
         <is>
           <t>Pinus sylvestris</t>
@@ -7112,10 +6834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384432</v>
+        <v>122384412</v>
       </c>
       <c r="B55" t="n">
-        <v>74691</v>
+        <v>57395</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7124,41 +6846,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650422</v>
+        <v>650399</v>
       </c>
       <c r="R55" t="n">
-        <v>6674376</v>
+        <v>6674181</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7190,7 +6916,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7200,7 +6926,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7209,24 +6935,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7243,10 +6953,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384439</v>
+        <v>122384397</v>
       </c>
       <c r="B56" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7259,26 +6969,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7286,10 +7000,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650238</v>
+        <v>650406</v>
       </c>
       <c r="R56" t="n">
-        <v>6674074</v>
+        <v>6674220</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7321,7 +7035,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7331,12 +7045,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7363,10 +7072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384443</v>
+        <v>122384477</v>
       </c>
       <c r="B57" t="n">
-        <v>90808</v>
+        <v>98211</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7375,41 +7084,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650438</v>
+        <v>650415</v>
       </c>
       <c r="R57" t="n">
-        <v>6674347</v>
+        <v>6674216</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7441,7 +7154,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7451,7 +7164,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7478,10 +7191,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384391</v>
+        <v>122384434</v>
       </c>
       <c r="B58" t="n">
-        <v>57395</v>
+        <v>74692</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7490,39 +7203,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6426</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7530,10 +7229,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650364</v>
+        <v>650407</v>
       </c>
       <c r="R58" t="n">
-        <v>6674383</v>
+        <v>6674363</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7565,7 +7264,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7575,7 +7274,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7602,10 +7301,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384400</v>
+        <v>122384454</v>
       </c>
       <c r="B59" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7618,46 +7317,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650362</v>
+        <v>650440</v>
       </c>
       <c r="R59" t="n">
-        <v>6674082</v>
+        <v>6674369</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7689,7 +7374,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7699,7 +7384,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7726,10 +7411,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384436</v>
+        <v>122384483</v>
       </c>
       <c r="B60" t="n">
-        <v>80608</v>
+        <v>100477</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7738,41 +7423,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650363</v>
+        <v>650238</v>
       </c>
       <c r="R60" t="n">
-        <v>6674334</v>
+        <v>6674076</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7804,7 +7485,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7814,7 +7495,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7841,10 +7522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384465</v>
+        <v>122384394</v>
       </c>
       <c r="B61" t="n">
-        <v>91092</v>
+        <v>57395</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7857,37 +7538,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650436</v>
+        <v>650394</v>
       </c>
       <c r="R61" t="n">
-        <v>6674342</v>
+        <v>6674272</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7604,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7614,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,7 +7641,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399639</v>
+        <v>122399641</v>
       </c>
       <c r="B62" t="n">
         <v>57395</v>
@@ -7973,11 +7658,6 @@
       </c>
       <c r="E62" t="n">
         <v>100049</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7998,7 +7678,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8008,10 +7688,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>650031</v>
+        <v>650092</v>
       </c>
       <c r="R62" t="n">
-        <v>6674158</v>
+        <v>6674138</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8043,7 +7723,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8053,7 +7733,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8080,10 +7760,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399637</v>
+        <v>122399650</v>
       </c>
       <c r="B63" t="n">
-        <v>57395</v>
+        <v>90778</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8092,39 +7772,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8132,10 +7798,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649994</v>
+        <v>650386</v>
       </c>
       <c r="R63" t="n">
-        <v>6674118</v>
+        <v>6673912</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8167,7 +7833,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8177,7 +7843,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8204,10 +7870,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399672</v>
+        <v>122399642</v>
       </c>
       <c r="B64" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8216,31 +7882,34 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8248,10 +7917,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650329</v>
+        <v>650411</v>
       </c>
       <c r="R64" t="n">
-        <v>6673994</v>
+        <v>6674002</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8283,7 +7952,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8293,7 +7962,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8320,10 +7989,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399658</v>
+        <v>122399649</v>
       </c>
       <c r="B65" t="n">
-        <v>94820</v>
+        <v>80609</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8332,31 +8001,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>210</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
+        <v>1049</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8364,10 +8027,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649956</v>
+        <v>650383</v>
       </c>
       <c r="R65" t="n">
-        <v>6674194</v>
+        <v>6673928</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8399,7 +8062,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8409,7 +8072,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8436,10 +8099,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399650</v>
+        <v>122399658</v>
       </c>
       <c r="B66" t="n">
-        <v>90773</v>
+        <v>94829</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8452,26 +8115,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>210</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8479,10 +8138,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>650386</v>
+        <v>649956</v>
       </c>
       <c r="R66" t="n">
-        <v>6673912</v>
+        <v>6674194</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8514,7 +8173,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8524,7 +8183,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8551,10 +8210,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399649</v>
+        <v>122399637</v>
       </c>
       <c r="B67" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8567,26 +8226,30 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8594,10 +8257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>650383</v>
+        <v>649994</v>
       </c>
       <c r="R67" t="n">
-        <v>6673928</v>
+        <v>6674118</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8629,7 +8292,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8639,7 +8302,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8666,10 +8329,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399640</v>
+        <v>122399672</v>
       </c>
       <c r="B68" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8678,39 +8341,26 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8718,10 +8368,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650059</v>
+        <v>650329</v>
       </c>
       <c r="R68" t="n">
-        <v>6674144</v>
+        <v>6673994</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8753,7 +8403,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8763,7 +8413,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8790,10 +8440,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399642</v>
+        <v>122399656</v>
       </c>
       <c r="B69" t="n">
-        <v>57395</v>
+        <v>94733</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8802,39 +8452,26 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>2818</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8842,10 +8479,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650411</v>
+        <v>649935</v>
       </c>
       <c r="R69" t="n">
-        <v>6674002</v>
+        <v>6674249</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8877,7 +8514,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8887,7 +8524,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8914,10 +8551,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399675</v>
+        <v>122399639</v>
       </c>
       <c r="B70" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8926,31 +8563,34 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8958,10 +8598,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>650473</v>
+        <v>650031</v>
       </c>
       <c r="R70" t="n">
-        <v>6673911</v>
+        <v>6674158</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8993,7 +8633,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9003,7 +8643,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9030,10 +8670,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399656</v>
+        <v>122399640</v>
       </c>
       <c r="B71" t="n">
-        <v>94724</v>
+        <v>57395</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9042,31 +8682,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2818</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Stubbspretmossa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9074,10 +8717,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>649935</v>
+        <v>650059</v>
       </c>
       <c r="R71" t="n">
-        <v>6674249</v>
+        <v>6674144</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9109,7 +8752,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9119,7 +8762,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9146,10 +8789,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399673</v>
+        <v>122399675</v>
       </c>
       <c r="B72" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9163,11 +8806,6 @@
       </c>
       <c r="E72" t="n">
         <v>222498</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -9190,10 +8828,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>650321</v>
+        <v>650473</v>
       </c>
       <c r="R72" t="n">
-        <v>6673981</v>
+        <v>6673911</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9225,7 +8863,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9235,7 +8873,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9262,10 +8900,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399641</v>
+        <v>122399673</v>
       </c>
       <c r="B73" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9274,39 +8912,26 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9314,10 +8939,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650092</v>
+        <v>650321</v>
       </c>
       <c r="R73" t="n">
-        <v>6674138</v>
+        <v>6673981</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +8974,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +8984,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9389,7 +9014,7 @@
         <v>122399657</v>
       </c>
       <c r="B74" t="n">
-        <v>94820</v>
+        <v>94829</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9403,11 +9028,6 @@
       </c>
       <c r="E74" t="n">
         <v>210</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9505,7 +9125,7 @@
         <v>122399660</v>
       </c>
       <c r="B75" t="n">
-        <v>94820</v>
+        <v>94829</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9519,11 +9139,6 @@
       </c>
       <c r="E75" t="n">
         <v>210</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9618,14 +9233,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399645</v>
+        <v>122399655</v>
       </c>
       <c r="B76" t="n">
-        <v>57749</v>
+        <v>94733</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9634,27 +9249,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>2818</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9662,10 +9272,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>649902</v>
+        <v>649962</v>
       </c>
       <c r="R76" t="n">
-        <v>6674271</v>
+        <v>6674201</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9697,7 +9307,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9707,7 +9317,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9730,22 +9340,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122399655</v>
+        <v>122399645</v>
       </c>
       <c r="B77" t="n">
-        <v>94724</v>
+        <v>57749</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9754,27 +9360,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2818</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Stubbspretmossa</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9782,10 +9383,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>649962</v>
+        <v>649902</v>
       </c>
       <c r="R77" t="n">
-        <v>6674201</v>
+        <v>6674271</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9817,7 +9418,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9827,7 +9428,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9850,7 +9451,11 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr"/>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -3468,10 +3468,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384484</v>
+        <v>122384391</v>
       </c>
       <c r="B26" t="n">
-        <v>100477</v>
+        <v>57395</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,37 +3480,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650407</v>
+        <v>650364</v>
       </c>
       <c r="R26" t="n">
-        <v>6674068</v>
+        <v>6674383</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3542,7 +3550,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3552,7 +3560,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3579,7 +3587,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384391</v>
+        <v>122384406</v>
       </c>
       <c r="B27" t="n">
         <v>57395</v>
@@ -3616,20 +3624,20 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650364</v>
+        <v>650115</v>
       </c>
       <c r="R27" t="n">
-        <v>6674383</v>
+        <v>6674245</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3661,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3671,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3698,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384406</v>
+        <v>122384484</v>
       </c>
       <c r="B28" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3710,34 +3718,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650115</v>
+        <v>650407</v>
       </c>
       <c r="R28" t="n">
-        <v>6674245</v>
+        <v>6674068</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384464</v>
+        <v>122384402</v>
       </c>
       <c r="B30" t="n">
-        <v>90813</v>
+        <v>57395</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3959,21 +3959,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3981,10 +3990,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650429</v>
+        <v>650297</v>
       </c>
       <c r="R30" t="n">
-        <v>6674188</v>
+        <v>6674040</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4016,7 +4025,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4026,7 +4035,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4282,10 +4291,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384402</v>
+        <v>122384464</v>
       </c>
       <c r="B33" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4298,30 +4307,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650297</v>
+        <v>650429</v>
       </c>
       <c r="R33" t="n">
-        <v>6674040</v>
+        <v>6674188</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5209,10 +5209,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384476</v>
+        <v>122384411</v>
       </c>
       <c r="B41" t="n">
-        <v>98211</v>
+        <v>57395</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5221,34 +5221,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650396</v>
+        <v>650415</v>
       </c>
       <c r="R41" t="n">
-        <v>6674252</v>
+        <v>6674083</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5328,10 +5328,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384411</v>
+        <v>122384476</v>
       </c>
       <c r="B42" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5340,34 +5340,34 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650415</v>
+        <v>650396</v>
       </c>
       <c r="R42" t="n">
-        <v>6674083</v>
+        <v>6674252</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5447,10 +5447,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384436</v>
+        <v>122384473</v>
       </c>
       <c r="B43" t="n">
-        <v>80609</v>
+        <v>98211</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5459,25 +5459,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5485,10 +5494,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650363</v>
+        <v>650400</v>
       </c>
       <c r="R43" t="n">
-        <v>6674334</v>
+        <v>6674415</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5520,7 +5529,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5530,7 +5539,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5557,7 +5566,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384473</v>
+        <v>122384472</v>
       </c>
       <c r="B44" t="n">
         <v>98211</v>
@@ -5587,7 +5596,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5604,10 +5613,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650400</v>
+        <v>650415</v>
       </c>
       <c r="R44" t="n">
-        <v>6674415</v>
+        <v>6674360</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5639,7 +5648,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5649,7 +5658,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5676,10 +5685,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384472</v>
+        <v>122384436</v>
       </c>
       <c r="B45" t="n">
-        <v>98211</v>
+        <v>80609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5688,34 +5697,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650415</v>
+        <v>650363</v>
       </c>
       <c r="R45" t="n">
-        <v>6674360</v>
+        <v>6674334</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7760,10 +7760,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399650</v>
+        <v>122399642</v>
       </c>
       <c r="B63" t="n">
-        <v>90778</v>
+        <v>57395</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7772,25 +7772,34 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7798,10 +7807,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>650386</v>
+        <v>650411</v>
       </c>
       <c r="R63" t="n">
-        <v>6673912</v>
+        <v>6674002</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7833,7 +7842,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7843,7 +7852,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7870,10 +7879,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399642</v>
+        <v>122399650</v>
       </c>
       <c r="B64" t="n">
-        <v>57395</v>
+        <v>90778</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7882,34 +7891,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650411</v>
+        <v>650386</v>
       </c>
       <c r="R64" t="n">
-        <v>6674002</v>
+        <v>6673912</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -3132,10 +3132,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384485</v>
+        <v>122384470</v>
       </c>
       <c r="B23" t="n">
-        <v>100477</v>
+        <v>91251</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3144,37 +3144,36 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650432</v>
+        <v>650388</v>
       </c>
       <c r="R23" t="n">
-        <v>6674247</v>
+        <v>6674308</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3206,7 +3205,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3216,7 +3215,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,10 +3242,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384470</v>
+        <v>122384439</v>
       </c>
       <c r="B24" t="n">
-        <v>91251</v>
+        <v>80609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3255,20 +3254,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>1049</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3277,14 +3276,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650388</v>
+        <v>650238</v>
       </c>
       <c r="R24" t="n">
-        <v>6674308</v>
+        <v>6674074</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3316,7 +3315,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3326,7 +3325,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3353,10 +3357,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384439</v>
+        <v>122384485</v>
       </c>
       <c r="B25" t="n">
-        <v>80609</v>
+        <v>100477</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3365,25 +3369,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3391,10 +3396,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650238</v>
+        <v>650432</v>
       </c>
       <c r="R25" t="n">
-        <v>6674074</v>
+        <v>6674247</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3426,7 +3431,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3436,12 +3441,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384402</v>
+        <v>122384464</v>
       </c>
       <c r="B30" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3959,30 +3959,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3990,10 +3981,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650297</v>
+        <v>650429</v>
       </c>
       <c r="R30" t="n">
-        <v>6674040</v>
+        <v>6674188</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4025,7 +4016,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4035,7 +4026,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4291,10 +4282,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384464</v>
+        <v>122384402</v>
       </c>
       <c r="B33" t="n">
-        <v>90813</v>
+        <v>57395</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4307,21 +4298,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650429</v>
+        <v>650297</v>
       </c>
       <c r="R33" t="n">
-        <v>6674188</v>
+        <v>6674040</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399671</v>
+        <v>122399626</v>
       </c>
       <c r="B2" t="n">
-        <v>100477</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,22 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100526</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650309</v>
+        <v>650382</v>
       </c>
       <c r="R2" t="n">
-        <v>6673789</v>
+        <v>6673643</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -749,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399626</v>
+        <v>122399652</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +808,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650382</v>
+        <v>650328</v>
       </c>
       <c r="R3" t="n">
-        <v>6673643</v>
+        <v>6673703</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399644</v>
+        <v>122399667</v>
       </c>
       <c r="B4" t="n">
-        <v>57749</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,30 +923,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650328</v>
+        <v>650365</v>
       </c>
       <c r="R4" t="n">
-        <v>6673703</v>
+        <v>6673701</v>
       </c>
       <c r="S4" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399633</v>
+        <v>122399668</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1047,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650328</v>
+        <v>650331</v>
       </c>
       <c r="R5" t="n">
-        <v>6673703</v>
+        <v>6673701</v>
       </c>
       <c r="S5" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1132,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1164,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399628</v>
+        <v>122399627</v>
       </c>
       <c r="B6" t="n">
         <v>5193</v>
@@ -1153,6 +1181,11 @@
       </c>
       <c r="E6" t="n">
         <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1180,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650379</v>
+        <v>650420</v>
       </c>
       <c r="R6" t="n">
-        <v>6673641</v>
+        <v>6673617</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1215,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1258,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399666</v>
+        <v>122399630</v>
       </c>
       <c r="B7" t="n">
-        <v>98211</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,30 +1297,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1295,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650369</v>
+        <v>650217</v>
       </c>
       <c r="R7" t="n">
-        <v>6673665</v>
+        <v>6673709</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1330,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399652</v>
+        <v>122399633</v>
       </c>
       <c r="B8" t="n">
-        <v>90813</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1422,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1445,7 +1493,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1503,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,7 +1530,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399630</v>
+        <v>122399628</v>
       </c>
       <c r="B9" t="n">
         <v>5193</v>
@@ -1499,6 +1547,11 @@
       </c>
       <c r="E9" t="n">
         <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1516,7 +1569,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1526,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650217</v>
+        <v>650379</v>
       </c>
       <c r="R9" t="n">
-        <v>6673709</v>
+        <v>6673641</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1561,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1654,7 @@
         <v>122399632</v>
       </c>
       <c r="B10" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,6 +1668,11 @@
       </c>
       <c r="E10" t="n">
         <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1717,10 +1775,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399627</v>
+        <v>122399670</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>98224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,31 +1787,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1761,10 +1827,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650420</v>
+        <v>650313</v>
       </c>
       <c r="R11" t="n">
-        <v>6673617</v>
+        <v>6673680</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1796,7 +1862,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1872,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399667</v>
+        <v>122399666</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,6 +1917,11 @@
       <c r="E12" t="n">
         <v>220787</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1863,14 +1934,10 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1880,10 +1947,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650365</v>
+        <v>650369</v>
       </c>
       <c r="R12" t="n">
-        <v>6673701</v>
+        <v>6673665</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1915,7 +1982,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1992,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +2024,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399668</v>
+        <v>122399671</v>
       </c>
       <c r="B13" t="n">
-        <v>98211</v>
+        <v>100490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,32 +2036,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1999,10 +2068,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650331</v>
+        <v>650309</v>
       </c>
       <c r="R13" t="n">
-        <v>6673701</v>
+        <v>6673789</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2034,7 +2103,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,12 +2113,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,10 +2140,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399670</v>
+        <v>122399644</v>
       </c>
       <c r="B14" t="n">
-        <v>98211</v>
+        <v>57753</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,34 +2152,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2123,13 +2188,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650313</v>
+        <v>650328</v>
       </c>
       <c r="R14" t="n">
-        <v>6673680</v>
+        <v>6673703</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2158,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,7 +2263,7 @@
         <v>122399676</v>
       </c>
       <c r="B15" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,6 +2277,11 @@
       </c>
       <c r="E15" t="n">
         <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2314,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384432</v>
+        <v>122384479</v>
       </c>
       <c r="B16" t="n">
-        <v>74692</v>
+        <v>100490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,21 +2400,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2352,10 +2428,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650422</v>
+        <v>650415</v>
       </c>
       <c r="R16" t="n">
-        <v>6674376</v>
+        <v>6674370</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2387,7 +2463,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2397,7 +2473,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,19 +2482,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2435,10 +2500,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384403</v>
+        <v>122384477</v>
       </c>
       <c r="B17" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,34 +2512,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2482,10 +2552,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650237</v>
+        <v>650415</v>
       </c>
       <c r="R17" t="n">
-        <v>6674049</v>
+        <v>6674216</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2517,7 +2587,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2527,7 +2597,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,10 +2624,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384442</v>
+        <v>122384432</v>
       </c>
       <c r="B18" t="n">
-        <v>90778</v>
+        <v>74696</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2570,16 +2640,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6426</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2588,14 +2663,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650393</v>
+        <v>650422</v>
       </c>
       <c r="R18" t="n">
-        <v>6674157</v>
+        <v>6674376</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2627,7 +2702,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2637,7 +2712,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,8 +2721,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2664,10 +2755,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384366</v>
+        <v>122384404</v>
       </c>
       <c r="B19" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2681,6 +2772,11 @@
       </c>
       <c r="E19" t="n">
         <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2707,14 +2803,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650419</v>
+        <v>650195</v>
       </c>
       <c r="R19" t="n">
-        <v>6674371</v>
+        <v>6674100</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2746,7 +2842,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2756,7 +2852,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2783,10 +2879,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384487</v>
+        <v>122384400</v>
       </c>
       <c r="B20" t="n">
-        <v>105317</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2795,37 +2891,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650442</v>
+        <v>650362</v>
       </c>
       <c r="R20" t="n">
-        <v>6674345</v>
+        <v>6674082</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2857,7 +2966,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2867,7 +2976,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2894,10 +3003,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384395</v>
+        <v>122384436</v>
       </c>
       <c r="B21" t="n">
-        <v>57395</v>
+        <v>80613</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2910,41 +3019,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650395</v>
+        <v>650363</v>
       </c>
       <c r="R21" t="n">
-        <v>6674254</v>
+        <v>6674334</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2976,7 +3081,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2986,7 +3091,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,10 +3118,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384369</v>
+        <v>122384468</v>
       </c>
       <c r="B22" t="n">
-        <v>57395</v>
+        <v>91264</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3025,34 +3130,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1209</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3060,10 +3161,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650395</v>
+        <v>650436</v>
       </c>
       <c r="R22" t="n">
-        <v>6674349</v>
+        <v>6674345</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3095,7 +3196,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3105,7 +3206,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3114,8 +3220,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3132,10 +3254,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384470</v>
+        <v>122384391</v>
       </c>
       <c r="B23" t="n">
-        <v>91251</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3144,25 +3266,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3170,10 +3306,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650388</v>
+        <v>650364</v>
       </c>
       <c r="R23" t="n">
-        <v>6674308</v>
+        <v>6674383</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3205,7 +3341,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3215,7 +3351,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,10 +3378,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384439</v>
+        <v>122384466</v>
       </c>
       <c r="B24" t="n">
-        <v>80609</v>
+        <v>91220</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3254,20 +3390,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>4217</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3276,14 +3417,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650238</v>
+        <v>650393</v>
       </c>
       <c r="R24" t="n">
-        <v>6674074</v>
+        <v>6674366</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3315,7 +3456,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3325,12 +3466,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3339,8 +3475,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3357,10 +3509,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384485</v>
+        <v>122384476</v>
       </c>
       <c r="B25" t="n">
-        <v>100477</v>
+        <v>98224</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3369,24 +3521,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3396,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650432</v>
+        <v>650396</v>
       </c>
       <c r="R25" t="n">
-        <v>6674247</v>
+        <v>6674252</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3431,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3441,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3468,10 +3633,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384391</v>
+        <v>122384472</v>
       </c>
       <c r="B26" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,34 +3645,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3515,10 +3685,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650364</v>
+        <v>650415</v>
       </c>
       <c r="R26" t="n">
-        <v>6674383</v>
+        <v>6674360</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3550,7 +3720,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3560,7 +3730,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3587,10 +3757,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384406</v>
+        <v>122384484</v>
       </c>
       <c r="B27" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3599,34 +3769,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3634,10 +3801,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650115</v>
+        <v>650407</v>
       </c>
       <c r="R27" t="n">
-        <v>6674245</v>
+        <v>6674068</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3669,7 +3836,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3846,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,10 +3873,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384484</v>
+        <v>122384481</v>
       </c>
       <c r="B28" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,6 +3890,11 @@
       </c>
       <c r="E28" t="n">
         <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3745,10 +3917,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650407</v>
+        <v>650230</v>
       </c>
       <c r="R28" t="n">
-        <v>6674068</v>
+        <v>6674064</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3780,7 +3952,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3790,7 +3962,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3817,10 +3989,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384468</v>
+        <v>122384395</v>
       </c>
       <c r="B29" t="n">
-        <v>91251</v>
+        <v>57399</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3829,36 +4001,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650436</v>
+        <v>650395</v>
       </c>
       <c r="R29" t="n">
-        <v>6674345</v>
+        <v>6674254</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3890,7 +4076,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3900,12 +4086,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3914,19 +4095,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3943,10 +4113,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384464</v>
+        <v>122384417</v>
       </c>
       <c r="B30" t="n">
-        <v>90813</v>
+        <v>57536</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3959,35 +4129,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650429</v>
+        <v>650385</v>
       </c>
       <c r="R30" t="n">
-        <v>6674188</v>
+        <v>6674365</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4016,7 +4200,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4026,7 +4210,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4053,10 +4242,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384373</v>
+        <v>122384412</v>
       </c>
       <c r="B31" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4070,6 +4259,11 @@
       </c>
       <c r="E31" t="n">
         <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4090,20 +4284,20 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650373</v>
+        <v>650399</v>
       </c>
       <c r="R31" t="n">
-        <v>6674389</v>
+        <v>6674181</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4135,7 +4329,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4145,7 +4339,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4172,10 +4366,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384437</v>
+        <v>122384366</v>
       </c>
       <c r="B32" t="n">
-        <v>80609</v>
+        <v>57399</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4188,32 +4382,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1049</v>
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650387</v>
+        <v>650419</v>
       </c>
       <c r="R32" t="n">
-        <v>6674259</v>
+        <v>6674371</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4245,7 +4453,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4255,7 +4463,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4282,10 +4490,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384402</v>
+        <v>122384439</v>
       </c>
       <c r="B33" t="n">
-        <v>57395</v>
+        <v>80613</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4298,30 +4506,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4329,10 +4533,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650297</v>
+        <v>650238</v>
       </c>
       <c r="R33" t="n">
-        <v>6674040</v>
+        <v>6674074</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4364,7 +4568,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4374,7 +4578,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4401,10 +4610,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384410</v>
+        <v>122384440</v>
       </c>
       <c r="B34" t="n">
-        <v>57395</v>
+        <v>80613</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4417,30 +4626,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4448,10 +4653,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650147</v>
+        <v>650077</v>
       </c>
       <c r="R34" t="n">
-        <v>6674088</v>
+        <v>6674268</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4483,7 +4688,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4493,7 +4698,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4520,10 +4725,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384400</v>
+        <v>122384464</v>
       </c>
       <c r="B35" t="n">
-        <v>57395</v>
+        <v>90826</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4536,30 +4741,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4567,10 +4768,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650362</v>
+        <v>650429</v>
       </c>
       <c r="R35" t="n">
-        <v>6674082</v>
+        <v>6674188</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4602,7 +4803,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4612,7 +4813,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4639,10 +4840,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384388</v>
+        <v>122384403</v>
       </c>
       <c r="B36" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4656,6 +4857,11 @@
       </c>
       <c r="E36" t="n">
         <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4676,20 +4882,20 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650400</v>
+        <v>650237</v>
       </c>
       <c r="R36" t="n">
-        <v>6674425</v>
+        <v>6674049</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4721,7 +4927,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4731,7 +4937,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4758,10 +4964,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384404</v>
+        <v>122384487</v>
       </c>
       <c r="B37" t="n">
-        <v>57395</v>
+        <v>105330</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4770,45 +4976,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650195</v>
+        <v>650442</v>
       </c>
       <c r="R37" t="n">
-        <v>6674100</v>
+        <v>6674345</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4840,7 +5043,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4850,7 +5053,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4877,10 +5080,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384480</v>
+        <v>122384410</v>
       </c>
       <c r="B38" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4889,26 +5092,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4916,10 +5132,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650316</v>
+        <v>650147</v>
       </c>
       <c r="R38" t="n">
-        <v>6674034</v>
+        <v>6674088</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4951,7 +5167,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4961,7 +5177,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4988,10 +5204,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384479</v>
+        <v>122384402</v>
       </c>
       <c r="B39" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5000,37 +5216,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650415</v>
+        <v>650297</v>
       </c>
       <c r="R39" t="n">
-        <v>6674370</v>
+        <v>6674040</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5062,7 +5291,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5072,7 +5301,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5099,10 +5328,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384462</v>
+        <v>122384442</v>
       </c>
       <c r="B40" t="n">
-        <v>90813</v>
+        <v>90791</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5111,20 +5340,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5133,14 +5367,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650428</v>
+        <v>650393</v>
       </c>
       <c r="R40" t="n">
-        <v>6674388</v>
+        <v>6674157</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5172,7 +5406,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5182,7 +5416,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5209,10 +5443,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384411</v>
+        <v>122384470</v>
       </c>
       <c r="B41" t="n">
-        <v>57395</v>
+        <v>91264</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5221,45 +5455,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1209</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650415</v>
+        <v>650388</v>
       </c>
       <c r="R41" t="n">
-        <v>6674083</v>
+        <v>6674308</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5291,7 +5521,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5301,7 +5531,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5328,10 +5558,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384476</v>
+        <v>122384483</v>
       </c>
       <c r="B42" t="n">
-        <v>98211</v>
+        <v>100490</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5340,32 +5570,29 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5375,10 +5602,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650396</v>
+        <v>650238</v>
       </c>
       <c r="R42" t="n">
-        <v>6674252</v>
+        <v>6674076</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5410,7 +5637,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5420,7 +5647,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5447,10 +5674,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384473</v>
+        <v>122384485</v>
       </c>
       <c r="B43" t="n">
-        <v>98211</v>
+        <v>100490</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5459,45 +5686,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650400</v>
+        <v>650432</v>
       </c>
       <c r="R43" t="n">
-        <v>6674415</v>
+        <v>6674247</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5529,7 +5753,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5539,7 +5763,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5566,10 +5790,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384472</v>
+        <v>122384373</v>
       </c>
       <c r="B44" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5578,34 +5802,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5613,10 +5842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650415</v>
+        <v>650373</v>
       </c>
       <c r="R44" t="n">
-        <v>6674360</v>
+        <v>6674389</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5648,7 +5877,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5658,7 +5887,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5685,10 +5914,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384436</v>
+        <v>122384369</v>
       </c>
       <c r="B45" t="n">
-        <v>80609</v>
+        <v>57399</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5701,21 +5930,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5723,10 +5966,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650363</v>
+        <v>650395</v>
       </c>
       <c r="R45" t="n">
-        <v>6674334</v>
+        <v>6674349</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5758,7 +6001,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5768,7 +6011,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5795,10 +6038,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384481</v>
+        <v>122384407</v>
       </c>
       <c r="B46" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5807,26 +6050,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5834,10 +6090,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650230</v>
+        <v>650101</v>
       </c>
       <c r="R46" t="n">
-        <v>6674064</v>
+        <v>6674120</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5869,7 +6125,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5879,7 +6135,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5906,10 +6162,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384443</v>
+        <v>122384480</v>
       </c>
       <c r="B47" t="n">
-        <v>90813</v>
+        <v>100490</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5918,36 +6174,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650438</v>
+        <v>650316</v>
       </c>
       <c r="R47" t="n">
-        <v>6674347</v>
+        <v>6674034</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5979,7 +6241,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5989,7 +6251,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6016,10 +6278,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384371</v>
+        <v>122384411</v>
       </c>
       <c r="B48" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6033,6 +6295,11 @@
       </c>
       <c r="E48" t="n">
         <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6053,7 +6320,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6063,13 +6330,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650400</v>
+        <v>650415</v>
       </c>
       <c r="R48" t="n">
-        <v>6674206</v>
+        <v>6674083</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6098,7 +6365,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6108,7 +6375,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6135,10 +6402,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384407</v>
+        <v>122384454</v>
       </c>
       <c r="B49" t="n">
-        <v>57395</v>
+        <v>90826</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6151,41 +6418,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1202</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650101</v>
+        <v>650440</v>
       </c>
       <c r="R49" t="n">
-        <v>6674120</v>
+        <v>6674369</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6217,7 +6480,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6227,7 +6490,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6254,10 +6517,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384465</v>
+        <v>122384443</v>
       </c>
       <c r="B50" t="n">
-        <v>91097</v>
+        <v>90826</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6270,16 +6533,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6292,10 +6560,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650436</v>
+        <v>650438</v>
       </c>
       <c r="R50" t="n">
-        <v>6674342</v>
+        <v>6674347</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6327,7 +6595,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6337,7 +6605,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6364,10 +6632,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384440</v>
+        <v>122384406</v>
       </c>
       <c r="B51" t="n">
-        <v>80609</v>
+        <v>57399</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6380,21 +6648,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1049</v>
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6402,10 +6684,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650077</v>
+        <v>650115</v>
       </c>
       <c r="R51" t="n">
-        <v>6674268</v>
+        <v>6674245</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6437,7 +6719,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6447,7 +6729,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6474,10 +6756,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384417</v>
+        <v>122384371</v>
       </c>
       <c r="B52" t="n">
-        <v>57532</v>
+        <v>57399</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6490,16 +6772,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6511,20 +6798,20 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650385</v>
+        <v>650400</v>
       </c>
       <c r="R52" t="n">
-        <v>6674365</v>
+        <v>6674206</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6556,7 +6843,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6566,12 +6853,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6598,10 +6880,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384438</v>
+        <v>122384388</v>
       </c>
       <c r="B53" t="n">
-        <v>80609</v>
+        <v>57399</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6614,32 +6896,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650353</v>
+        <v>650400</v>
       </c>
       <c r="R53" t="n">
-        <v>6674235</v>
+        <v>6674425</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6671,7 +6967,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6681,12 +6977,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6713,10 +7004,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384466</v>
+        <v>122384434</v>
       </c>
       <c r="B54" t="n">
-        <v>91207</v>
+        <v>74696</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6729,16 +7020,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4217</v>
+        <v>6426</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6751,10 +7047,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650393</v>
+        <v>650407</v>
       </c>
       <c r="R54" t="n">
-        <v>6674366</v>
+        <v>6674363</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6786,7 +7082,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6796,7 +7092,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6805,19 +7101,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6834,10 +7119,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384412</v>
+        <v>122384437</v>
       </c>
       <c r="B55" t="n">
-        <v>57395</v>
+        <v>80613</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6850,30 +7135,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6881,10 +7162,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650399</v>
+        <v>650387</v>
       </c>
       <c r="R55" t="n">
-        <v>6674181</v>
+        <v>6674259</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6916,7 +7197,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6926,7 +7207,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6953,10 +7234,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384397</v>
+        <v>122384438</v>
       </c>
       <c r="B56" t="n">
-        <v>57395</v>
+        <v>80613</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6969,30 +7250,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7000,10 +7277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650406</v>
+        <v>650353</v>
       </c>
       <c r="R56" t="n">
-        <v>6674220</v>
+        <v>6674235</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7035,7 +7312,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7045,7 +7322,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7072,10 +7354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384477</v>
+        <v>122384473</v>
       </c>
       <c r="B57" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7090,6 +7372,11 @@
       <c r="E57" t="n">
         <v>220787</v>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -7102,7 +7389,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7115,14 +7402,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650415</v>
+        <v>650400</v>
       </c>
       <c r="R57" t="n">
-        <v>6674216</v>
+        <v>6674415</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7154,7 +7441,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7164,7 +7451,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7191,10 +7478,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384434</v>
+        <v>122384465</v>
       </c>
       <c r="B58" t="n">
-        <v>74692</v>
+        <v>91110</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7203,20 +7490,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>658</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7229,10 +7521,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650407</v>
+        <v>650436</v>
       </c>
       <c r="R58" t="n">
-        <v>6674363</v>
+        <v>6674342</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7264,7 +7556,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7274,7 +7566,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7301,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384454</v>
+        <v>122384394</v>
       </c>
       <c r="B59" t="n">
-        <v>90813</v>
+        <v>57399</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7317,32 +7609,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650440</v>
+        <v>650394</v>
       </c>
       <c r="R59" t="n">
-        <v>6674369</v>
+        <v>6674272</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7374,7 +7680,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7384,7 +7690,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7411,10 +7717,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384483</v>
+        <v>122384397</v>
       </c>
       <c r="B60" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7423,26 +7729,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7450,10 +7769,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650238</v>
+        <v>650406</v>
       </c>
       <c r="R60" t="n">
-        <v>6674076</v>
+        <v>6674220</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7485,7 +7804,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7495,7 +7814,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7522,10 +7841,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384394</v>
+        <v>122384462</v>
       </c>
       <c r="B61" t="n">
-        <v>57395</v>
+        <v>90826</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7538,41 +7857,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>1202</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650394</v>
+        <v>650428</v>
       </c>
       <c r="R61" t="n">
-        <v>6674272</v>
+        <v>6674388</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7604,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7614,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7644,7 +7959,7 @@
         <v>122399641</v>
       </c>
       <c r="B62" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7658,6 +7973,11 @@
       </c>
       <c r="E62" t="n">
         <v>100049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7760,10 +8080,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399642</v>
+        <v>122399673</v>
       </c>
       <c r="B63" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7772,34 +8092,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7807,10 +8124,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>650411</v>
+        <v>650321</v>
       </c>
       <c r="R63" t="n">
-        <v>6674002</v>
+        <v>6673981</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7842,7 +8159,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7852,7 +8169,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7879,10 +8196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399650</v>
+        <v>122399642</v>
       </c>
       <c r="B64" t="n">
-        <v>90778</v>
+        <v>57399</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7891,25 +8208,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>100049</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7917,10 +8248,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650386</v>
+        <v>650411</v>
       </c>
       <c r="R64" t="n">
-        <v>6673912</v>
+        <v>6674002</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7952,7 +8283,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,7 +8293,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7989,10 +8320,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399649</v>
+        <v>122399640</v>
       </c>
       <c r="B65" t="n">
-        <v>80609</v>
+        <v>57399</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8005,21 +8336,35 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1049</v>
+        <v>100049</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8027,10 +8372,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650383</v>
+        <v>650059</v>
       </c>
       <c r="R65" t="n">
-        <v>6673928</v>
+        <v>6674144</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8062,7 +8407,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8072,7 +8417,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8099,10 +8444,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399658</v>
+        <v>122399672</v>
       </c>
       <c r="B66" t="n">
-        <v>94829</v>
+        <v>100490</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8115,16 +8460,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>210</v>
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8138,10 +8488,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>649956</v>
+        <v>650329</v>
       </c>
       <c r="R66" t="n">
-        <v>6674194</v>
+        <v>6673994</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8173,7 +8523,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8183,7 +8533,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8210,10 +8560,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399637</v>
+        <v>122399658</v>
       </c>
       <c r="B67" t="n">
-        <v>57395</v>
+        <v>94842</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8222,34 +8572,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>210</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8257,10 +8604,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649994</v>
+        <v>649956</v>
       </c>
       <c r="R67" t="n">
-        <v>6674118</v>
+        <v>6674194</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8292,7 +8639,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8302,7 +8649,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8329,10 +8676,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399672</v>
+        <v>122399650</v>
       </c>
       <c r="B68" t="n">
-        <v>100477</v>
+        <v>90791</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8345,22 +8692,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>5447</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8368,10 +8719,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650329</v>
+        <v>650386</v>
       </c>
       <c r="R68" t="n">
-        <v>6673994</v>
+        <v>6673912</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8403,7 +8754,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8413,7 +8764,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8440,10 +8791,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399656</v>
+        <v>122399649</v>
       </c>
       <c r="B69" t="n">
-        <v>94733</v>
+        <v>80613</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8452,26 +8803,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2818</v>
+        <v>1049</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8479,10 +8834,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>649935</v>
+        <v>650383</v>
       </c>
       <c r="R69" t="n">
-        <v>6674249</v>
+        <v>6673928</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8514,7 +8869,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8524,7 +8879,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8551,10 +8906,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399639</v>
+        <v>122399656</v>
       </c>
       <c r="B70" t="n">
-        <v>57395</v>
+        <v>94746</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8563,34 +8918,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>2818</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8598,10 +8950,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>650031</v>
+        <v>649935</v>
       </c>
       <c r="R70" t="n">
-        <v>6674158</v>
+        <v>6674249</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8633,7 +8985,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8643,7 +8995,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8670,10 +9022,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399640</v>
+        <v>122399637</v>
       </c>
       <c r="B71" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8687,6 +9039,11 @@
       </c>
       <c r="E71" t="n">
         <v>100049</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8717,10 +9074,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650059</v>
+        <v>649994</v>
       </c>
       <c r="R71" t="n">
-        <v>6674144</v>
+        <v>6674118</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -8752,7 +9109,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8762,7 +9119,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8792,7 +9149,7 @@
         <v>122399675</v>
       </c>
       <c r="B72" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8806,6 +9163,11 @@
       </c>
       <c r="E72" t="n">
         <v>222498</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8900,10 +9262,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399673</v>
+        <v>122399639</v>
       </c>
       <c r="B73" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8912,26 +9274,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8939,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650321</v>
+        <v>650031</v>
       </c>
       <c r="R73" t="n">
-        <v>6673981</v>
+        <v>6674158</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -8974,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8984,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9011,10 +9386,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399657</v>
+        <v>122399660</v>
       </c>
       <c r="B74" t="n">
-        <v>94829</v>
+        <v>94842</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9028,6 +9403,11 @@
       </c>
       <c r="E74" t="n">
         <v>210</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9050,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649950</v>
+        <v>649992</v>
       </c>
       <c r="R74" t="n">
-        <v>6674175</v>
+        <v>6674192</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9085,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9095,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9122,10 +9502,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399660</v>
+        <v>122399655</v>
       </c>
       <c r="B75" t="n">
-        <v>94829</v>
+        <v>94746</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9138,16 +9518,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>210</v>
+        <v>2818</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9161,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649992</v>
+        <v>649962</v>
       </c>
       <c r="R75" t="n">
-        <v>6674192</v>
+        <v>6674201</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9196,7 +9581,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9206,7 +9591,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9233,10 +9618,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399655</v>
+        <v>122399657</v>
       </c>
       <c r="B76" t="n">
-        <v>94733</v>
+        <v>94842</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9249,16 +9634,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2818</v>
+        <v>210</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9272,10 +9662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>649962</v>
+        <v>649950</v>
       </c>
       <c r="R76" t="n">
-        <v>6674201</v>
+        <v>6674175</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9307,7 +9697,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9317,7 +9707,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9347,7 +9737,7 @@
         <v>122399645</v>
       </c>
       <c r="B77" t="n">
-        <v>57749</v>
+        <v>57753</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9361,6 +9751,11 @@
       </c>
       <c r="E77" t="n">
         <v>103015</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399626</v>
+        <v>122399627</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650382</v>
+        <v>650420</v>
       </c>
       <c r="R2" t="n">
-        <v>6673643</v>
+        <v>6673617</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399652</v>
+        <v>122399666</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,30 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650328</v>
+        <v>650369</v>
       </c>
       <c r="R3" t="n">
-        <v>6673703</v>
+        <v>6673665</v>
       </c>
       <c r="S3" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +889,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399667</v>
+        <v>122399632</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,39 +933,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650365</v>
+        <v>650256</v>
       </c>
       <c r="R4" t="n">
-        <v>6673701</v>
+        <v>6673700</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -998,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399668</v>
+        <v>122399670</v>
       </c>
       <c r="B5" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,7 +1080,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650331</v>
+        <v>650313</v>
       </c>
       <c r="R5" t="n">
-        <v>6673701</v>
+        <v>6673680</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1122,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,12 +1142,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399627</v>
+        <v>122399633</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,20 +1181,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1197,13 +1202,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1213,13 +1221,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650420</v>
+        <v>650328</v>
       </c>
       <c r="R6" t="n">
-        <v>6673617</v>
+        <v>6673703</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1266,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399630</v>
+        <v>122399644</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>57753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,16 +1309,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1318,15 +1326,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1334,13 +1341,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650217</v>
+        <v>650328</v>
       </c>
       <c r="R7" t="n">
-        <v>6673709</v>
+        <v>6673703</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,10 +1413,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399633</v>
+        <v>122399668</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,39 +1425,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1458,13 +1465,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650328</v>
+        <v>650331</v>
       </c>
       <c r="R8" t="n">
-        <v>6673703</v>
+        <v>6673701</v>
       </c>
       <c r="S8" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1493,7 +1500,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,7 +1510,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,7 +1542,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399628</v>
+        <v>122399630</v>
       </c>
       <c r="B9" t="n">
         <v>5193</v>
@@ -1569,7 +1581,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1579,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650379</v>
+        <v>650217</v>
       </c>
       <c r="R9" t="n">
-        <v>6673641</v>
+        <v>6673709</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1614,7 +1626,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1636,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399632</v>
+        <v>122399667</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,39 +1675,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1703,10 +1715,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650256</v>
+        <v>650365</v>
       </c>
       <c r="R10" t="n">
-        <v>6673700</v>
+        <v>6673701</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1738,7 +1750,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1748,7 +1760,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,10 +1787,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399670</v>
+        <v>122399671</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>100503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1787,37 +1799,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1827,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650313</v>
+        <v>650309</v>
       </c>
       <c r="R11" t="n">
-        <v>6673680</v>
+        <v>6673789</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1862,7 +1866,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1872,7 +1876,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399666</v>
+        <v>122399626</v>
       </c>
       <c r="B12" t="n">
-        <v>98224</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,35 +1915,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1947,10 +1952,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650369</v>
+        <v>650382</v>
       </c>
       <c r="R12" t="n">
-        <v>6673665</v>
+        <v>6673643</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1992,12 +1997,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399671</v>
+        <v>122399652</v>
       </c>
       <c r="B13" t="n">
-        <v>100490</v>
+        <v>90839</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,31 +2036,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2068,13 +2067,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650309</v>
+        <v>650328</v>
       </c>
       <c r="R13" t="n">
-        <v>6673789</v>
+        <v>6673703</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2103,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2113,7 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399644</v>
+        <v>122399628</v>
       </c>
       <c r="B14" t="n">
-        <v>57753</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2156,16 +2155,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2173,14 +2172,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650328</v>
+        <v>650379</v>
       </c>
       <c r="R14" t="n">
-        <v>6673703</v>
+        <v>6673641</v>
       </c>
       <c r="S14" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,7 +2263,7 @@
         <v>122399676</v>
       </c>
       <c r="B15" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384479</v>
+        <v>122384432</v>
       </c>
       <c r="B16" t="n">
-        <v>100490</v>
+        <v>74696</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2400,27 +2400,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2428,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650415</v>
+        <v>650422</v>
       </c>
       <c r="R16" t="n">
-        <v>6674370</v>
+        <v>6674376</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2463,7 +2462,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2473,7 +2472,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2482,8 +2481,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2500,10 +2515,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384477</v>
+        <v>122384373</v>
       </c>
       <c r="B17" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2512,50 +2527,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650415</v>
+        <v>650373</v>
       </c>
       <c r="R17" t="n">
-        <v>6674216</v>
+        <v>6674389</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2587,7 +2602,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2597,7 +2612,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2624,10 +2639,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384432</v>
+        <v>122384366</v>
       </c>
       <c r="B18" t="n">
-        <v>74696</v>
+        <v>57399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2636,30 +2651,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2667,10 +2691,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650422</v>
+        <v>650419</v>
       </c>
       <c r="R18" t="n">
-        <v>6674376</v>
+        <v>6674371</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2702,7 +2726,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2712,7 +2736,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,24 +2745,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2755,7 +2763,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384404</v>
+        <v>122384388</v>
       </c>
       <c r="B19" t="n">
         <v>57399</v>
@@ -2797,20 +2805,20 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650195</v>
+        <v>650400</v>
       </c>
       <c r="R19" t="n">
-        <v>6674100</v>
+        <v>6674425</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2842,7 +2850,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2852,7 +2860,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2879,10 +2887,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384400</v>
+        <v>122384473</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2891,50 +2899,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650362</v>
+        <v>650400</v>
       </c>
       <c r="R20" t="n">
-        <v>6674082</v>
+        <v>6674415</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2966,7 +2974,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2976,7 +2984,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3003,10 +3011,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384436</v>
+        <v>122384397</v>
       </c>
       <c r="B21" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3019,37 +3027,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650363</v>
+        <v>650406</v>
       </c>
       <c r="R21" t="n">
-        <v>6674334</v>
+        <v>6674220</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3081,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3091,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3118,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384468</v>
+        <v>122384483</v>
       </c>
       <c r="B22" t="n">
-        <v>91264</v>
+        <v>100503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,41 +3147,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650436</v>
+        <v>650238</v>
       </c>
       <c r="R22" t="n">
-        <v>6674345</v>
+        <v>6674076</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3196,7 +3214,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3206,12 +3224,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3220,24 +3233,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3254,10 +3251,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384391</v>
+        <v>122384439</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3270,46 +3267,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650364</v>
+        <v>650238</v>
       </c>
       <c r="R23" t="n">
-        <v>6674383</v>
+        <v>6674074</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3341,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3351,7 +3339,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3378,10 +3371,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384466</v>
+        <v>122384402</v>
       </c>
       <c r="B24" t="n">
-        <v>91220</v>
+        <v>57399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3390,41 +3383,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650393</v>
+        <v>650297</v>
       </c>
       <c r="R24" t="n">
-        <v>6674366</v>
+        <v>6674040</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3456,7 +3458,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3466,7 +3468,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3475,24 +3477,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3509,10 +3495,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384476</v>
+        <v>122384472</v>
       </c>
       <c r="B25" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3544,7 +3530,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3557,14 +3543,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650396</v>
+        <v>650415</v>
       </c>
       <c r="R25" t="n">
-        <v>6674252</v>
+        <v>6674360</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3596,7 +3582,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3592,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3633,10 +3619,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384472</v>
+        <v>122384487</v>
       </c>
       <c r="B26" t="n">
-        <v>98224</v>
+        <v>105343</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3645,37 +3631,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3685,10 +3663,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650415</v>
+        <v>650442</v>
       </c>
       <c r="R26" t="n">
-        <v>6674360</v>
+        <v>6674345</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3720,7 +3698,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3730,7 +3708,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3757,10 +3735,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384484</v>
+        <v>122384404</v>
       </c>
       <c r="B27" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3769,31 +3747,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3801,10 +3787,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650407</v>
+        <v>650195</v>
       </c>
       <c r="R27" t="n">
-        <v>6674068</v>
+        <v>6674100</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3836,7 +3822,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3846,7 +3832,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3873,10 +3859,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384481</v>
+        <v>122384391</v>
       </c>
       <c r="B28" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3885,42 +3871,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650230</v>
+        <v>650364</v>
       </c>
       <c r="R28" t="n">
-        <v>6674064</v>
+        <v>6674383</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3952,7 +3946,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3962,7 +3956,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3989,10 +3983,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384395</v>
+        <v>122384442</v>
       </c>
       <c r="B29" t="n">
-        <v>57399</v>
+        <v>90804</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4001,39 +3995,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4041,10 +4026,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650395</v>
+        <v>650393</v>
       </c>
       <c r="R29" t="n">
-        <v>6674254</v>
+        <v>6674157</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4076,7 +4061,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4086,7 +4071,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,10 +4098,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384417</v>
+        <v>122384395</v>
       </c>
       <c r="B30" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4129,21 +4114,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4155,23 +4140,23 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650385</v>
+        <v>650395</v>
       </c>
       <c r="R30" t="n">
-        <v>6674365</v>
+        <v>6674254</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4200,7 +4185,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4210,12 +4195,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4242,7 +4222,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384412</v>
+        <v>122384410</v>
       </c>
       <c r="B31" t="n">
         <v>57399</v>
@@ -4294,10 +4274,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650399</v>
+        <v>650147</v>
       </c>
       <c r="R31" t="n">
-        <v>6674181</v>
+        <v>6674088</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4329,7 +4309,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4339,7 +4319,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4366,10 +4346,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384366</v>
+        <v>122384443</v>
       </c>
       <c r="B32" t="n">
-        <v>57399</v>
+        <v>90839</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4382,35 +4362,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4418,10 +4389,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650419</v>
+        <v>650438</v>
       </c>
       <c r="R32" t="n">
-        <v>6674371</v>
+        <v>6674347</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4453,7 +4424,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4463,7 +4434,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4490,10 +4461,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384439</v>
+        <v>122384369</v>
       </c>
       <c r="B33" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4506,37 +4477,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650238</v>
+        <v>650395</v>
       </c>
       <c r="R33" t="n">
-        <v>6674074</v>
+        <v>6674349</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4568,7 +4548,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4578,12 +4558,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4610,10 +4585,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384440</v>
+        <v>122384371</v>
       </c>
       <c r="B34" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4626,26 +4601,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4653,13 +4637,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650077</v>
+        <v>650400</v>
       </c>
       <c r="R34" t="n">
-        <v>6674268</v>
+        <v>6674206</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4688,7 +4672,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4698,7 +4682,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4725,10 +4709,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384464</v>
+        <v>122384412</v>
       </c>
       <c r="B35" t="n">
-        <v>90826</v>
+        <v>57399</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4741,26 +4725,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4768,10 +4761,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650429</v>
+        <v>650399</v>
       </c>
       <c r="R35" t="n">
-        <v>6674188</v>
+        <v>6674181</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4803,7 +4796,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4813,7 +4806,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4840,10 +4833,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384403</v>
+        <v>122384470</v>
       </c>
       <c r="B36" t="n">
-        <v>57399</v>
+        <v>91277</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4852,50 +4845,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650237</v>
+        <v>650388</v>
       </c>
       <c r="R36" t="n">
-        <v>6674049</v>
+        <v>6674308</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4927,7 +4911,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4937,7 +4921,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4964,10 +4948,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384487</v>
+        <v>122384438</v>
       </c>
       <c r="B37" t="n">
-        <v>105330</v>
+        <v>80613</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4976,42 +4960,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>1049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650442</v>
+        <v>650353</v>
       </c>
       <c r="R37" t="n">
-        <v>6674345</v>
+        <v>6674235</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5043,7 +5026,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5053,7 +5036,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5080,7 +5068,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384410</v>
+        <v>122384411</v>
       </c>
       <c r="B38" t="n">
         <v>57399</v>
@@ -5132,10 +5120,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650147</v>
+        <v>650415</v>
       </c>
       <c r="R38" t="n">
-        <v>6674088</v>
+        <v>6674083</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5167,7 +5155,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5177,7 +5165,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5204,10 +5192,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384402</v>
+        <v>122384484</v>
       </c>
       <c r="B39" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5216,39 +5204,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5256,10 +5236,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650297</v>
+        <v>650407</v>
       </c>
       <c r="R39" t="n">
-        <v>6674040</v>
+        <v>6674068</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5291,7 +5271,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5301,7 +5281,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5328,10 +5308,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384442</v>
+        <v>122384394</v>
       </c>
       <c r="B40" t="n">
-        <v>90791</v>
+        <v>57399</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5340,30 +5320,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5371,10 +5360,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650393</v>
+        <v>650394</v>
       </c>
       <c r="R40" t="n">
-        <v>6674157</v>
+        <v>6674272</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5406,7 +5395,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5416,7 +5405,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5443,10 +5432,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384470</v>
+        <v>122384403</v>
       </c>
       <c r="B41" t="n">
-        <v>91264</v>
+        <v>57399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5455,41 +5444,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650388</v>
+        <v>650237</v>
       </c>
       <c r="R41" t="n">
-        <v>6674308</v>
+        <v>6674049</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5521,7 +5519,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5531,7 +5529,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5558,10 +5556,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384483</v>
+        <v>122384462</v>
       </c>
       <c r="B42" t="n">
-        <v>100490</v>
+        <v>90839</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5570,42 +5568,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650238</v>
+        <v>650428</v>
       </c>
       <c r="R42" t="n">
-        <v>6674076</v>
+        <v>6674388</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5637,7 +5634,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5647,7 +5644,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5674,10 +5671,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384485</v>
+        <v>122384466</v>
       </c>
       <c r="B43" t="n">
-        <v>100490</v>
+        <v>91233</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5690,38 +5687,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>4217</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650432</v>
+        <v>650393</v>
       </c>
       <c r="R43" t="n">
-        <v>6674247</v>
+        <v>6674366</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5753,7 +5749,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5763,7 +5759,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5772,8 +5768,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5790,10 +5802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384373</v>
+        <v>122384454</v>
       </c>
       <c r="B44" t="n">
-        <v>57399</v>
+        <v>90839</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5806,35 +5818,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5842,10 +5845,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650373</v>
+        <v>650440</v>
       </c>
       <c r="R44" t="n">
-        <v>6674389</v>
+        <v>6674369</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5877,7 +5880,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5887,7 +5890,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5914,10 +5917,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384369</v>
+        <v>122384465</v>
       </c>
       <c r="B45" t="n">
-        <v>57399</v>
+        <v>91123</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5930,35 +5933,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5966,10 +5960,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650395</v>
+        <v>650436</v>
       </c>
       <c r="R45" t="n">
-        <v>6674349</v>
+        <v>6674342</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -6001,7 +5995,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6011,7 +6005,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6038,10 +6032,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384407</v>
+        <v>122384437</v>
       </c>
       <c r="B46" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6054,35 +6048,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6090,10 +6075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650101</v>
+        <v>650387</v>
       </c>
       <c r="R46" t="n">
-        <v>6674120</v>
+        <v>6674259</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6125,7 +6110,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6135,7 +6120,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6162,10 +6147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384480</v>
+        <v>122384481</v>
       </c>
       <c r="B47" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6206,10 +6191,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650316</v>
+        <v>650230</v>
       </c>
       <c r="R47" t="n">
-        <v>6674034</v>
+        <v>6674064</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6241,7 +6226,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6251,7 +6236,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6278,10 +6263,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384411</v>
+        <v>122384479</v>
       </c>
       <c r="B48" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6290,50 +6275,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
         <v>650415</v>
       </c>
       <c r="R48" t="n">
-        <v>6674083</v>
+        <v>6674370</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6365,7 +6342,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6375,7 +6352,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6402,10 +6379,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384454</v>
+        <v>122384434</v>
       </c>
       <c r="B49" t="n">
-        <v>90826</v>
+        <v>74696</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6414,25 +6391,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6445,10 +6422,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650440</v>
+        <v>650407</v>
       </c>
       <c r="R49" t="n">
-        <v>6674369</v>
+        <v>6674363</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6480,7 +6457,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6490,7 +6467,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6517,10 +6494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384443</v>
+        <v>122384464</v>
       </c>
       <c r="B50" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6556,14 +6533,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650438</v>
+        <v>650429</v>
       </c>
       <c r="R50" t="n">
-        <v>6674347</v>
+        <v>6674188</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6595,7 +6572,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6605,7 +6582,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6632,10 +6609,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384406</v>
+        <v>122384468</v>
       </c>
       <c r="B51" t="n">
-        <v>57399</v>
+        <v>91277</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6644,50 +6621,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650115</v>
+        <v>650436</v>
       </c>
       <c r="R51" t="n">
-        <v>6674245</v>
+        <v>6674345</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6719,7 +6687,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6729,7 +6697,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6738,8 +6711,24 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6756,7 +6745,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384371</v>
+        <v>122384400</v>
       </c>
       <c r="B52" t="n">
         <v>57399</v>
@@ -6798,7 +6787,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6808,13 +6797,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650400</v>
+        <v>650362</v>
       </c>
       <c r="R52" t="n">
-        <v>6674206</v>
+        <v>6674082</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6843,7 +6832,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6853,7 +6842,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6880,10 +6869,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384388</v>
+        <v>122384440</v>
       </c>
       <c r="B53" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6896,46 +6885,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650400</v>
+        <v>650077</v>
       </c>
       <c r="R53" t="n">
-        <v>6674425</v>
+        <v>6674268</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6967,7 +6947,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6977,7 +6957,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7004,10 +6984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384434</v>
+        <v>122384406</v>
       </c>
       <c r="B54" t="n">
-        <v>74696</v>
+        <v>57399</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7016,41 +6996,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650407</v>
+        <v>650115</v>
       </c>
       <c r="R54" t="n">
-        <v>6674363</v>
+        <v>6674245</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7082,7 +7071,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7092,7 +7081,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7119,10 +7108,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384437</v>
+        <v>122384417</v>
       </c>
       <c r="B55" t="n">
-        <v>80613</v>
+        <v>57536</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7135,40 +7124,49 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650387</v>
+        <v>650385</v>
       </c>
       <c r="R55" t="n">
-        <v>6674259</v>
+        <v>6674365</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7197,7 +7195,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7207,7 +7205,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7234,10 +7237,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384438</v>
+        <v>122384485</v>
       </c>
       <c r="B56" t="n">
-        <v>80613</v>
+        <v>100503</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7246,30 +7249,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7277,10 +7281,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650353</v>
+        <v>650432</v>
       </c>
       <c r="R56" t="n">
-        <v>6674235</v>
+        <v>6674247</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7312,7 +7316,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7322,12 +7326,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7354,10 +7353,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384473</v>
+        <v>122384480</v>
       </c>
       <c r="B57" t="n">
-        <v>98224</v>
+        <v>100503</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7366,50 +7365,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650400</v>
+        <v>650316</v>
       </c>
       <c r="R57" t="n">
-        <v>6674415</v>
+        <v>6674034</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7441,7 +7432,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7451,7 +7442,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7478,10 +7469,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384465</v>
+        <v>122384477</v>
       </c>
       <c r="B58" t="n">
-        <v>91110</v>
+        <v>98237</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7490,41 +7481,50 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650436</v>
+        <v>650415</v>
       </c>
       <c r="R58" t="n">
-        <v>6674342</v>
+        <v>6674216</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7593,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384394</v>
+        <v>122384476</v>
       </c>
       <c r="B59" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7605,39 +7605,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650394</v>
+        <v>650396</v>
       </c>
       <c r="R59" t="n">
-        <v>6674272</v>
+        <v>6674252</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7717,10 +7717,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384397</v>
+        <v>122384436</v>
       </c>
       <c r="B60" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7733,46 +7733,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650406</v>
+        <v>650363</v>
       </c>
       <c r="R60" t="n">
-        <v>6674220</v>
+        <v>6674334</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7804,7 +7795,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7814,7 +7805,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7841,10 +7832,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384462</v>
+        <v>122384407</v>
       </c>
       <c r="B61" t="n">
-        <v>90826</v>
+        <v>57399</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7857,37 +7848,46 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650428</v>
+        <v>650101</v>
       </c>
       <c r="R61" t="n">
-        <v>6674388</v>
+        <v>6674120</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,7 +7956,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399641</v>
+        <v>122399637</v>
       </c>
       <c r="B62" t="n">
         <v>57399</v>
@@ -7998,7 +7998,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8008,10 +8008,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>650092</v>
+        <v>649994</v>
       </c>
       <c r="R62" t="n">
-        <v>6674138</v>
+        <v>6674118</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8080,10 +8080,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399673</v>
+        <v>122399640</v>
       </c>
       <c r="B63" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8092,31 +8092,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8124,10 +8132,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>650321</v>
+        <v>650059</v>
       </c>
       <c r="R63" t="n">
-        <v>6673981</v>
+        <v>6674144</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8159,7 +8167,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8169,7 +8177,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8196,7 +8204,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399642</v>
+        <v>122399641</v>
       </c>
       <c r="B64" t="n">
         <v>57399</v>
@@ -8248,10 +8256,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650411</v>
+        <v>650092</v>
       </c>
       <c r="R64" t="n">
-        <v>6674002</v>
+        <v>6674138</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8283,7 +8291,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8293,7 +8301,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8320,10 +8328,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399640</v>
+        <v>122399650</v>
       </c>
       <c r="B65" t="n">
-        <v>57399</v>
+        <v>90804</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8332,39 +8340,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8372,10 +8371,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650059</v>
+        <v>650386</v>
       </c>
       <c r="R65" t="n">
-        <v>6674144</v>
+        <v>6673912</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8407,7 +8406,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8417,7 +8416,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8444,10 +8443,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399672</v>
+        <v>122399642</v>
       </c>
       <c r="B66" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8456,31 +8455,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8488,10 +8495,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>650329</v>
+        <v>650411</v>
       </c>
       <c r="R66" t="n">
-        <v>6673994</v>
+        <v>6674002</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8523,7 +8530,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8533,7 +8540,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8560,10 +8567,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399658</v>
+        <v>122399675</v>
       </c>
       <c r="B67" t="n">
-        <v>94842</v>
+        <v>100503</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8576,21 +8583,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8604,10 +8611,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649956</v>
+        <v>650473</v>
       </c>
       <c r="R67" t="n">
-        <v>6674194</v>
+        <v>6673911</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8639,7 +8646,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8649,7 +8656,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8676,10 +8683,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399650</v>
+        <v>122399673</v>
       </c>
       <c r="B68" t="n">
-        <v>90791</v>
+        <v>100503</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8692,26 +8699,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8719,10 +8727,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650386</v>
+        <v>650321</v>
       </c>
       <c r="R68" t="n">
-        <v>6673912</v>
+        <v>6673981</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8754,7 +8762,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8764,7 +8772,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8791,10 +8799,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399649</v>
+        <v>122399672</v>
       </c>
       <c r="B69" t="n">
-        <v>80613</v>
+        <v>100503</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8803,30 +8811,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8834,10 +8843,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650383</v>
+        <v>650329</v>
       </c>
       <c r="R69" t="n">
-        <v>6673928</v>
+        <v>6673994</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8869,7 +8878,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8879,7 +8888,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8906,10 +8915,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399656</v>
+        <v>122399639</v>
       </c>
       <c r="B70" t="n">
-        <v>94746</v>
+        <v>57399</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8918,31 +8927,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8950,10 +8967,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>649935</v>
+        <v>650031</v>
       </c>
       <c r="R70" t="n">
-        <v>6674249</v>
+        <v>6674158</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8985,7 +9002,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8995,7 +9012,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9022,10 +9039,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399637</v>
+        <v>122399656</v>
       </c>
       <c r="B71" t="n">
-        <v>57399</v>
+        <v>94759</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9034,39 +9051,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9074,10 +9083,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>649994</v>
+        <v>649935</v>
       </c>
       <c r="R71" t="n">
-        <v>6674118</v>
+        <v>6674249</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9109,7 +9118,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9119,7 +9128,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9146,10 +9155,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399675</v>
+        <v>122399658</v>
       </c>
       <c r="B72" t="n">
-        <v>100490</v>
+        <v>94855</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9162,21 +9171,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9190,10 +9199,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>650473</v>
+        <v>649956</v>
       </c>
       <c r="R72" t="n">
-        <v>6673911</v>
+        <v>6674194</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9225,7 +9234,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9235,7 +9244,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9262,10 +9271,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399639</v>
+        <v>122399649</v>
       </c>
       <c r="B73" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9278,35 +9287,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650031</v>
+        <v>650383</v>
       </c>
       <c r="R73" t="n">
-        <v>6674158</v>
+        <v>6673928</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9386,10 +9386,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399660</v>
+        <v>122399655</v>
       </c>
       <c r="B74" t="n">
-        <v>94842</v>
+        <v>94759</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9402,21 +9402,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649992</v>
+        <v>649962</v>
       </c>
       <c r="R74" t="n">
-        <v>6674192</v>
+        <v>6674201</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,14 +9502,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399655</v>
+        <v>122399645</v>
       </c>
       <c r="B75" t="n">
-        <v>94746</v>
+        <v>57753</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9518,27 +9518,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2818</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649962</v>
+        <v>649902</v>
       </c>
       <c r="R75" t="n">
-        <v>6674201</v>
+        <v>6674271</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9614,14 +9614,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399657</v>
+        <v>122399660</v>
       </c>
       <c r="B76" t="n">
-        <v>94842</v>
+        <v>94855</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9662,10 +9666,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>649950</v>
+        <v>649992</v>
       </c>
       <c r="R76" t="n">
-        <v>6674175</v>
+        <v>6674192</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9697,7 +9701,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9707,7 +9711,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9734,14 +9738,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122399645</v>
+        <v>122399657</v>
       </c>
       <c r="B77" t="n">
-        <v>57753</v>
+        <v>94855</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9750,27 +9754,27 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>210</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9778,10 +9782,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>649902</v>
+        <v>649950</v>
       </c>
       <c r="R77" t="n">
-        <v>6674271</v>
+        <v>6674175</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9813,7 +9817,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9823,7 +9827,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9846,11 +9850,7 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -3495,10 +3495,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384472</v>
+        <v>122384487</v>
       </c>
       <c r="B25" t="n">
-        <v>98237</v>
+        <v>105343</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3507,37 +3507,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3547,10 +3539,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650415</v>
+        <v>650442</v>
       </c>
       <c r="R25" t="n">
-        <v>6674360</v>
+        <v>6674345</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3582,7 +3574,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3592,7 +3584,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3619,10 +3611,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384487</v>
+        <v>122384472</v>
       </c>
       <c r="B26" t="n">
-        <v>105343</v>
+        <v>98237</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3631,29 +3623,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650442</v>
+        <v>650415</v>
       </c>
       <c r="R26" t="n">
-        <v>6674345</v>
+        <v>6674360</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4098,7 +4098,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384395</v>
+        <v>122384410</v>
       </c>
       <c r="B30" t="n">
         <v>57399</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650395</v>
+        <v>650147</v>
       </c>
       <c r="R30" t="n">
-        <v>6674254</v>
+        <v>6674088</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4222,7 +4222,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384410</v>
+        <v>122384395</v>
       </c>
       <c r="B31" t="n">
         <v>57399</v>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650147</v>
+        <v>650395</v>
       </c>
       <c r="R31" t="n">
-        <v>6674088</v>
+        <v>6674254</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5308,7 +5308,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384394</v>
+        <v>122384403</v>
       </c>
       <c r="B40" t="n">
         <v>57399</v>
@@ -5350,7 +5350,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650394</v>
+        <v>650237</v>
       </c>
       <c r="R40" t="n">
-        <v>6674272</v>
+        <v>6674049</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5432,7 +5432,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384403</v>
+        <v>122384394</v>
       </c>
       <c r="B41" t="n">
         <v>57399</v>
@@ -5474,7 +5474,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650237</v>
+        <v>650394</v>
       </c>
       <c r="R41" t="n">
-        <v>6674049</v>
+        <v>6674272</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -8915,10 +8915,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399639</v>
+        <v>122399656</v>
       </c>
       <c r="B70" t="n">
-        <v>57399</v>
+        <v>94759</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8927,39 +8927,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8967,10 +8959,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>650031</v>
+        <v>649935</v>
       </c>
       <c r="R70" t="n">
-        <v>6674158</v>
+        <v>6674249</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -9002,7 +8994,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9012,7 +9004,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9039,10 +9031,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399656</v>
+        <v>122399639</v>
       </c>
       <c r="B71" t="n">
-        <v>94759</v>
+        <v>57399</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9051,31 +9043,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>649935</v>
+        <v>650031</v>
       </c>
       <c r="R71" t="n">
-        <v>6674249</v>
+        <v>6674158</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399627</v>
+        <v>122399668</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650420</v>
+        <v>650331</v>
       </c>
       <c r="R2" t="n">
-        <v>6673617</v>
+        <v>6673701</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399666</v>
+        <v>122399652</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>90839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +816,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650369</v>
+        <v>650328</v>
       </c>
       <c r="R3" t="n">
-        <v>6673665</v>
+        <v>6673703</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,12 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1045,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399670</v>
+        <v>122399627</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,39 +1055,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1097,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650313</v>
+        <v>650420</v>
       </c>
       <c r="R5" t="n">
-        <v>6673680</v>
+        <v>6673617</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1132,7 +1127,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,7 +1137,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399633</v>
+        <v>122399667</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,39 +1176,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,13 +1216,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650328</v>
+        <v>650365</v>
       </c>
       <c r="R6" t="n">
-        <v>6673703</v>
+        <v>6673701</v>
       </c>
       <c r="S6" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,7 +1251,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,7 +1261,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399644</v>
+        <v>122399671</v>
       </c>
       <c r="B7" t="n">
-        <v>57753</v>
+        <v>100503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,31 +1304,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1341,13 +1332,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650328</v>
+        <v>650309</v>
       </c>
       <c r="R7" t="n">
-        <v>6673703</v>
+        <v>6673789</v>
       </c>
       <c r="S7" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399668</v>
+        <v>122399633</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,39 +1416,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1465,13 +1456,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650331</v>
+        <v>650328</v>
       </c>
       <c r="R8" t="n">
-        <v>6673701</v>
+        <v>6673703</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1510,12 +1501,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399630</v>
+        <v>122399644</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>57753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1558,16 +1544,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1575,15 +1561,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1591,13 +1576,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650217</v>
+        <v>650328</v>
       </c>
       <c r="R9" t="n">
-        <v>6673709</v>
+        <v>6673703</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1626,7 +1611,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1636,7 +1621,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399667</v>
+        <v>122399630</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,39 +1660,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1715,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650365</v>
+        <v>650217</v>
       </c>
       <c r="R10" t="n">
-        <v>6673701</v>
+        <v>6673709</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1750,7 +1732,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1760,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1787,10 +1769,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399671</v>
+        <v>122399626</v>
       </c>
       <c r="B11" t="n">
-        <v>100503</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,27 +1785,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1831,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650309</v>
+        <v>650382</v>
       </c>
       <c r="R11" t="n">
-        <v>6673789</v>
+        <v>6673643</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1866,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1876,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1903,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399626</v>
+        <v>122399628</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1919,21 +1906,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1952,10 +1939,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650382</v>
+        <v>650379</v>
       </c>
       <c r="R12" t="n">
-        <v>6673643</v>
+        <v>6673641</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1987,7 +1974,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1997,7 +1984,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,10 +2011,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399652</v>
+        <v>122399670</v>
       </c>
       <c r="B13" t="n">
-        <v>90839</v>
+        <v>98237</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,30 +2023,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2067,13 +2063,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650328</v>
+        <v>650313</v>
       </c>
       <c r="R13" t="n">
-        <v>6673703</v>
+        <v>6673680</v>
       </c>
       <c r="S13" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2102,7 +2098,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2108,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,10 +2135,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399628</v>
+        <v>122399666</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>98237</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,36 +2147,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650379</v>
+        <v>650369</v>
       </c>
       <c r="R14" t="n">
-        <v>6673641</v>
+        <v>6673665</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2223,7 +2218,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2228,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384432</v>
+        <v>122384373</v>
       </c>
       <c r="B16" t="n">
-        <v>74696</v>
+        <v>57399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,30 +2396,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2427,10 +2436,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650422</v>
+        <v>650373</v>
       </c>
       <c r="R16" t="n">
-        <v>6674376</v>
+        <v>6674389</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2462,7 +2471,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,7 +2481,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,24 +2490,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2515,10 +2508,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384373</v>
+        <v>122384468</v>
       </c>
       <c r="B17" t="n">
-        <v>57399</v>
+        <v>91277</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2527,39 +2520,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2567,10 +2551,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650373</v>
+        <v>650436</v>
       </c>
       <c r="R17" t="n">
-        <v>6674389</v>
+        <v>6674345</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2602,7 +2586,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2612,7 +2596,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2621,8 +2610,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2639,7 +2644,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384366</v>
+        <v>122384394</v>
       </c>
       <c r="B18" t="n">
         <v>57399</v>
@@ -2681,20 +2686,20 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650419</v>
+        <v>650394</v>
       </c>
       <c r="R18" t="n">
-        <v>6674371</v>
+        <v>6674272</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2726,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2736,7 +2741,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2763,10 +2768,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384388</v>
+        <v>122384472</v>
       </c>
       <c r="B19" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2775,39 +2780,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2815,10 +2820,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650400</v>
+        <v>650415</v>
       </c>
       <c r="R19" t="n">
-        <v>6674425</v>
+        <v>6674360</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2850,7 +2855,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2860,7 +2865,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2887,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384473</v>
+        <v>122384436</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>80613</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2899,39 +2904,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2939,10 +2935,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650400</v>
+        <v>650363</v>
       </c>
       <c r="R20" t="n">
-        <v>6674415</v>
+        <v>6674334</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2974,7 +2970,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2984,7 +2980,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3011,7 +3007,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384397</v>
+        <v>122384388</v>
       </c>
       <c r="B21" t="n">
         <v>57399</v>
@@ -3059,14 +3055,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650406</v>
+        <v>650400</v>
       </c>
       <c r="R21" t="n">
-        <v>6674220</v>
+        <v>6674425</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3098,7 +3094,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3104,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3135,10 +3131,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384483</v>
+        <v>122384442</v>
       </c>
       <c r="B22" t="n">
-        <v>100503</v>
+        <v>90804</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3151,27 +3147,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650238</v>
+        <v>650393</v>
       </c>
       <c r="R22" t="n">
-        <v>6674076</v>
+        <v>6674157</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3214,7 +3209,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3224,7 +3219,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,10 +3246,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384439</v>
+        <v>122384462</v>
       </c>
       <c r="B23" t="n">
-        <v>80613</v>
+        <v>90839</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,21 +3262,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3290,14 +3285,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650238</v>
+        <v>650428</v>
       </c>
       <c r="R23" t="n">
-        <v>6674074</v>
+        <v>6674388</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3329,7 +3324,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3339,12 +3334,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3371,10 +3361,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384402</v>
+        <v>122384477</v>
       </c>
       <c r="B24" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3383,39 +3373,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3423,10 +3413,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650297</v>
+        <v>650415</v>
       </c>
       <c r="R24" t="n">
-        <v>6674040</v>
+        <v>6674216</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3458,7 +3448,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3468,7 +3458,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3495,10 +3485,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384487</v>
+        <v>122384484</v>
       </c>
       <c r="B25" t="n">
-        <v>105343</v>
+        <v>100503</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3511,21 +3501,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3535,14 +3525,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650442</v>
+        <v>650407</v>
       </c>
       <c r="R25" t="n">
-        <v>6674345</v>
+        <v>6674068</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3574,7 +3564,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3584,7 +3574,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3611,10 +3601,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384472</v>
+        <v>122384432</v>
       </c>
       <c r="B26" t="n">
-        <v>98237</v>
+        <v>74696</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3623,39 +3613,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3663,10 +3644,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650415</v>
+        <v>650422</v>
       </c>
       <c r="R26" t="n">
-        <v>6674360</v>
+        <v>6674376</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3698,7 +3679,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3708,7 +3689,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3717,8 +3698,24 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3735,10 +3732,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384404</v>
+        <v>122384434</v>
       </c>
       <c r="B27" t="n">
-        <v>57399</v>
+        <v>74696</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3747,50 +3744,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650195</v>
+        <v>650407</v>
       </c>
       <c r="R27" t="n">
-        <v>6674100</v>
+        <v>6674363</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3822,7 +3810,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3832,7 +3820,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3859,7 +3847,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384391</v>
+        <v>122384400</v>
       </c>
       <c r="B28" t="n">
         <v>57399</v>
@@ -3901,20 +3889,20 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650364</v>
+        <v>650362</v>
       </c>
       <c r="R28" t="n">
-        <v>6674383</v>
+        <v>6674082</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3946,7 +3934,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3956,7 +3944,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3983,10 +3971,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384442</v>
+        <v>122384465</v>
       </c>
       <c r="B29" t="n">
-        <v>90804</v>
+        <v>91123</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3995,25 +3983,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4022,14 +4010,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650393</v>
+        <v>650436</v>
       </c>
       <c r="R29" t="n">
-        <v>6674157</v>
+        <v>6674342</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4061,7 +4049,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4071,7 +4059,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4098,7 +4086,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384410</v>
+        <v>122384407</v>
       </c>
       <c r="B30" t="n">
         <v>57399</v>
@@ -4140,7 +4128,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4150,10 +4138,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650147</v>
+        <v>650101</v>
       </c>
       <c r="R30" t="n">
-        <v>6674088</v>
+        <v>6674120</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4185,7 +4173,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4195,7 +4183,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4222,10 +4210,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384395</v>
+        <v>122384466</v>
       </c>
       <c r="B31" t="n">
-        <v>57399</v>
+        <v>91233</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4234,50 +4222,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650395</v>
+        <v>650393</v>
       </c>
       <c r="R31" t="n">
-        <v>6674254</v>
+        <v>6674366</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4309,7 +4288,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4319,7 +4298,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4328,8 +4307,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4346,10 +4341,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384443</v>
+        <v>122384476</v>
       </c>
       <c r="B32" t="n">
-        <v>90839</v>
+        <v>98237</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4358,41 +4353,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650438</v>
+        <v>650396</v>
       </c>
       <c r="R32" t="n">
-        <v>6674347</v>
+        <v>6674252</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4424,7 +4428,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4434,7 +4438,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4461,7 +4465,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384369</v>
+        <v>122384406</v>
       </c>
       <c r="B33" t="n">
         <v>57399</v>
@@ -4503,20 +4507,20 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650395</v>
+        <v>650115</v>
       </c>
       <c r="R33" t="n">
-        <v>6674349</v>
+        <v>6674245</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4548,7 +4552,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4558,7 +4562,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4585,7 +4589,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384371</v>
+        <v>122384410</v>
       </c>
       <c r="B34" t="n">
         <v>57399</v>
@@ -4627,7 +4631,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4637,13 +4641,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650400</v>
+        <v>650147</v>
       </c>
       <c r="R34" t="n">
-        <v>6674206</v>
+        <v>6674088</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4672,7 +4676,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4682,7 +4686,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4709,10 +4713,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384412</v>
+        <v>122384417</v>
       </c>
       <c r="B35" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4725,21 +4729,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4751,23 +4755,23 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650399</v>
+        <v>650385</v>
       </c>
       <c r="R35" t="n">
-        <v>6674181</v>
+        <v>6674365</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4796,7 +4800,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4806,7 +4810,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4833,10 +4842,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384470</v>
+        <v>122384473</v>
       </c>
       <c r="B36" t="n">
-        <v>91277</v>
+        <v>98237</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4849,26 +4858,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4876,10 +4894,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650388</v>
+        <v>650400</v>
       </c>
       <c r="R36" t="n">
-        <v>6674308</v>
+        <v>6674415</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4911,7 +4929,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4921,7 +4939,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4948,7 +4966,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384438</v>
+        <v>122384439</v>
       </c>
       <c r="B37" t="n">
         <v>80613</v>
@@ -4991,10 +5009,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650353</v>
+        <v>650238</v>
       </c>
       <c r="R37" t="n">
-        <v>6674235</v>
+        <v>6674074</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5026,7 +5044,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5036,12 +5054,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Riklig mängd.</t>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5068,10 +5086,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384411</v>
+        <v>122384443</v>
       </c>
       <c r="B38" t="n">
-        <v>57399</v>
+        <v>90839</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5084,46 +5102,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650415</v>
+        <v>650438</v>
       </c>
       <c r="R38" t="n">
-        <v>6674083</v>
+        <v>6674347</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5155,7 +5164,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5165,7 +5174,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5192,7 +5201,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384484</v>
+        <v>122384483</v>
       </c>
       <c r="B39" t="n">
         <v>100503</v>
@@ -5236,10 +5245,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650407</v>
+        <v>650238</v>
       </c>
       <c r="R39" t="n">
-        <v>6674068</v>
+        <v>6674076</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5271,7 +5280,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5281,7 +5290,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5308,10 +5317,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384403</v>
+        <v>122384470</v>
       </c>
       <c r="B40" t="n">
-        <v>57399</v>
+        <v>91277</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5320,50 +5329,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650237</v>
+        <v>650388</v>
       </c>
       <c r="R40" t="n">
-        <v>6674049</v>
+        <v>6674308</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5432,7 +5432,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384394</v>
+        <v>122384412</v>
       </c>
       <c r="B41" t="n">
         <v>57399</v>
@@ -5474,7 +5474,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650394</v>
+        <v>650399</v>
       </c>
       <c r="R41" t="n">
-        <v>6674272</v>
+        <v>6674181</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5556,10 +5556,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384462</v>
+        <v>122384437</v>
       </c>
       <c r="B42" t="n">
-        <v>90839</v>
+        <v>80613</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5572,21 +5572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5595,14 +5595,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650428</v>
+        <v>650387</v>
       </c>
       <c r="R42" t="n">
-        <v>6674388</v>
+        <v>6674259</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5671,10 +5671,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384466</v>
+        <v>122384454</v>
       </c>
       <c r="B43" t="n">
-        <v>91233</v>
+        <v>90839</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5683,25 +5683,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650393</v>
+        <v>650440</v>
       </c>
       <c r="R43" t="n">
-        <v>6674366</v>
+        <v>6674369</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5768,24 +5768,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5802,10 +5786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384454</v>
+        <v>122384369</v>
       </c>
       <c r="B44" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5818,26 +5802,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5845,10 +5838,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650440</v>
+        <v>650395</v>
       </c>
       <c r="R44" t="n">
-        <v>6674369</v>
+        <v>6674349</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5880,7 +5873,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5890,7 +5883,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5917,10 +5910,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384465</v>
+        <v>122384404</v>
       </c>
       <c r="B45" t="n">
-        <v>91123</v>
+        <v>57399</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5933,37 +5926,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650436</v>
+        <v>650195</v>
       </c>
       <c r="R45" t="n">
-        <v>6674342</v>
+        <v>6674100</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5995,7 +5997,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6005,7 +6007,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6032,10 +6034,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384437</v>
+        <v>122384479</v>
       </c>
       <c r="B46" t="n">
-        <v>80613</v>
+        <v>100503</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6044,41 +6046,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650387</v>
+        <v>650415</v>
       </c>
       <c r="R46" t="n">
-        <v>6674259</v>
+        <v>6674370</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6110,7 +6113,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6120,7 +6123,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6147,10 +6150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384481</v>
+        <v>122384366</v>
       </c>
       <c r="B47" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6159,42 +6162,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650230</v>
+        <v>650419</v>
       </c>
       <c r="R47" t="n">
-        <v>6674064</v>
+        <v>6674371</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6226,7 +6237,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6236,7 +6247,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6263,10 +6274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384479</v>
+        <v>122384487</v>
       </c>
       <c r="B48" t="n">
-        <v>100503</v>
+        <v>105343</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6279,21 +6290,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6307,10 +6318,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650415</v>
+        <v>650442</v>
       </c>
       <c r="R48" t="n">
-        <v>6674370</v>
+        <v>6674345</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6342,7 +6353,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6352,7 +6363,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6379,10 +6390,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384434</v>
+        <v>122384395</v>
       </c>
       <c r="B49" t="n">
-        <v>74696</v>
+        <v>57399</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6391,41 +6402,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650407</v>
+        <v>650395</v>
       </c>
       <c r="R49" t="n">
-        <v>6674363</v>
+        <v>6674254</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6457,7 +6477,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6467,7 +6487,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6494,10 +6514,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384464</v>
+        <v>122384480</v>
       </c>
       <c r="B50" t="n">
-        <v>90839</v>
+        <v>100503</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6506,30 +6526,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6537,10 +6558,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650429</v>
+        <v>650316</v>
       </c>
       <c r="R50" t="n">
-        <v>6674188</v>
+        <v>6674034</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6572,7 +6593,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6582,7 +6603,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6609,10 +6630,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384468</v>
+        <v>122384464</v>
       </c>
       <c r="B51" t="n">
-        <v>91277</v>
+        <v>90839</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6621,25 +6642,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6648,14 +6669,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650436</v>
+        <v>650429</v>
       </c>
       <c r="R51" t="n">
-        <v>6674345</v>
+        <v>6674188</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6687,7 +6708,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6697,12 +6718,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6711,24 +6727,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6745,10 +6745,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384400</v>
+        <v>122384485</v>
       </c>
       <c r="B52" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6757,39 +6757,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6797,10 +6789,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650362</v>
+        <v>650432</v>
       </c>
       <c r="R52" t="n">
-        <v>6674082</v>
+        <v>6674247</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6832,7 +6824,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6842,7 +6834,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6869,10 +6861,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384440</v>
+        <v>122384481</v>
       </c>
       <c r="B53" t="n">
-        <v>80613</v>
+        <v>100503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6881,30 +6873,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6912,10 +6905,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650077</v>
+        <v>650230</v>
       </c>
       <c r="R53" t="n">
-        <v>6674268</v>
+        <v>6674064</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6947,7 +6940,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6957,7 +6950,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6984,7 +6977,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384406</v>
+        <v>122384391</v>
       </c>
       <c r="B54" t="n">
         <v>57399</v>
@@ -7026,20 +7019,20 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650115</v>
+        <v>650364</v>
       </c>
       <c r="R54" t="n">
-        <v>6674245</v>
+        <v>6674383</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7071,7 +7064,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7081,7 +7074,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7108,10 +7101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384417</v>
+        <v>122384411</v>
       </c>
       <c r="B55" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7124,21 +7117,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7150,23 +7143,23 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650385</v>
+        <v>650415</v>
       </c>
       <c r="R55" t="n">
-        <v>6674365</v>
+        <v>6674083</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7195,7 +7188,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7205,12 +7198,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7237,10 +7225,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384485</v>
+        <v>122384402</v>
       </c>
       <c r="B56" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7249,31 +7237,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7281,10 +7277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650432</v>
+        <v>650297</v>
       </c>
       <c r="R56" t="n">
-        <v>6674247</v>
+        <v>6674040</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7316,7 +7312,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7326,7 +7322,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7353,10 +7349,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384480</v>
+        <v>122384438</v>
       </c>
       <c r="B57" t="n">
-        <v>100503</v>
+        <v>80613</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7365,31 +7361,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7397,10 +7392,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650316</v>
+        <v>650353</v>
       </c>
       <c r="R57" t="n">
-        <v>6674034</v>
+        <v>6674235</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7432,7 +7427,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7442,7 +7437,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7469,10 +7469,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384477</v>
+        <v>122384440</v>
       </c>
       <c r="B58" t="n">
-        <v>98237</v>
+        <v>80613</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7481,39 +7481,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7521,10 +7512,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650415</v>
+        <v>650077</v>
       </c>
       <c r="R58" t="n">
-        <v>6674216</v>
+        <v>6674268</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7556,7 +7547,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7566,7 +7557,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7593,10 +7584,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384476</v>
+        <v>122384397</v>
       </c>
       <c r="B59" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7605,39 +7596,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7645,10 +7636,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650396</v>
+        <v>650406</v>
       </c>
       <c r="R59" t="n">
-        <v>6674252</v>
+        <v>6674220</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7680,7 +7671,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7690,7 +7681,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7717,10 +7708,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384436</v>
+        <v>122384371</v>
       </c>
       <c r="B60" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7733,40 +7724,49 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650363</v>
+        <v>650400</v>
       </c>
       <c r="R60" t="n">
-        <v>6674334</v>
+        <v>6674206</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7832,7 +7832,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384407</v>
+        <v>122384403</v>
       </c>
       <c r="B61" t="n">
         <v>57399</v>
@@ -7874,7 +7874,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650101</v>
+        <v>650237</v>
       </c>
       <c r="R61" t="n">
-        <v>6674120</v>
+        <v>6674049</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,10 +7956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399637</v>
+        <v>122399658</v>
       </c>
       <c r="B62" t="n">
-        <v>57399</v>
+        <v>94855</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7968,39 +7968,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8008,10 +8000,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649994</v>
+        <v>649956</v>
       </c>
       <c r="R62" t="n">
-        <v>6674118</v>
+        <v>6674194</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8043,7 +8035,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8053,7 +8045,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8080,10 +8072,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399640</v>
+        <v>122399656</v>
       </c>
       <c r="B63" t="n">
-        <v>57399</v>
+        <v>94759</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8092,39 +8084,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8132,10 +8116,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>650059</v>
+        <v>649935</v>
       </c>
       <c r="R63" t="n">
-        <v>6674144</v>
+        <v>6674249</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8167,7 +8151,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8177,7 +8161,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8204,7 +8188,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399641</v>
+        <v>122399637</v>
       </c>
       <c r="B64" t="n">
         <v>57399</v>
@@ -8246,7 +8230,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8256,10 +8240,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650092</v>
+        <v>649994</v>
       </c>
       <c r="R64" t="n">
-        <v>6674138</v>
+        <v>6674118</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8291,7 +8275,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8301,7 +8285,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8328,10 +8312,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399650</v>
+        <v>122399673</v>
       </c>
       <c r="B65" t="n">
-        <v>90804</v>
+        <v>100503</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8344,26 +8328,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8371,10 +8356,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650386</v>
+        <v>650321</v>
       </c>
       <c r="R65" t="n">
-        <v>6673912</v>
+        <v>6673981</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8406,7 +8391,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8416,7 +8401,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8443,7 +8428,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399642</v>
+        <v>122399641</v>
       </c>
       <c r="B66" t="n">
         <v>57399</v>
@@ -8495,10 +8480,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>650411</v>
+        <v>650092</v>
       </c>
       <c r="R66" t="n">
-        <v>6674002</v>
+        <v>6674138</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8530,7 +8515,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8540,7 +8525,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8567,10 +8552,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399675</v>
+        <v>122399650</v>
       </c>
       <c r="B67" t="n">
-        <v>100503</v>
+        <v>90804</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8583,27 +8568,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8611,10 +8595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>650473</v>
+        <v>650386</v>
       </c>
       <c r="R67" t="n">
-        <v>6673911</v>
+        <v>6673912</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8646,7 +8630,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8656,7 +8640,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8683,10 +8667,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399673</v>
+        <v>122399649</v>
       </c>
       <c r="B68" t="n">
-        <v>100503</v>
+        <v>80613</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8695,31 +8679,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8727,10 +8710,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650321</v>
+        <v>650383</v>
       </c>
       <c r="R68" t="n">
-        <v>6673981</v>
+        <v>6673928</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8762,7 +8745,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8772,7 +8755,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8799,7 +8782,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399672</v>
+        <v>122399675</v>
       </c>
       <c r="B69" t="n">
         <v>100503</v>
@@ -8843,10 +8826,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650329</v>
+        <v>650473</v>
       </c>
       <c r="R69" t="n">
-        <v>6673994</v>
+        <v>6673911</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8878,7 +8861,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8888,7 +8871,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8915,10 +8898,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399656</v>
+        <v>122399672</v>
       </c>
       <c r="B70" t="n">
-        <v>94759</v>
+        <v>100503</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8931,21 +8914,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8959,10 +8942,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>649935</v>
+        <v>650329</v>
       </c>
       <c r="R70" t="n">
-        <v>6674249</v>
+        <v>6673994</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8994,7 +8977,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9004,7 +8987,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9031,7 +9014,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399639</v>
+        <v>122399640</v>
       </c>
       <c r="B71" t="n">
         <v>57399</v>
@@ -9083,10 +9066,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650031</v>
+        <v>650059</v>
       </c>
       <c r="R71" t="n">
-        <v>6674158</v>
+        <v>6674144</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9118,7 +9101,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9128,7 +9111,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9155,10 +9138,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399658</v>
+        <v>122399639</v>
       </c>
       <c r="B72" t="n">
-        <v>94855</v>
+        <v>57399</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9167,31 +9150,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9199,10 +9190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>649956</v>
+        <v>650031</v>
       </c>
       <c r="R72" t="n">
-        <v>6674194</v>
+        <v>6674158</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9234,7 +9225,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9244,7 +9235,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9271,10 +9262,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399649</v>
+        <v>122399642</v>
       </c>
       <c r="B73" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9287,26 +9278,35 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650383</v>
+        <v>650411</v>
       </c>
       <c r="R73" t="n">
-        <v>6673928</v>
+        <v>6674002</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9386,14 +9386,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399655</v>
+        <v>122399645</v>
       </c>
       <c r="B74" t="n">
-        <v>94759</v>
+        <v>57753</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9402,27 +9402,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2818</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649962</v>
+        <v>649902</v>
       </c>
       <c r="R74" t="n">
-        <v>6674201</v>
+        <v>6674271</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9498,18 +9498,22 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr"/>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399645</v>
+        <v>122399655</v>
       </c>
       <c r="B75" t="n">
-        <v>57753</v>
+        <v>94759</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9518,27 +9522,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>2818</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9546,10 +9550,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649902</v>
+        <v>649962</v>
       </c>
       <c r="R75" t="n">
-        <v>6674271</v>
+        <v>6674201</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9581,7 +9585,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9591,7 +9595,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9614,11 +9618,7 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -2892,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384436</v>
+        <v>122384388</v>
       </c>
       <c r="B20" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2908,26 +2908,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2935,10 +2944,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650363</v>
+        <v>650400</v>
       </c>
       <c r="R20" t="n">
-        <v>6674334</v>
+        <v>6674425</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2970,7 +2979,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2980,7 +2989,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3007,10 +3016,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384388</v>
+        <v>122384436</v>
       </c>
       <c r="B21" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3023,35 +3032,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650400</v>
+        <v>650363</v>
       </c>
       <c r="R21" t="n">
-        <v>6674425</v>
+        <v>6674334</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -5556,10 +5556,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384437</v>
+        <v>122384454</v>
       </c>
       <c r="B42" t="n">
-        <v>80613</v>
+        <v>90839</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5572,21 +5572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5595,14 +5595,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650387</v>
+        <v>650440</v>
       </c>
       <c r="R42" t="n">
-        <v>6674259</v>
+        <v>6674369</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5671,10 +5671,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384454</v>
+        <v>122384369</v>
       </c>
       <c r="B43" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5687,26 +5687,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5714,10 +5723,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650440</v>
+        <v>650395</v>
       </c>
       <c r="R43" t="n">
-        <v>6674369</v>
+        <v>6674349</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5749,7 +5758,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5759,7 +5768,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5786,7 +5795,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384369</v>
+        <v>122384404</v>
       </c>
       <c r="B44" t="n">
         <v>57399</v>
@@ -5834,14 +5843,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650395</v>
+        <v>650195</v>
       </c>
       <c r="R44" t="n">
-        <v>6674349</v>
+        <v>6674100</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5873,7 +5882,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5883,7 +5892,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5910,10 +5919,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384404</v>
+        <v>122384479</v>
       </c>
       <c r="B45" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5922,50 +5931,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650195</v>
+        <v>650415</v>
       </c>
       <c r="R45" t="n">
-        <v>6674100</v>
+        <v>6674370</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5997,7 +5998,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6007,7 +6008,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6034,10 +6035,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384479</v>
+        <v>122384437</v>
       </c>
       <c r="B46" t="n">
-        <v>100503</v>
+        <v>80613</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6046,42 +6047,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650415</v>
+        <v>650387</v>
       </c>
       <c r="R46" t="n">
-        <v>6674370</v>
+        <v>6674259</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -9138,7 +9138,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399639</v>
+        <v>122399642</v>
       </c>
       <c r="B72" t="n">
         <v>57399</v>
@@ -9180,7 +9180,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9190,10 +9190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>650031</v>
+        <v>650411</v>
       </c>
       <c r="R72" t="n">
-        <v>6674158</v>
+        <v>6674002</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9262,7 +9262,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399642</v>
+        <v>122399639</v>
       </c>
       <c r="B73" t="n">
         <v>57399</v>
@@ -9304,7 +9304,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650411</v>
+        <v>650031</v>
       </c>
       <c r="R73" t="n">
-        <v>6674002</v>
+        <v>6674158</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399668</v>
+        <v>122399628</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650331</v>
+        <v>650379</v>
       </c>
       <c r="R2" t="n">
-        <v>6673701</v>
+        <v>6673641</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,7 +799,7 @@
         <v>122399652</v>
       </c>
       <c r="B3" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399632</v>
+        <v>122399670</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +923,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650256</v>
+        <v>650313</v>
       </c>
       <c r="R4" t="n">
-        <v>6673700</v>
+        <v>6673680</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1006,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399627</v>
+        <v>122399671</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>100506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,32 +1051,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1092,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650420</v>
+        <v>650309</v>
       </c>
       <c r="R5" t="n">
-        <v>6673617</v>
+        <v>6673789</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1127,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399667</v>
+        <v>122399626</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,39 +1163,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1216,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650365</v>
+        <v>650382</v>
       </c>
       <c r="R6" t="n">
-        <v>6673701</v>
+        <v>6673643</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1251,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1261,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399671</v>
+        <v>122399633</v>
       </c>
       <c r="B7" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,31 +1284,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1332,13 +1324,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650309</v>
+        <v>650328</v>
       </c>
       <c r="R7" t="n">
-        <v>6673789</v>
+        <v>6673703</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399633</v>
+        <v>122399632</v>
       </c>
       <c r="B8" t="n">
         <v>57399</v>
@@ -1446,7 +1438,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1456,13 +1448,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650328</v>
+        <v>650256</v>
       </c>
       <c r="R8" t="n">
-        <v>6673703</v>
+        <v>6673700</v>
       </c>
       <c r="S8" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1491,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1501,7 +1493,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399644</v>
+        <v>122399666</v>
       </c>
       <c r="B9" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,35 +1532,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1576,13 +1568,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650328</v>
+        <v>650369</v>
       </c>
       <c r="R9" t="n">
-        <v>6673703</v>
+        <v>6673665</v>
       </c>
       <c r="S9" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,7 +1603,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1621,7 +1613,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,7 +1645,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399630</v>
+        <v>122399627</v>
       </c>
       <c r="B10" t="n">
         <v>5193</v>
@@ -1687,7 +1684,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1697,10 +1694,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650217</v>
+        <v>650420</v>
       </c>
       <c r="R10" t="n">
-        <v>6673709</v>
+        <v>6673617</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1732,7 +1729,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1742,7 +1739,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,10 +1766,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399626</v>
+        <v>122399630</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,21 +1782,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1808,7 +1805,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1818,10 +1815,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650382</v>
+        <v>650217</v>
       </c>
       <c r="R11" t="n">
-        <v>6673643</v>
+        <v>6673709</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1853,7 +1850,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1860,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399628</v>
+        <v>122399668</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>98240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1902,36 +1899,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650379</v>
+        <v>650331</v>
       </c>
       <c r="R12" t="n">
-        <v>6673641</v>
+        <v>6673701</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1984,7 +1984,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2011,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399670</v>
+        <v>122399644</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
+        <v>57753</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2023,39 +2028,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2063,13 +2064,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650313</v>
+        <v>650328</v>
       </c>
       <c r="R13" t="n">
-        <v>6673680</v>
+        <v>6673703</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2098,7 +2099,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2108,7 +2109,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,10 +2136,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399666</v>
+        <v>122399667</v>
       </c>
       <c r="B14" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2170,10 +2171,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2183,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650369</v>
+        <v>650365</v>
       </c>
       <c r="R14" t="n">
-        <v>6673665</v>
+        <v>6673701</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2218,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2228,12 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,7 +2263,7 @@
         <v>122399676</v>
       </c>
       <c r="B15" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384373</v>
+        <v>122384466</v>
       </c>
       <c r="B16" t="n">
-        <v>57399</v>
+        <v>91234</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,39 +2396,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2436,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650373</v>
+        <v>650393</v>
       </c>
       <c r="R16" t="n">
-        <v>6674389</v>
+        <v>6674366</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2471,7 +2462,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2481,7 +2472,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,8 +2481,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2508,10 +2515,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384468</v>
+        <v>122384462</v>
       </c>
       <c r="B17" t="n">
-        <v>91277</v>
+        <v>90833</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2520,25 +2527,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2551,10 +2558,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650436</v>
+        <v>650428</v>
       </c>
       <c r="R17" t="n">
-        <v>6674345</v>
+        <v>6674388</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2586,7 +2593,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2596,12 +2603,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,24 +2612,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2644,10 +2630,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384394</v>
+        <v>122384417</v>
       </c>
       <c r="B18" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2660,21 +2646,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2686,23 +2672,23 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650394</v>
+        <v>650385</v>
       </c>
       <c r="R18" t="n">
-        <v>6674272</v>
+        <v>6674365</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2731,7 +2717,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,7 +2727,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2768,10 +2759,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384472</v>
+        <v>122384443</v>
       </c>
       <c r="B19" t="n">
-        <v>98237</v>
+        <v>90833</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2780,39 +2771,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2820,10 +2802,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650415</v>
+        <v>650438</v>
       </c>
       <c r="R19" t="n">
-        <v>6674360</v>
+        <v>6674347</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2855,7 +2837,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2865,7 +2847,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2892,10 +2874,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384388</v>
+        <v>122384468</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>91278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2904,39 +2886,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2944,10 +2917,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650400</v>
+        <v>650436</v>
       </c>
       <c r="R20" t="n">
-        <v>6674425</v>
+        <v>6674345</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2979,7 +2952,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2989,7 +2962,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2998,8 +2976,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3016,10 +3010,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384436</v>
+        <v>122384434</v>
       </c>
       <c r="B21" t="n">
-        <v>80613</v>
+        <v>74696</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3028,25 +3022,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3059,10 +3053,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650363</v>
+        <v>650407</v>
       </c>
       <c r="R21" t="n">
-        <v>6674334</v>
+        <v>6674363</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3094,7 +3088,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3104,7 +3098,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3131,10 +3125,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384442</v>
+        <v>122384407</v>
       </c>
       <c r="B22" t="n">
-        <v>90804</v>
+        <v>57399</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3143,30 +3137,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3174,10 +3177,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650393</v>
+        <v>650101</v>
       </c>
       <c r="R22" t="n">
-        <v>6674157</v>
+        <v>6674120</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3209,7 +3212,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3219,7 +3222,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3246,10 +3249,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384462</v>
+        <v>122384485</v>
       </c>
       <c r="B23" t="n">
-        <v>90839</v>
+        <v>100506</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3258,41 +3261,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650428</v>
+        <v>650432</v>
       </c>
       <c r="R23" t="n">
-        <v>6674388</v>
+        <v>6674247</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3324,7 +3328,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3334,7 +3338,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3361,10 +3365,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384477</v>
+        <v>122384394</v>
       </c>
       <c r="B24" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3373,39 +3377,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3413,10 +3417,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650415</v>
+        <v>650394</v>
       </c>
       <c r="R24" t="n">
-        <v>6674216</v>
+        <v>6674272</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3448,7 +3452,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3458,7 +3462,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3485,10 +3489,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384484</v>
+        <v>122384373</v>
       </c>
       <c r="B25" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3497,42 +3501,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650407</v>
+        <v>650373</v>
       </c>
       <c r="R25" t="n">
-        <v>6674068</v>
+        <v>6674389</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3564,7 +3576,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3574,7 +3586,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3601,10 +3613,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384432</v>
+        <v>122384436</v>
       </c>
       <c r="B26" t="n">
-        <v>74696</v>
+        <v>80613</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3613,25 +3625,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3644,10 +3656,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650422</v>
+        <v>650363</v>
       </c>
       <c r="R26" t="n">
-        <v>6674376</v>
+        <v>6674334</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3679,7 +3691,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3689,7 +3701,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3698,24 +3710,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3732,10 +3728,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384434</v>
+        <v>122384464</v>
       </c>
       <c r="B27" t="n">
-        <v>74696</v>
+        <v>90833</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3744,25 +3740,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3771,14 +3767,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650407</v>
+        <v>650429</v>
       </c>
       <c r="R27" t="n">
-        <v>6674363</v>
+        <v>6674188</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3810,7 +3806,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3820,7 +3816,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3847,10 +3843,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384400</v>
+        <v>122384477</v>
       </c>
       <c r="B28" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3859,39 +3855,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3899,10 +3895,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650362</v>
+        <v>650415</v>
       </c>
       <c r="R28" t="n">
-        <v>6674082</v>
+        <v>6674216</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3934,7 +3930,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3944,7 +3940,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3971,10 +3967,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384465</v>
+        <v>122384410</v>
       </c>
       <c r="B29" t="n">
-        <v>91123</v>
+        <v>57399</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3987,37 +3983,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650436</v>
+        <v>650147</v>
       </c>
       <c r="R29" t="n">
-        <v>6674342</v>
+        <v>6674088</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4049,7 +4054,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4059,7 +4064,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4086,7 +4091,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384407</v>
+        <v>122384404</v>
       </c>
       <c r="B30" t="n">
         <v>57399</v>
@@ -4128,7 +4133,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650101</v>
+        <v>650195</v>
       </c>
       <c r="R30" t="n">
-        <v>6674120</v>
+        <v>6674100</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4173,7 +4178,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4183,7 +4188,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4210,10 +4215,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384466</v>
+        <v>122384411</v>
       </c>
       <c r="B31" t="n">
-        <v>91233</v>
+        <v>57399</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4222,41 +4227,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650393</v>
+        <v>650415</v>
       </c>
       <c r="R31" t="n">
-        <v>6674366</v>
+        <v>6674083</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4288,7 +4302,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4298,7 +4312,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4307,24 +4321,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4341,10 +4339,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384476</v>
+        <v>122384465</v>
       </c>
       <c r="B32" t="n">
-        <v>98237</v>
+        <v>91124</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4353,50 +4351,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650396</v>
+        <v>650436</v>
       </c>
       <c r="R32" t="n">
-        <v>6674252</v>
+        <v>6674342</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4428,7 +4417,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4438,7 +4427,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4589,7 +4578,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384410</v>
+        <v>122384395</v>
       </c>
       <c r="B34" t="n">
         <v>57399</v>
@@ -4641,10 +4630,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650147</v>
+        <v>650395</v>
       </c>
       <c r="R34" t="n">
-        <v>6674088</v>
+        <v>6674254</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4676,7 +4665,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4686,7 +4675,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4713,10 +4702,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384417</v>
+        <v>122384403</v>
       </c>
       <c r="B35" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4729,21 +4718,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4755,23 +4744,23 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650385</v>
+        <v>650237</v>
       </c>
       <c r="R35" t="n">
-        <v>6674365</v>
+        <v>6674049</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4800,7 +4789,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4810,12 +4799,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4842,10 +4826,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384473</v>
+        <v>122384400</v>
       </c>
       <c r="B36" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4854,50 +4838,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650400</v>
+        <v>650362</v>
       </c>
       <c r="R36" t="n">
-        <v>6674415</v>
+        <v>6674082</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4929,7 +4913,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4939,7 +4923,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4966,10 +4950,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384439</v>
+        <v>122384391</v>
       </c>
       <c r="B37" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4982,37 +4966,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650238</v>
+        <v>650364</v>
       </c>
       <c r="R37" t="n">
-        <v>6674074</v>
+        <v>6674383</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5044,7 +5037,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5054,12 +5047,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5086,10 +5074,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384443</v>
+        <v>122384397</v>
       </c>
       <c r="B38" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5102,37 +5090,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650438</v>
+        <v>650406</v>
       </c>
       <c r="R38" t="n">
-        <v>6674347</v>
+        <v>6674220</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5164,7 +5161,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5174,7 +5171,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5201,10 +5198,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384483</v>
+        <v>122384484</v>
       </c>
       <c r="B39" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5245,10 +5242,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650238</v>
+        <v>650407</v>
       </c>
       <c r="R39" t="n">
-        <v>6674076</v>
+        <v>6674068</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5280,7 +5277,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5290,7 +5287,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5317,10 +5314,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384470</v>
+        <v>122384479</v>
       </c>
       <c r="B40" t="n">
-        <v>91277</v>
+        <v>100506</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5329,30 +5326,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5360,10 +5358,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650388</v>
+        <v>650415</v>
       </c>
       <c r="R40" t="n">
-        <v>6674308</v>
+        <v>6674370</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5395,7 +5393,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5405,7 +5403,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5432,10 +5430,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384412</v>
+        <v>122384480</v>
       </c>
       <c r="B41" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5444,39 +5442,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5484,10 +5474,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650399</v>
+        <v>650316</v>
       </c>
       <c r="R41" t="n">
-        <v>6674181</v>
+        <v>6674034</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5519,7 +5509,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5529,7 +5519,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5556,10 +5546,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384454</v>
+        <v>122384472</v>
       </c>
       <c r="B42" t="n">
-        <v>90839</v>
+        <v>98240</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5568,30 +5558,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5599,10 +5598,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650440</v>
+        <v>650415</v>
       </c>
       <c r="R42" t="n">
-        <v>6674369</v>
+        <v>6674360</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5634,7 +5633,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5644,7 +5643,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5671,10 +5670,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384369</v>
+        <v>122384481</v>
       </c>
       <c r="B43" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5683,50 +5682,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650395</v>
+        <v>650230</v>
       </c>
       <c r="R43" t="n">
-        <v>6674349</v>
+        <v>6674064</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5758,7 +5749,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5768,7 +5759,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5795,10 +5786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384404</v>
+        <v>122384487</v>
       </c>
       <c r="B44" t="n">
-        <v>57399</v>
+        <v>105346</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5807,50 +5798,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650195</v>
+        <v>650442</v>
       </c>
       <c r="R44" t="n">
-        <v>6674100</v>
+        <v>6674345</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5882,7 +5865,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5892,7 +5875,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5919,10 +5902,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384479</v>
+        <v>122384470</v>
       </c>
       <c r="B45" t="n">
-        <v>100503</v>
+        <v>91278</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5931,31 +5914,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5963,10 +5945,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650415</v>
+        <v>650388</v>
       </c>
       <c r="R45" t="n">
-        <v>6674370</v>
+        <v>6674308</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5998,7 +5980,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6008,7 +5990,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6035,10 +6017,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384437</v>
+        <v>122384454</v>
       </c>
       <c r="B46" t="n">
-        <v>80613</v>
+        <v>90833</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6051,21 +6033,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6074,14 +6056,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650387</v>
+        <v>650440</v>
       </c>
       <c r="R46" t="n">
-        <v>6674259</v>
+        <v>6674369</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6113,7 +6095,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6123,7 +6105,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6150,10 +6132,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384366</v>
+        <v>122384437</v>
       </c>
       <c r="B47" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6166,46 +6148,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650419</v>
+        <v>650387</v>
       </c>
       <c r="R47" t="n">
-        <v>6674371</v>
+        <v>6674259</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6237,7 +6210,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6247,7 +6220,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6274,10 +6247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384487</v>
+        <v>122384366</v>
       </c>
       <c r="B48" t="n">
-        <v>105343</v>
+        <v>57399</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6286,31 +6259,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6318,10 +6299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650442</v>
+        <v>650419</v>
       </c>
       <c r="R48" t="n">
-        <v>6674345</v>
+        <v>6674371</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6353,7 +6334,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6363,7 +6344,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6390,10 +6371,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384395</v>
+        <v>122384473</v>
       </c>
       <c r="B49" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6402,50 +6383,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650395</v>
+        <v>650400</v>
       </c>
       <c r="R49" t="n">
-        <v>6674254</v>
+        <v>6674415</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6477,7 +6458,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6487,7 +6468,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6514,10 +6495,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384480</v>
+        <v>122384432</v>
       </c>
       <c r="B50" t="n">
-        <v>100503</v>
+        <v>74696</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6530,38 +6511,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650316</v>
+        <v>650422</v>
       </c>
       <c r="R50" t="n">
-        <v>6674034</v>
+        <v>6674376</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6593,7 +6573,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6603,7 +6583,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6612,8 +6592,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6630,10 +6626,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384464</v>
+        <v>122384371</v>
       </c>
       <c r="B51" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6646,26 +6642,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6673,13 +6678,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650429</v>
+        <v>650400</v>
       </c>
       <c r="R51" t="n">
-        <v>6674188</v>
+        <v>6674206</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6708,7 +6713,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6718,7 +6723,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6745,10 +6750,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384485</v>
+        <v>122384440</v>
       </c>
       <c r="B52" t="n">
-        <v>100503</v>
+        <v>80613</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6757,31 +6762,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6789,10 +6793,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650432</v>
+        <v>650077</v>
       </c>
       <c r="R52" t="n">
-        <v>6674247</v>
+        <v>6674268</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6824,7 +6828,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6834,7 +6838,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6861,10 +6865,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384481</v>
+        <v>122384476</v>
       </c>
       <c r="B53" t="n">
-        <v>100503</v>
+        <v>98240</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6873,29 +6877,37 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6905,10 +6917,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650230</v>
+        <v>650396</v>
       </c>
       <c r="R53" t="n">
-        <v>6674064</v>
+        <v>6674252</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6940,7 +6952,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6950,7 +6962,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6977,7 +6989,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384391</v>
+        <v>122384402</v>
       </c>
       <c r="B54" t="n">
         <v>57399</v>
@@ -7019,20 +7031,20 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650364</v>
+        <v>650297</v>
       </c>
       <c r="R54" t="n">
-        <v>6674383</v>
+        <v>6674040</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7064,7 +7076,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7074,7 +7086,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7101,7 +7113,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384411</v>
+        <v>122384388</v>
       </c>
       <c r="B55" t="n">
         <v>57399</v>
@@ -7143,20 +7155,20 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650415</v>
+        <v>650400</v>
       </c>
       <c r="R55" t="n">
-        <v>6674083</v>
+        <v>6674425</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7188,7 +7200,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7198,7 +7210,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7225,10 +7237,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384402</v>
+        <v>122384438</v>
       </c>
       <c r="B56" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7241,35 +7253,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7277,10 +7280,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650297</v>
+        <v>650353</v>
       </c>
       <c r="R56" t="n">
-        <v>6674040</v>
+        <v>6674235</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7312,7 +7315,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7322,7 +7325,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7349,10 +7357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384438</v>
+        <v>122384442</v>
       </c>
       <c r="B57" t="n">
-        <v>80613</v>
+        <v>90798</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7361,25 +7369,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7392,10 +7400,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650353</v>
+        <v>650393</v>
       </c>
       <c r="R57" t="n">
-        <v>6674235</v>
+        <v>6674157</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7427,7 +7435,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7437,12 +7445,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7469,10 +7472,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384440</v>
+        <v>122384483</v>
       </c>
       <c r="B58" t="n">
-        <v>80613</v>
+        <v>100506</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7481,30 +7484,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7512,10 +7516,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650077</v>
+        <v>650238</v>
       </c>
       <c r="R58" t="n">
-        <v>6674268</v>
+        <v>6674076</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7547,7 +7551,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7557,7 +7561,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7584,7 +7588,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384397</v>
+        <v>122384412</v>
       </c>
       <c r="B59" t="n">
         <v>57399</v>
@@ -7626,7 +7630,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7636,10 +7640,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650406</v>
+        <v>650399</v>
       </c>
       <c r="R59" t="n">
-        <v>6674220</v>
+        <v>6674181</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7671,7 +7675,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7681,7 +7685,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7708,10 +7712,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384371</v>
+        <v>122384439</v>
       </c>
       <c r="B60" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7724,35 +7728,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7760,13 +7755,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650400</v>
+        <v>650238</v>
       </c>
       <c r="R60" t="n">
-        <v>6674206</v>
+        <v>6674074</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7795,7 +7790,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7805,7 +7800,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7832,7 +7832,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384403</v>
+        <v>122384369</v>
       </c>
       <c r="B61" t="n">
         <v>57399</v>
@@ -7880,14 +7880,14 @@
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650237</v>
+        <v>650395</v>
       </c>
       <c r="R61" t="n">
-        <v>6674049</v>
+        <v>6674349</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,10 +7956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399658</v>
+        <v>122399640</v>
       </c>
       <c r="B62" t="n">
-        <v>94855</v>
+        <v>57399</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7968,31 +7968,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8000,10 +8008,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649956</v>
+        <v>650059</v>
       </c>
       <c r="R62" t="n">
-        <v>6674194</v>
+        <v>6674144</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8035,7 +8043,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8045,7 +8053,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8072,10 +8080,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399656</v>
+        <v>122399673</v>
       </c>
       <c r="B63" t="n">
-        <v>94759</v>
+        <v>100506</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8088,21 +8096,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8116,10 +8124,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649935</v>
+        <v>650321</v>
       </c>
       <c r="R63" t="n">
-        <v>6674249</v>
+        <v>6673981</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8151,7 +8159,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8161,7 +8169,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8188,10 +8196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399637</v>
+        <v>122399675</v>
       </c>
       <c r="B64" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8200,39 +8208,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649994</v>
+        <v>650473</v>
       </c>
       <c r="R64" t="n">
-        <v>6674118</v>
+        <v>6673911</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8312,10 +8312,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399673</v>
+        <v>122399650</v>
       </c>
       <c r="B65" t="n">
-        <v>100503</v>
+        <v>90798</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8328,27 +8328,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8356,10 +8355,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650321</v>
+        <v>650386</v>
       </c>
       <c r="R65" t="n">
-        <v>6673981</v>
+        <v>6673912</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8391,7 +8390,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8401,7 +8400,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8428,10 +8427,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399641</v>
+        <v>122399658</v>
       </c>
       <c r="B66" t="n">
-        <v>57399</v>
+        <v>94857</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8440,39 +8439,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8480,10 +8471,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>650092</v>
+        <v>649956</v>
       </c>
       <c r="R66" t="n">
-        <v>6674138</v>
+        <v>6674194</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8515,7 +8506,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8525,7 +8516,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8552,10 +8543,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399650</v>
+        <v>122399642</v>
       </c>
       <c r="B67" t="n">
-        <v>90804</v>
+        <v>57399</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8564,30 +8555,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8595,10 +8595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>650386</v>
+        <v>650411</v>
       </c>
       <c r="R67" t="n">
-        <v>6673912</v>
+        <v>6674002</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8667,10 +8667,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399649</v>
+        <v>122399639</v>
       </c>
       <c r="B68" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8683,26 +8683,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8710,10 +8719,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650383</v>
+        <v>650031</v>
       </c>
       <c r="R68" t="n">
-        <v>6673928</v>
+        <v>6674158</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8745,7 +8754,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8755,7 +8764,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8782,10 +8791,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399675</v>
+        <v>122399649</v>
       </c>
       <c r="B69" t="n">
-        <v>100503</v>
+        <v>80613</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8794,31 +8803,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8826,10 +8834,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650473</v>
+        <v>650383</v>
       </c>
       <c r="R69" t="n">
-        <v>6673911</v>
+        <v>6673928</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8861,7 +8869,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8871,7 +8879,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8898,10 +8906,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399672</v>
+        <v>122399637</v>
       </c>
       <c r="B70" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8910,31 +8918,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8942,10 +8958,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>650329</v>
+        <v>649994</v>
       </c>
       <c r="R70" t="n">
-        <v>6673994</v>
+        <v>6674118</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8977,7 +8993,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8987,7 +9003,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9014,10 +9030,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399640</v>
+        <v>122399672</v>
       </c>
       <c r="B71" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9026,39 +9042,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9066,10 +9074,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650059</v>
+        <v>650329</v>
       </c>
       <c r="R71" t="n">
-        <v>6674144</v>
+        <v>6673994</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9101,7 +9109,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9111,7 +9119,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9138,10 +9146,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399642</v>
+        <v>122399656</v>
       </c>
       <c r="B72" t="n">
-        <v>57399</v>
+        <v>94761</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9150,39 +9158,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9190,10 +9190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>650411</v>
+        <v>649935</v>
       </c>
       <c r="R72" t="n">
-        <v>6674002</v>
+        <v>6674249</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9262,7 +9262,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399639</v>
+        <v>122399641</v>
       </c>
       <c r="B73" t="n">
         <v>57399</v>
@@ -9304,7 +9304,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650031</v>
+        <v>650092</v>
       </c>
       <c r="R73" t="n">
-        <v>6674158</v>
+        <v>6674138</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9386,14 +9386,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399645</v>
+        <v>122399660</v>
       </c>
       <c r="B74" t="n">
-        <v>57753</v>
+        <v>94857</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9402,27 +9402,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>210</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649902</v>
+        <v>649992</v>
       </c>
       <c r="R74" t="n">
-        <v>6674271</v>
+        <v>6674192</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9498,18 +9498,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399655</v>
+        <v>122399657</v>
       </c>
       <c r="B75" t="n">
-        <v>94759</v>
+        <v>94857</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9522,21 +9518,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9550,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649962</v>
+        <v>649950</v>
       </c>
       <c r="R75" t="n">
-        <v>6674201</v>
+        <v>6674175</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9585,7 +9581,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9595,7 +9591,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9622,10 +9618,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399660</v>
+        <v>122399655</v>
       </c>
       <c r="B76" t="n">
-        <v>94855</v>
+        <v>94761</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9638,21 +9634,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9666,10 +9662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>649992</v>
+        <v>649962</v>
       </c>
       <c r="R76" t="n">
-        <v>6674192</v>
+        <v>6674201</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9701,7 +9697,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9711,7 +9707,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9738,14 +9734,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122399657</v>
+        <v>122399645</v>
       </c>
       <c r="B77" t="n">
-        <v>94855</v>
+        <v>57753</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9754,27 +9750,27 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9782,10 +9778,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>649950</v>
+        <v>649902</v>
       </c>
       <c r="R77" t="n">
-        <v>6674175</v>
+        <v>6674271</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9817,7 +9813,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9827,7 +9823,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9850,7 +9846,11 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr"/>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399628</v>
+        <v>122399633</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,13 +708,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650379</v>
+        <v>650328</v>
       </c>
       <c r="R2" t="n">
-        <v>6673641</v>
+        <v>6673703</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399652</v>
+        <v>122399670</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,30 +811,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650328</v>
+        <v>650313</v>
       </c>
       <c r="R3" t="n">
-        <v>6673703</v>
+        <v>6673680</v>
       </c>
       <c r="S3" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399670</v>
+        <v>122399630</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,39 +935,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650313</v>
+        <v>650217</v>
       </c>
       <c r="R4" t="n">
-        <v>6673680</v>
+        <v>6673709</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -998,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399671</v>
+        <v>122399668</v>
       </c>
       <c r="B5" t="n">
-        <v>100506</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,29 +1056,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1079,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650309</v>
+        <v>650331</v>
       </c>
       <c r="R5" t="n">
-        <v>6673789</v>
+        <v>6673701</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1141,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399626</v>
+        <v>122399666</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,36 +1185,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650382</v>
+        <v>650369</v>
       </c>
       <c r="R6" t="n">
-        <v>6673643</v>
+        <v>6673665</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1235,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1266,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1298,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399633</v>
+        <v>122399671</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,39 +1310,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,13 +1342,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650328</v>
+        <v>650309</v>
       </c>
       <c r="R7" t="n">
-        <v>6673703</v>
+        <v>6673789</v>
       </c>
       <c r="S7" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,7 +1377,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1387,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399632</v>
+        <v>122399652</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>90833</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,35 +1430,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1448,13 +1457,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650256</v>
+        <v>650328</v>
       </c>
       <c r="R8" t="n">
-        <v>6673700</v>
+        <v>6673703</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1493,7 +1502,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399666</v>
+        <v>122399627</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,35 +1541,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1568,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650369</v>
+        <v>650420</v>
       </c>
       <c r="R9" t="n">
-        <v>6673665</v>
+        <v>6673617</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1603,7 +1613,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,12 +1623,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,10 +1650,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399627</v>
+        <v>122399632</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1657,20 +1662,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1678,13 +1683,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1694,10 +1702,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650420</v>
+        <v>650256</v>
       </c>
       <c r="R10" t="n">
-        <v>6673617</v>
+        <v>6673700</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1729,7 +1737,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1739,7 +1747,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1766,7 +1774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399630</v>
+        <v>122399628</v>
       </c>
       <c r="B11" t="n">
         <v>5193</v>
@@ -1805,7 +1813,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1815,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650217</v>
+        <v>650379</v>
       </c>
       <c r="R11" t="n">
-        <v>6673709</v>
+        <v>6673641</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1850,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1860,7 +1868,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399668</v>
+        <v>122399626</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,39 +1907,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650331</v>
+        <v>650382</v>
       </c>
       <c r="R12" t="n">
-        <v>6673701</v>
+        <v>6673643</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1974,7 +1979,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1984,12 +1989,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399644</v>
+        <v>122399667</v>
       </c>
       <c r="B13" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,35 +2028,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2064,13 +2068,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650328</v>
+        <v>650365</v>
       </c>
       <c r="R13" t="n">
-        <v>6673703</v>
+        <v>6673701</v>
       </c>
       <c r="S13" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2099,7 +2103,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2109,7 +2113,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,10 +2140,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399667</v>
+        <v>122399644</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>57753</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,39 +2152,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650365</v>
+        <v>650328</v>
       </c>
       <c r="R14" t="n">
-        <v>6673701</v>
+        <v>6673703</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384466</v>
+        <v>122384439</v>
       </c>
       <c r="B16" t="n">
-        <v>91234</v>
+        <v>80613</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,25 +2396,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4217</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2423,14 +2423,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650393</v>
+        <v>650238</v>
       </c>
       <c r="R16" t="n">
-        <v>6674366</v>
+        <v>6674074</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,7 +2472,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,24 +2486,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2515,10 +2504,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384462</v>
+        <v>122384438</v>
       </c>
       <c r="B17" t="n">
-        <v>90833</v>
+        <v>80613</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2531,21 +2520,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2554,14 +2543,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650428</v>
+        <v>650353</v>
       </c>
       <c r="R17" t="n">
-        <v>6674388</v>
+        <v>6674235</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2593,7 +2582,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2603,7 +2592,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2630,10 +2624,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384417</v>
+        <v>122384406</v>
       </c>
       <c r="B18" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2646,21 +2640,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2672,23 +2666,23 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650385</v>
+        <v>650115</v>
       </c>
       <c r="R18" t="n">
-        <v>6674365</v>
+        <v>6674245</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2717,7 +2711,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2727,12 +2721,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2759,10 +2748,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384443</v>
+        <v>122384466</v>
       </c>
       <c r="B19" t="n">
-        <v>90833</v>
+        <v>91234</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,25 +2760,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2802,10 +2791,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650438</v>
+        <v>650393</v>
       </c>
       <c r="R19" t="n">
-        <v>6674347</v>
+        <v>6674366</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2837,7 +2826,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2847,7 +2836,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2856,8 +2845,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2874,7 +2879,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384468</v>
+        <v>122384470</v>
       </c>
       <c r="B20" t="n">
         <v>91278</v>
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650436</v>
+        <v>650388</v>
       </c>
       <c r="R20" t="n">
-        <v>6674345</v>
+        <v>6674308</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2952,7 +2957,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2962,12 +2967,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2976,24 +2976,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3010,10 +2994,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384434</v>
+        <v>122384454</v>
       </c>
       <c r="B21" t="n">
-        <v>74696</v>
+        <v>90833</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3022,25 +3006,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3053,10 +3037,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650407</v>
+        <v>650440</v>
       </c>
       <c r="R21" t="n">
-        <v>6674363</v>
+        <v>6674369</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3088,7 +3072,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3098,7 +3082,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3125,10 +3109,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384407</v>
+        <v>122384434</v>
       </c>
       <c r="B22" t="n">
-        <v>57399</v>
+        <v>74696</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3137,50 +3121,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650101</v>
+        <v>650407</v>
       </c>
       <c r="R22" t="n">
-        <v>6674120</v>
+        <v>6674363</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3212,7 +3187,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3222,7 +3197,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3249,10 +3224,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384485</v>
+        <v>122384411</v>
       </c>
       <c r="B23" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3261,31 +3236,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3293,10 +3276,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650432</v>
+        <v>650415</v>
       </c>
       <c r="R23" t="n">
-        <v>6674247</v>
+        <v>6674083</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3328,7 +3311,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3338,7 +3321,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3489,7 +3472,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384373</v>
+        <v>122384412</v>
       </c>
       <c r="B25" t="n">
         <v>57399</v>
@@ -3531,20 +3514,20 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650373</v>
+        <v>650399</v>
       </c>
       <c r="R25" t="n">
-        <v>6674389</v>
+        <v>6674181</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3576,7 +3559,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3586,7 +3569,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3613,10 +3596,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384436</v>
+        <v>122384397</v>
       </c>
       <c r="B26" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3629,37 +3612,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650363</v>
+        <v>650406</v>
       </c>
       <c r="R26" t="n">
-        <v>6674334</v>
+        <v>6674220</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3691,7 +3683,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3701,7 +3693,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3728,10 +3720,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384464</v>
+        <v>122384487</v>
       </c>
       <c r="B27" t="n">
-        <v>90833</v>
+        <v>105346</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3740,41 +3732,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650429</v>
+        <v>650442</v>
       </c>
       <c r="R27" t="n">
-        <v>6674188</v>
+        <v>6674345</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3806,7 +3799,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3816,7 +3809,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3843,10 +3836,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384477</v>
+        <v>122384442</v>
       </c>
       <c r="B28" t="n">
-        <v>98240</v>
+        <v>90798</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3855,39 +3848,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3895,10 +3879,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650415</v>
+        <v>650393</v>
       </c>
       <c r="R28" t="n">
-        <v>6674216</v>
+        <v>6674157</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3930,7 +3914,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3940,7 +3924,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3967,10 +3951,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384410</v>
+        <v>122384440</v>
       </c>
       <c r="B29" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3983,35 +3967,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4019,10 +3994,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650147</v>
+        <v>650077</v>
       </c>
       <c r="R29" t="n">
-        <v>6674088</v>
+        <v>6674268</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4054,7 +4029,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4064,7 +4039,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4215,10 +4190,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384411</v>
+        <v>122384477</v>
       </c>
       <c r="B31" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4227,39 +4202,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4270,7 +4245,7 @@
         <v>650415</v>
       </c>
       <c r="R31" t="n">
-        <v>6674083</v>
+        <v>6674216</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4302,7 +4277,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4312,7 +4287,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4339,10 +4314,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384465</v>
+        <v>122384473</v>
       </c>
       <c r="B32" t="n">
-        <v>91124</v>
+        <v>98240</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4351,30 +4326,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4382,10 +4366,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650436</v>
+        <v>650400</v>
       </c>
       <c r="R32" t="n">
-        <v>6674342</v>
+        <v>6674415</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4417,7 +4401,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4427,7 +4411,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4454,10 +4438,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384406</v>
+        <v>122384480</v>
       </c>
       <c r="B33" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4466,39 +4450,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4506,10 +4482,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650115</v>
+        <v>650316</v>
       </c>
       <c r="R33" t="n">
-        <v>6674245</v>
+        <v>6674034</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4541,7 +4517,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4551,7 +4527,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4578,7 +4554,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384395</v>
+        <v>122384366</v>
       </c>
       <c r="B34" t="n">
         <v>57399</v>
@@ -4626,14 +4602,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650395</v>
+        <v>650419</v>
       </c>
       <c r="R34" t="n">
-        <v>6674254</v>
+        <v>6674371</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4665,7 +4641,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4675,7 +4651,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4702,10 +4678,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384403</v>
+        <v>122384417</v>
       </c>
       <c r="B35" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4718,21 +4694,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4744,23 +4720,23 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650237</v>
+        <v>650385</v>
       </c>
       <c r="R35" t="n">
-        <v>6674049</v>
+        <v>6674365</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4789,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4799,7 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4826,10 +4807,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384400</v>
+        <v>122384483</v>
       </c>
       <c r="B36" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4838,39 +4819,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4878,10 +4851,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650362</v>
+        <v>650238</v>
       </c>
       <c r="R36" t="n">
-        <v>6674082</v>
+        <v>6674076</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4913,7 +4886,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4923,7 +4896,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4950,7 +4923,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384391</v>
+        <v>122384410</v>
       </c>
       <c r="B37" t="n">
         <v>57399</v>
@@ -4998,14 +4971,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650364</v>
+        <v>650147</v>
       </c>
       <c r="R37" t="n">
-        <v>6674383</v>
+        <v>6674088</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5037,7 +5010,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5047,7 +5020,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5074,7 +5047,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384397</v>
+        <v>122384403</v>
       </c>
       <c r="B38" t="n">
         <v>57399</v>
@@ -5116,7 +5089,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5126,10 +5099,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650406</v>
+        <v>650237</v>
       </c>
       <c r="R38" t="n">
-        <v>6674220</v>
+        <v>6674049</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5161,7 +5134,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5171,7 +5144,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5198,10 +5171,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384484</v>
+        <v>122384391</v>
       </c>
       <c r="B39" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5210,42 +5183,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650407</v>
+        <v>650364</v>
       </c>
       <c r="R39" t="n">
-        <v>6674068</v>
+        <v>6674383</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5277,7 +5258,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5287,7 +5268,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5430,10 +5411,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384480</v>
+        <v>122384432</v>
       </c>
       <c r="B41" t="n">
-        <v>100506</v>
+        <v>74696</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5446,38 +5427,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650316</v>
+        <v>650422</v>
       </c>
       <c r="R41" t="n">
-        <v>6674034</v>
+        <v>6674376</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5509,7 +5489,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5519,7 +5499,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5528,8 +5508,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5546,10 +5542,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384472</v>
+        <v>122384443</v>
       </c>
       <c r="B42" t="n">
-        <v>98240</v>
+        <v>90833</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5558,39 +5554,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5598,10 +5585,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650415</v>
+        <v>650438</v>
       </c>
       <c r="R42" t="n">
-        <v>6674360</v>
+        <v>6674347</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5633,7 +5620,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5643,7 +5630,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5670,10 +5657,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384481</v>
+        <v>122384395</v>
       </c>
       <c r="B43" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5682,31 +5669,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5714,10 +5709,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650230</v>
+        <v>650395</v>
       </c>
       <c r="R43" t="n">
-        <v>6674064</v>
+        <v>6674254</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5749,7 +5744,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5759,7 +5754,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5786,10 +5781,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384487</v>
+        <v>122384371</v>
       </c>
       <c r="B44" t="n">
-        <v>105346</v>
+        <v>57399</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5798,45 +5793,53 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650442</v>
+        <v>650400</v>
       </c>
       <c r="R44" t="n">
-        <v>6674345</v>
+        <v>6674206</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5865,7 +5868,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5875,7 +5878,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5902,10 +5905,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384470</v>
+        <v>122384465</v>
       </c>
       <c r="B45" t="n">
-        <v>91278</v>
+        <v>91124</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5914,25 +5917,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5945,10 +5948,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650388</v>
+        <v>650436</v>
       </c>
       <c r="R45" t="n">
-        <v>6674308</v>
+        <v>6674342</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5980,7 +5983,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5990,7 +5993,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6017,10 +6020,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384454</v>
+        <v>122384373</v>
       </c>
       <c r="B46" t="n">
-        <v>90833</v>
+        <v>57399</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6033,26 +6036,35 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6060,10 +6072,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650440</v>
+        <v>650373</v>
       </c>
       <c r="R46" t="n">
-        <v>6674369</v>
+        <v>6674389</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6095,7 +6107,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6105,7 +6117,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6132,10 +6144,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384437</v>
+        <v>122384472</v>
       </c>
       <c r="B47" t="n">
-        <v>80613</v>
+        <v>98240</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6144,41 +6156,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650387</v>
+        <v>650415</v>
       </c>
       <c r="R47" t="n">
-        <v>6674259</v>
+        <v>6674360</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6210,7 +6231,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6220,7 +6241,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6247,7 +6268,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384366</v>
+        <v>122384402</v>
       </c>
       <c r="B48" t="n">
         <v>57399</v>
@@ -6289,20 +6310,20 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650419</v>
+        <v>650297</v>
       </c>
       <c r="R48" t="n">
-        <v>6674371</v>
+        <v>6674040</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6334,7 +6355,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6344,7 +6365,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6371,10 +6392,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384473</v>
+        <v>122384369</v>
       </c>
       <c r="B49" t="n">
-        <v>98240</v>
+        <v>57399</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6383,39 +6404,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6423,10 +6444,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650400</v>
+        <v>650395</v>
       </c>
       <c r="R49" t="n">
-        <v>6674415</v>
+        <v>6674349</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6458,7 +6479,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6468,7 +6489,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6495,10 +6516,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384432</v>
+        <v>122384476</v>
       </c>
       <c r="B50" t="n">
-        <v>74696</v>
+        <v>98240</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6507,41 +6528,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650422</v>
+        <v>650396</v>
       </c>
       <c r="R50" t="n">
-        <v>6674376</v>
+        <v>6674252</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6573,7 +6603,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6583,7 +6613,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6592,24 +6622,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6626,10 +6640,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384371</v>
+        <v>122384484</v>
       </c>
       <c r="B51" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6638,39 +6652,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6678,13 +6684,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650400</v>
+        <v>650407</v>
       </c>
       <c r="R51" t="n">
-        <v>6674206</v>
+        <v>6674068</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6713,7 +6719,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6723,7 +6729,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6750,10 +6756,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384440</v>
+        <v>122384485</v>
       </c>
       <c r="B52" t="n">
-        <v>80613</v>
+        <v>100506</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6762,30 +6768,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6793,10 +6800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650077</v>
+        <v>650432</v>
       </c>
       <c r="R52" t="n">
-        <v>6674268</v>
+        <v>6674247</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6828,7 +6835,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6838,7 +6845,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6865,10 +6872,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384476</v>
+        <v>122384468</v>
       </c>
       <c r="B53" t="n">
-        <v>98240</v>
+        <v>91278</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6881,46 +6888,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650396</v>
+        <v>650436</v>
       </c>
       <c r="R53" t="n">
-        <v>6674252</v>
+        <v>6674345</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6952,7 +6950,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6962,7 +6960,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6971,8 +6974,24 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6989,10 +7008,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384402</v>
+        <v>122384464</v>
       </c>
       <c r="B54" t="n">
-        <v>57399</v>
+        <v>90833</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7005,35 +7024,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7041,10 +7051,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650297</v>
+        <v>650429</v>
       </c>
       <c r="R54" t="n">
-        <v>6674040</v>
+        <v>6674188</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7076,7 +7086,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7086,7 +7096,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7113,7 +7123,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384388</v>
+        <v>122384400</v>
       </c>
       <c r="B55" t="n">
         <v>57399</v>
@@ -7161,14 +7171,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650400</v>
+        <v>650362</v>
       </c>
       <c r="R55" t="n">
-        <v>6674425</v>
+        <v>6674082</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7200,7 +7210,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7210,7 +7220,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7237,10 +7247,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384438</v>
+        <v>122384462</v>
       </c>
       <c r="B56" t="n">
-        <v>80613</v>
+        <v>90833</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7253,21 +7263,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7276,14 +7286,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650353</v>
+        <v>650428</v>
       </c>
       <c r="R56" t="n">
-        <v>6674235</v>
+        <v>6674388</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7315,7 +7325,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7325,12 +7335,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7357,10 +7362,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384442</v>
+        <v>122384481</v>
       </c>
       <c r="B57" t="n">
-        <v>90798</v>
+        <v>100506</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7373,26 +7378,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7400,10 +7406,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650393</v>
+        <v>650230</v>
       </c>
       <c r="R57" t="n">
-        <v>6674157</v>
+        <v>6674064</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7435,7 +7441,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7445,7 +7451,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7472,10 +7478,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384483</v>
+        <v>122384437</v>
       </c>
       <c r="B58" t="n">
-        <v>100506</v>
+        <v>80613</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7484,31 +7490,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7516,10 +7521,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650238</v>
+        <v>650387</v>
       </c>
       <c r="R58" t="n">
-        <v>6674076</v>
+        <v>6674259</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7551,7 +7556,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7561,7 +7566,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7588,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384412</v>
+        <v>122384436</v>
       </c>
       <c r="B59" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7604,46 +7609,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650399</v>
+        <v>650363</v>
       </c>
       <c r="R59" t="n">
-        <v>6674181</v>
+        <v>6674334</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7675,7 +7671,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7685,7 +7681,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7712,10 +7708,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384439</v>
+        <v>122384407</v>
       </c>
       <c r="B60" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7728,26 +7724,35 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7755,10 +7760,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650238</v>
+        <v>650101</v>
       </c>
       <c r="R60" t="n">
-        <v>6674074</v>
+        <v>6674120</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7790,7 +7795,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7800,12 +7805,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7832,7 +7832,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384369</v>
+        <v>122384388</v>
       </c>
       <c r="B61" t="n">
         <v>57399</v>
@@ -7874,7 +7874,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650395</v>
+        <v>650400</v>
       </c>
       <c r="R61" t="n">
-        <v>6674349</v>
+        <v>6674425</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,10 +7956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399640</v>
+        <v>122399650</v>
       </c>
       <c r="B62" t="n">
-        <v>57399</v>
+        <v>90798</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7968,39 +7968,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8008,10 +7999,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>650059</v>
+        <v>650386</v>
       </c>
       <c r="R62" t="n">
-        <v>6674144</v>
+        <v>6673912</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8043,7 +8034,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8053,7 +8044,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8196,7 +8187,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399675</v>
+        <v>122399672</v>
       </c>
       <c r="B64" t="n">
         <v>100506</v>
@@ -8240,10 +8231,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650473</v>
+        <v>650329</v>
       </c>
       <c r="R64" t="n">
-        <v>6673911</v>
+        <v>6673994</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8275,7 +8266,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8285,7 +8276,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8312,10 +8303,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399650</v>
+        <v>122399656</v>
       </c>
       <c r="B65" t="n">
-        <v>90798</v>
+        <v>94761</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8328,26 +8319,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8355,10 +8347,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650386</v>
+        <v>649935</v>
       </c>
       <c r="R65" t="n">
-        <v>6673912</v>
+        <v>6674249</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8390,7 +8382,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8400,7 +8392,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8427,10 +8419,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399658</v>
+        <v>122399641</v>
       </c>
       <c r="B66" t="n">
-        <v>94857</v>
+        <v>57399</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8439,31 +8431,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>649956</v>
+        <v>650092</v>
       </c>
       <c r="R66" t="n">
-        <v>6674194</v>
+        <v>6674138</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8543,10 +8543,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399642</v>
+        <v>122399675</v>
       </c>
       <c r="B67" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8555,39 +8555,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8595,10 +8587,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>650411</v>
+        <v>650473</v>
       </c>
       <c r="R67" t="n">
-        <v>6674002</v>
+        <v>6673911</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8630,7 +8622,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8640,7 +8632,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8667,10 +8659,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399639</v>
+        <v>122399649</v>
       </c>
       <c r="B68" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8683,35 +8675,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8719,10 +8702,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650031</v>
+        <v>650383</v>
       </c>
       <c r="R68" t="n">
-        <v>6674158</v>
+        <v>6673928</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8754,7 +8737,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8764,7 +8747,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8791,10 +8774,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399649</v>
+        <v>122399639</v>
       </c>
       <c r="B69" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8807,26 +8790,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8834,10 +8826,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650383</v>
+        <v>650031</v>
       </c>
       <c r="R69" t="n">
-        <v>6673928</v>
+        <v>6674158</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8869,7 +8861,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8879,7 +8871,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8906,7 +8898,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399637</v>
+        <v>122399640</v>
       </c>
       <c r="B70" t="n">
         <v>57399</v>
@@ -8958,10 +8950,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>649994</v>
+        <v>650059</v>
       </c>
       <c r="R70" t="n">
-        <v>6674118</v>
+        <v>6674144</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8993,7 +8985,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9003,7 +8995,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9030,10 +9022,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399672</v>
+        <v>122399642</v>
       </c>
       <c r="B71" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9042,31 +9034,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9074,10 +9074,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650329</v>
+        <v>650411</v>
       </c>
       <c r="R71" t="n">
-        <v>6673994</v>
+        <v>6674002</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9146,10 +9146,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399656</v>
+        <v>122399637</v>
       </c>
       <c r="B72" t="n">
-        <v>94761</v>
+        <v>57399</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9158,31 +9158,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9190,10 +9198,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>649935</v>
+        <v>649994</v>
       </c>
       <c r="R72" t="n">
-        <v>6674249</v>
+        <v>6674118</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9225,7 +9233,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9235,7 +9243,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9262,10 +9270,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399641</v>
+        <v>122399658</v>
       </c>
       <c r="B73" t="n">
-        <v>57399</v>
+        <v>94857</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9274,39 +9282,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650092</v>
+        <v>649956</v>
       </c>
       <c r="R73" t="n">
-        <v>6674138</v>
+        <v>6674194</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9386,7 +9386,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399660</v>
+        <v>122399657</v>
       </c>
       <c r="B74" t="n">
         <v>94857</v>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649992</v>
+        <v>649950</v>
       </c>
       <c r="R74" t="n">
-        <v>6674192</v>
+        <v>6674175</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,7 +9502,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399657</v>
+        <v>122399660</v>
       </c>
       <c r="B75" t="n">
         <v>94857</v>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649950</v>
+        <v>649992</v>
       </c>
       <c r="R75" t="n">
-        <v>6674175</v>
+        <v>6674192</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9618,14 +9618,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399655</v>
+        <v>122399645</v>
       </c>
       <c r="B76" t="n">
-        <v>94761</v>
+        <v>57753</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9634,27 +9634,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2818</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>649962</v>
+        <v>649902</v>
       </c>
       <c r="R76" t="n">
-        <v>6674201</v>
+        <v>6674271</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9730,18 +9730,22 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122399645</v>
+        <v>122399655</v>
       </c>
       <c r="B77" t="n">
-        <v>57753</v>
+        <v>94761</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9750,27 +9754,27 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>2818</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9778,10 +9782,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>649902</v>
+        <v>649962</v>
       </c>
       <c r="R77" t="n">
-        <v>6674271</v>
+        <v>6674201</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9813,7 +9817,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9823,7 +9827,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9846,11 +9850,7 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399633</v>
+        <v>122399632</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650328</v>
+        <v>650256</v>
       </c>
       <c r="R2" t="n">
-        <v>6673703</v>
+        <v>6673700</v>
       </c>
       <c r="S2" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399670</v>
+        <v>122399644</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>57754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,39 +811,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650313</v>
+        <v>650328</v>
       </c>
       <c r="R3" t="n">
-        <v>6673680</v>
+        <v>6673703</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399630</v>
+        <v>122399667</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,36 +931,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650217</v>
+        <v>650365</v>
       </c>
       <c r="R4" t="n">
-        <v>6673709</v>
+        <v>6673701</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1007,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399668</v>
+        <v>122399626</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,39 +1055,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1096,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650331</v>
+        <v>650382</v>
       </c>
       <c r="R5" t="n">
-        <v>6673701</v>
+        <v>6673643</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1131,7 +1127,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1137,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399666</v>
+        <v>122399668</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,10 +1199,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1221,10 +1216,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650369</v>
+        <v>650331</v>
       </c>
       <c r="R6" t="n">
-        <v>6673665</v>
+        <v>6673701</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1256,7 +1251,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,12 +1261,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst!</t>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399671</v>
+        <v>122399630</v>
       </c>
       <c r="B7" t="n">
-        <v>100506</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,27 +1309,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650309</v>
+        <v>650217</v>
       </c>
       <c r="R7" t="n">
-        <v>6673789</v>
+        <v>6673709</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399652</v>
+        <v>122399666</v>
       </c>
       <c r="B8" t="n">
-        <v>90833</v>
+        <v>98241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,30 +1426,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1457,13 +1462,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650328</v>
+        <v>650369</v>
       </c>
       <c r="R8" t="n">
-        <v>6673703</v>
+        <v>6673665</v>
       </c>
       <c r="S8" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1492,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1507,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399627</v>
+        <v>122399633</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,20 +1551,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1562,13 +1572,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1578,13 +1591,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650420</v>
+        <v>650328</v>
       </c>
       <c r="R9" t="n">
-        <v>6673617</v>
+        <v>6673703</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1613,7 +1626,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1623,7 +1636,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399632</v>
+        <v>122399652</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>90834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,35 +1679,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1702,13 +1706,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650256</v>
+        <v>650328</v>
       </c>
       <c r="R10" t="n">
-        <v>6673700</v>
+        <v>6673703</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1747,7 +1751,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1895,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399626</v>
+        <v>122399670</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>98241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,36 +1911,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1944,10 +1951,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650382</v>
+        <v>650313</v>
       </c>
       <c r="R12" t="n">
-        <v>6673643</v>
+        <v>6673680</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1979,7 +1986,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1989,7 +1996,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,10 +2023,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399667</v>
+        <v>122399627</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,39 +2035,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2068,10 +2072,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650365</v>
+        <v>650420</v>
       </c>
       <c r="R13" t="n">
-        <v>6673701</v>
+        <v>6673617</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2113,7 +2117,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399644</v>
+        <v>122399671</v>
       </c>
       <c r="B14" t="n">
-        <v>57753</v>
+        <v>100507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2156,31 +2160,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650328</v>
+        <v>650309</v>
       </c>
       <c r="R14" t="n">
-        <v>6673703</v>
+        <v>6673789</v>
       </c>
       <c r="S14" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,7 +2263,7 @@
         <v>122399676</v>
       </c>
       <c r="B15" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384439</v>
+        <v>122384395</v>
       </c>
       <c r="B16" t="n">
-        <v>80613</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2400,26 +2400,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2427,10 +2436,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650238</v>
+        <v>650395</v>
       </c>
       <c r="R16" t="n">
-        <v>6674074</v>
+        <v>6674254</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2462,7 +2471,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,12 +2481,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2504,10 +2508,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384438</v>
+        <v>122384369</v>
       </c>
       <c r="B17" t="n">
-        <v>80613</v>
+        <v>57400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2520,37 +2524,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650353</v>
+        <v>650395</v>
       </c>
       <c r="R17" t="n">
-        <v>6674235</v>
+        <v>6674349</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2582,7 +2595,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2592,12 +2605,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2624,10 +2632,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384406</v>
+        <v>122384437</v>
       </c>
       <c r="B18" t="n">
-        <v>57399</v>
+        <v>80614</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2640,35 +2648,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2676,10 +2675,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650115</v>
+        <v>650387</v>
       </c>
       <c r="R18" t="n">
-        <v>6674245</v>
+        <v>6674259</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2711,7 +2710,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2721,7 +2720,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2748,10 +2747,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384466</v>
+        <v>122384440</v>
       </c>
       <c r="B19" t="n">
-        <v>91234</v>
+        <v>80614</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2760,25 +2759,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4217</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2787,14 +2786,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650393</v>
+        <v>650077</v>
       </c>
       <c r="R19" t="n">
-        <v>6674366</v>
+        <v>6674268</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2826,7 +2825,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2836,7 +2835,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2845,24 +2844,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2879,10 +2862,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384470</v>
+        <v>122384439</v>
       </c>
       <c r="B20" t="n">
-        <v>91278</v>
+        <v>80614</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2891,25 +2874,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2918,14 +2901,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650388</v>
+        <v>650238</v>
       </c>
       <c r="R20" t="n">
-        <v>6674308</v>
+        <v>6674074</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2957,7 +2940,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2967,7 +2950,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2994,10 +2982,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384454</v>
+        <v>122384462</v>
       </c>
       <c r="B21" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3037,10 +3025,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650440</v>
+        <v>650428</v>
       </c>
       <c r="R21" t="n">
-        <v>6674369</v>
+        <v>6674388</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3072,7 +3060,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3082,7 +3070,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3109,10 +3097,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384434</v>
+        <v>122384404</v>
       </c>
       <c r="B22" t="n">
-        <v>74696</v>
+        <v>57400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3121,41 +3109,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650407</v>
+        <v>650195</v>
       </c>
       <c r="R22" t="n">
-        <v>6674363</v>
+        <v>6674100</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3187,7 +3184,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3197,7 +3194,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3224,10 +3221,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384411</v>
+        <v>122384366</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3272,14 +3269,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650415</v>
+        <v>650419</v>
       </c>
       <c r="R23" t="n">
-        <v>6674083</v>
+        <v>6674371</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3311,7 +3308,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3321,7 +3318,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3348,10 +3345,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384394</v>
+        <v>122384403</v>
       </c>
       <c r="B24" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3390,7 +3387,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3400,10 +3397,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650394</v>
+        <v>650237</v>
       </c>
       <c r="R24" t="n">
-        <v>6674272</v>
+        <v>6674049</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3435,7 +3432,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3445,7 +3442,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3472,10 +3469,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384412</v>
+        <v>122384472</v>
       </c>
       <c r="B25" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3484,50 +3481,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650399</v>
+        <v>650415</v>
       </c>
       <c r="R25" t="n">
-        <v>6674181</v>
+        <v>6674360</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3559,7 +3556,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3569,7 +3566,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3596,10 +3593,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384397</v>
+        <v>122384411</v>
       </c>
       <c r="B26" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3638,7 +3635,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3648,10 +3645,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650406</v>
+        <v>650415</v>
       </c>
       <c r="R26" t="n">
-        <v>6674220</v>
+        <v>6674083</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3683,7 +3680,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3693,7 +3690,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3720,10 +3717,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384487</v>
+        <v>122384388</v>
       </c>
       <c r="B27" t="n">
-        <v>105346</v>
+        <v>57400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3732,31 +3729,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3764,10 +3769,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650442</v>
+        <v>650400</v>
       </c>
       <c r="R27" t="n">
-        <v>6674345</v>
+        <v>6674425</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3799,7 +3804,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3809,7 +3814,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3836,10 +3841,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384442</v>
+        <v>122384436</v>
       </c>
       <c r="B28" t="n">
-        <v>90798</v>
+        <v>80614</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3848,25 +3853,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3875,14 +3880,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650393</v>
+        <v>650363</v>
       </c>
       <c r="R28" t="n">
-        <v>6674157</v>
+        <v>6674334</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3914,7 +3919,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3924,7 +3929,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3951,10 +3956,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384440</v>
+        <v>122384391</v>
       </c>
       <c r="B29" t="n">
-        <v>80613</v>
+        <v>57400</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3967,37 +3972,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650077</v>
+        <v>650364</v>
       </c>
       <c r="R29" t="n">
-        <v>6674268</v>
+        <v>6674383</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4029,7 +4043,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4039,7 +4053,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4066,10 +4080,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384404</v>
+        <v>122384397</v>
       </c>
       <c r="B30" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4108,7 +4122,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4118,10 +4132,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650195</v>
+        <v>650406</v>
       </c>
       <c r="R30" t="n">
-        <v>6674100</v>
+        <v>6674220</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4153,7 +4167,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4163,7 +4177,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4190,10 +4204,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384477</v>
+        <v>122384400</v>
       </c>
       <c r="B31" t="n">
-        <v>98240</v>
+        <v>57400</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4202,39 +4216,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4242,10 +4256,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650415</v>
+        <v>650362</v>
       </c>
       <c r="R31" t="n">
-        <v>6674216</v>
+        <v>6674082</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4277,7 +4291,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4287,7 +4301,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4314,10 +4328,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384473</v>
+        <v>122384417</v>
       </c>
       <c r="B32" t="n">
-        <v>98240</v>
+        <v>57537</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4326,39 +4340,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4366,13 +4380,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650400</v>
+        <v>650385</v>
       </c>
       <c r="R32" t="n">
-        <v>6674415</v>
+        <v>6674365</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4401,7 +4415,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4411,7 +4425,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4438,10 +4457,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384480</v>
+        <v>122384371</v>
       </c>
       <c r="B33" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4450,31 +4469,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4482,13 +4509,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650316</v>
+        <v>650400</v>
       </c>
       <c r="R33" t="n">
-        <v>6674034</v>
+        <v>6674206</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4517,7 +4544,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4527,7 +4554,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4554,10 +4581,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384366</v>
+        <v>122384443</v>
       </c>
       <c r="B34" t="n">
-        <v>57399</v>
+        <v>90834</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4570,35 +4597,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4606,10 +4624,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650419</v>
+        <v>650438</v>
       </c>
       <c r="R34" t="n">
-        <v>6674371</v>
+        <v>6674347</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4641,7 +4659,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4651,7 +4669,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4678,10 +4696,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384417</v>
+        <v>122384466</v>
       </c>
       <c r="B35" t="n">
-        <v>57536</v>
+        <v>91235</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4690,39 +4708,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>4217</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4730,13 +4739,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650385</v>
+        <v>650393</v>
       </c>
       <c r="R35" t="n">
-        <v>6674365</v>
+        <v>6674366</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4765,7 +4774,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4784,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4789,8 +4793,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4807,10 +4827,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384483</v>
+        <v>122384394</v>
       </c>
       <c r="B36" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4819,31 +4839,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4851,10 +4879,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650238</v>
+        <v>650394</v>
       </c>
       <c r="R36" t="n">
-        <v>6674076</v>
+        <v>6674272</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4886,7 +4914,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4896,7 +4924,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4923,10 +4951,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384410</v>
+        <v>122384470</v>
       </c>
       <c r="B37" t="n">
-        <v>57399</v>
+        <v>91279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4935,50 +4963,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650147</v>
+        <v>650388</v>
       </c>
       <c r="R37" t="n">
-        <v>6674088</v>
+        <v>6674308</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5010,7 +5029,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5020,7 +5039,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5047,10 +5066,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384403</v>
+        <v>122384476</v>
       </c>
       <c r="B38" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5059,39 +5078,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5099,10 +5118,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650237</v>
+        <v>650396</v>
       </c>
       <c r="R38" t="n">
-        <v>6674049</v>
+        <v>6674252</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5134,7 +5153,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5144,7 +5163,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5171,10 +5190,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384391</v>
+        <v>122384432</v>
       </c>
       <c r="B39" t="n">
-        <v>57399</v>
+        <v>74697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5183,39 +5202,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5223,10 +5233,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650364</v>
+        <v>650422</v>
       </c>
       <c r="R39" t="n">
-        <v>6674383</v>
+        <v>6674376</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5258,7 +5268,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5268,7 +5278,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5277,8 +5287,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5295,10 +5321,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384479</v>
+        <v>122384410</v>
       </c>
       <c r="B40" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5307,42 +5333,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650415</v>
+        <v>650147</v>
       </c>
       <c r="R40" t="n">
-        <v>6674370</v>
+        <v>6674088</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5374,7 +5408,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5384,7 +5418,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5411,10 +5445,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384432</v>
+        <v>122384373</v>
       </c>
       <c r="B41" t="n">
-        <v>74696</v>
+        <v>57400</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5423,30 +5457,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5454,10 +5497,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650422</v>
+        <v>650373</v>
       </c>
       <c r="R41" t="n">
-        <v>6674376</v>
+        <v>6674389</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5489,7 +5532,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5499,7 +5542,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5508,24 +5551,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5542,10 +5569,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384443</v>
+        <v>122384481</v>
       </c>
       <c r="B42" t="n">
-        <v>90833</v>
+        <v>100507</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5554,41 +5581,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650438</v>
+        <v>650230</v>
       </c>
       <c r="R42" t="n">
-        <v>6674347</v>
+        <v>6674064</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5620,7 +5648,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5630,7 +5658,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5657,10 +5685,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384395</v>
+        <v>122384406</v>
       </c>
       <c r="B43" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5699,7 +5727,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5709,10 +5737,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650395</v>
+        <v>650115</v>
       </c>
       <c r="R43" t="n">
-        <v>6674254</v>
+        <v>6674245</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5744,7 +5772,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5754,7 +5782,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5781,10 +5809,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384371</v>
+        <v>122384407</v>
       </c>
       <c r="B44" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5823,7 +5851,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5833,13 +5861,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650400</v>
+        <v>650101</v>
       </c>
       <c r="R44" t="n">
-        <v>6674206</v>
+        <v>6674120</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5868,7 +5896,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5878,7 +5906,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5905,10 +5933,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384465</v>
+        <v>122384487</v>
       </c>
       <c r="B45" t="n">
-        <v>91124</v>
+        <v>105347</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5917,30 +5945,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5948,10 +5977,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650436</v>
+        <v>650442</v>
       </c>
       <c r="R45" t="n">
-        <v>6674342</v>
+        <v>6674345</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5983,7 +6012,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5993,7 +6022,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6020,10 +6049,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384373</v>
+        <v>122384479</v>
       </c>
       <c r="B46" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6032,39 +6061,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6072,10 +6093,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650373</v>
+        <v>650415</v>
       </c>
       <c r="R46" t="n">
-        <v>6674389</v>
+        <v>6674370</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6107,7 +6128,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6117,7 +6138,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6144,10 +6165,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384472</v>
+        <v>122384465</v>
       </c>
       <c r="B47" t="n">
-        <v>98240</v>
+        <v>91125</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6156,39 +6177,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6196,10 +6208,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650415</v>
+        <v>650436</v>
       </c>
       <c r="R47" t="n">
-        <v>6674360</v>
+        <v>6674342</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6231,7 +6243,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6241,7 +6253,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6268,10 +6280,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384402</v>
+        <v>122384468</v>
       </c>
       <c r="B48" t="n">
-        <v>57399</v>
+        <v>91279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6280,50 +6292,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650297</v>
+        <v>650436</v>
       </c>
       <c r="R48" t="n">
-        <v>6674040</v>
+        <v>6674345</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6355,7 +6358,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6365,7 +6368,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6374,8 +6382,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6392,10 +6416,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384369</v>
+        <v>122384434</v>
       </c>
       <c r="B49" t="n">
-        <v>57399</v>
+        <v>74697</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6404,39 +6428,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6444,10 +6459,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650395</v>
+        <v>650407</v>
       </c>
       <c r="R49" t="n">
-        <v>6674349</v>
+        <v>6674363</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6479,7 +6494,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6489,7 +6504,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6516,10 +6531,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384476</v>
+        <v>122384485</v>
       </c>
       <c r="B50" t="n">
-        <v>98240</v>
+        <v>100507</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6528,37 +6543,29 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -6568,10 +6575,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650396</v>
+        <v>650432</v>
       </c>
       <c r="R50" t="n">
-        <v>6674252</v>
+        <v>6674247</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6603,7 +6610,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6613,7 +6620,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6640,10 +6647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384484</v>
+        <v>122384454</v>
       </c>
       <c r="B51" t="n">
-        <v>100506</v>
+        <v>90834</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6652,42 +6659,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650407</v>
+        <v>650440</v>
       </c>
       <c r="R51" t="n">
-        <v>6674068</v>
+        <v>6674369</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6719,7 +6725,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6729,7 +6735,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6756,10 +6762,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384485</v>
+        <v>122384464</v>
       </c>
       <c r="B52" t="n">
-        <v>100506</v>
+        <v>90834</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6768,31 +6774,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6800,10 +6805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650432</v>
+        <v>650429</v>
       </c>
       <c r="R52" t="n">
-        <v>6674247</v>
+        <v>6674188</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6835,7 +6840,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6845,7 +6850,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6872,10 +6877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384468</v>
+        <v>122384402</v>
       </c>
       <c r="B53" t="n">
-        <v>91278</v>
+        <v>57400</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6884,41 +6889,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650436</v>
+        <v>650297</v>
       </c>
       <c r="R53" t="n">
-        <v>6674345</v>
+        <v>6674040</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6950,7 +6964,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6960,12 +6974,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6974,24 +6983,8 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7008,10 +7001,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384464</v>
+        <v>122384412</v>
       </c>
       <c r="B54" t="n">
-        <v>90833</v>
+        <v>57400</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7024,26 +7017,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7051,10 +7053,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650429</v>
+        <v>650399</v>
       </c>
       <c r="R54" t="n">
-        <v>6674188</v>
+        <v>6674181</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7086,7 +7088,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7096,7 +7098,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7123,10 +7125,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384400</v>
+        <v>122384442</v>
       </c>
       <c r="B55" t="n">
-        <v>57399</v>
+        <v>90799</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7135,39 +7137,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7175,10 +7168,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650362</v>
+        <v>650393</v>
       </c>
       <c r="R55" t="n">
-        <v>6674082</v>
+        <v>6674157</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7210,7 +7203,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7220,7 +7213,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7247,10 +7240,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384462</v>
+        <v>122384438</v>
       </c>
       <c r="B56" t="n">
-        <v>90833</v>
+        <v>80614</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7263,21 +7256,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7286,14 +7279,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650428</v>
+        <v>650353</v>
       </c>
       <c r="R56" t="n">
-        <v>6674388</v>
+        <v>6674235</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7325,7 +7318,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7335,7 +7328,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7362,10 +7360,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384481</v>
+        <v>122384483</v>
       </c>
       <c r="B57" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7406,10 +7404,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650230</v>
+        <v>650238</v>
       </c>
       <c r="R57" t="n">
-        <v>6674064</v>
+        <v>6674076</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7441,7 +7439,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7451,7 +7449,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7478,10 +7476,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384437</v>
+        <v>122384477</v>
       </c>
       <c r="B58" t="n">
-        <v>80613</v>
+        <v>98241</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7490,30 +7488,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7521,10 +7528,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650387</v>
+        <v>650415</v>
       </c>
       <c r="R58" t="n">
-        <v>6674259</v>
+        <v>6674216</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7556,7 +7563,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7566,7 +7573,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7593,10 +7600,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384436</v>
+        <v>122384484</v>
       </c>
       <c r="B59" t="n">
-        <v>80613</v>
+        <v>100507</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7605,41 +7612,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650363</v>
+        <v>650407</v>
       </c>
       <c r="R59" t="n">
-        <v>6674334</v>
+        <v>6674068</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7671,7 +7679,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7681,7 +7689,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7708,10 +7716,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384407</v>
+        <v>122384473</v>
       </c>
       <c r="B60" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7720,50 +7728,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650101</v>
+        <v>650400</v>
       </c>
       <c r="R60" t="n">
-        <v>6674120</v>
+        <v>6674415</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7795,7 +7803,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7805,7 +7813,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7832,10 +7840,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384388</v>
+        <v>122384480</v>
       </c>
       <c r="B61" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7844,50 +7852,42 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650400</v>
+        <v>650316</v>
       </c>
       <c r="R61" t="n">
-        <v>6674425</v>
+        <v>6674034</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,10 +7956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399650</v>
+        <v>122399656</v>
       </c>
       <c r="B62" t="n">
-        <v>90798</v>
+        <v>94762</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7972,26 +7972,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7999,10 +8000,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>650386</v>
+        <v>649935</v>
       </c>
       <c r="R62" t="n">
-        <v>6673912</v>
+        <v>6674249</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8034,7 +8035,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8044,7 +8045,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8071,10 +8072,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399673</v>
+        <v>122399637</v>
       </c>
       <c r="B63" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8083,31 +8084,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8115,10 +8124,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>650321</v>
+        <v>649994</v>
       </c>
       <c r="R63" t="n">
-        <v>6673981</v>
+        <v>6674118</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8150,7 +8159,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8160,7 +8169,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8187,10 +8196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399672</v>
+        <v>122399640</v>
       </c>
       <c r="B64" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8199,31 +8208,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8231,10 +8248,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650329</v>
+        <v>650059</v>
       </c>
       <c r="R64" t="n">
-        <v>6673994</v>
+        <v>6674144</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8266,7 +8283,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8276,7 +8293,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8303,10 +8320,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399656</v>
+        <v>122399639</v>
       </c>
       <c r="B65" t="n">
-        <v>94761</v>
+        <v>57400</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8315,31 +8332,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8347,10 +8372,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649935</v>
+        <v>650031</v>
       </c>
       <c r="R65" t="n">
-        <v>6674249</v>
+        <v>6674158</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8382,7 +8407,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8392,7 +8417,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8419,10 +8444,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399641</v>
+        <v>122399649</v>
       </c>
       <c r="B66" t="n">
-        <v>57399</v>
+        <v>80614</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8435,35 +8460,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8471,10 +8487,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>650092</v>
+        <v>650383</v>
       </c>
       <c r="R66" t="n">
-        <v>6674138</v>
+        <v>6673928</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8506,7 +8522,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8516,7 +8532,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8546,7 +8562,7 @@
         <v>122399675</v>
       </c>
       <c r="B67" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8659,10 +8675,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399649</v>
+        <v>122399673</v>
       </c>
       <c r="B68" t="n">
-        <v>80613</v>
+        <v>100507</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8671,30 +8687,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8702,10 +8719,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650383</v>
+        <v>650321</v>
       </c>
       <c r="R68" t="n">
-        <v>6673928</v>
+        <v>6673981</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8737,7 +8754,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8747,7 +8764,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8774,10 +8791,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399639</v>
+        <v>122399672</v>
       </c>
       <c r="B69" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8786,39 +8803,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8826,10 +8835,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650031</v>
+        <v>650329</v>
       </c>
       <c r="R69" t="n">
-        <v>6674158</v>
+        <v>6673994</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8861,7 +8870,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8871,7 +8880,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8898,10 +8907,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399640</v>
+        <v>122399658</v>
       </c>
       <c r="B70" t="n">
-        <v>57399</v>
+        <v>94858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8910,39 +8919,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8950,10 +8951,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>650059</v>
+        <v>649956</v>
       </c>
       <c r="R70" t="n">
-        <v>6674144</v>
+        <v>6674194</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8985,7 +8986,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8995,7 +8996,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9025,7 +9026,7 @@
         <v>122399642</v>
       </c>
       <c r="B71" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9146,10 +9147,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399637</v>
+        <v>122399641</v>
       </c>
       <c r="B72" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9188,7 +9189,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9198,10 +9199,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>649994</v>
+        <v>650092</v>
       </c>
       <c r="R72" t="n">
-        <v>6674118</v>
+        <v>6674138</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9233,7 +9234,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9243,7 +9244,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9270,10 +9271,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399658</v>
+        <v>122399650</v>
       </c>
       <c r="B73" t="n">
-        <v>94857</v>
+        <v>90799</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9286,27 +9287,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>649956</v>
+        <v>650386</v>
       </c>
       <c r="R73" t="n">
-        <v>6674194</v>
+        <v>6673912</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9386,10 +9386,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122399657</v>
+        <v>122399660</v>
       </c>
       <c r="B74" t="n">
-        <v>94857</v>
+        <v>94858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649950</v>
+        <v>649992</v>
       </c>
       <c r="R74" t="n">
-        <v>6674175</v>
+        <v>6674192</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9502,10 +9502,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399660</v>
+        <v>122399657</v>
       </c>
       <c r="B75" t="n">
-        <v>94857</v>
+        <v>94858</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649992</v>
+        <v>649950</v>
       </c>
       <c r="R75" t="n">
-        <v>6674192</v>
+        <v>6674175</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9621,7 +9621,7 @@
         <v>122399645</v>
       </c>
       <c r="B76" t="n">
-        <v>57753</v>
+        <v>57754</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>122399655</v>
       </c>
       <c r="B77" t="n">
-        <v>94761</v>
+        <v>94762</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -1899,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399670</v>
+        <v>122399627</v>
       </c>
       <c r="B12" t="n">
-        <v>98241</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,39 +1911,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1951,10 +1948,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650313</v>
+        <v>650420</v>
       </c>
       <c r="R12" t="n">
-        <v>6673680</v>
+        <v>6673617</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1986,7 +1983,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1996,7 +1993,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399627</v>
+        <v>122399670</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>98241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2035,36 +2032,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650420</v>
+        <v>650313</v>
       </c>
       <c r="R13" t="n">
-        <v>6673617</v>
+        <v>6673680</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2862,10 +2862,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384439</v>
+        <v>122384366</v>
       </c>
       <c r="B20" t="n">
-        <v>80614</v>
+        <v>57400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2878,37 +2878,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650238</v>
+        <v>650419</v>
       </c>
       <c r="R20" t="n">
-        <v>6674074</v>
+        <v>6674371</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2940,7 +2949,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2950,12 +2959,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2982,10 +2986,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384462</v>
+        <v>122384404</v>
       </c>
       <c r="B21" t="n">
-        <v>90834</v>
+        <v>57400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2998,37 +3002,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650428</v>
+        <v>650195</v>
       </c>
       <c r="R21" t="n">
-        <v>6674388</v>
+        <v>6674100</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3060,7 +3073,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3070,7 +3083,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3097,10 +3110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384404</v>
+        <v>122384439</v>
       </c>
       <c r="B22" t="n">
-        <v>57400</v>
+        <v>80614</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3113,35 +3126,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3149,10 +3153,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650195</v>
+        <v>650238</v>
       </c>
       <c r="R22" t="n">
-        <v>6674100</v>
+        <v>6674074</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3184,7 +3188,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3194,7 +3198,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3221,10 +3230,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384366</v>
+        <v>122384462</v>
       </c>
       <c r="B23" t="n">
-        <v>57400</v>
+        <v>90834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3237,35 +3246,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650419</v>
+        <v>650428</v>
       </c>
       <c r="R23" t="n">
-        <v>6674371</v>
+        <v>6674388</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399632</v>
+        <v>122399671</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650256</v>
+        <v>650309</v>
       </c>
       <c r="R2" t="n">
-        <v>6673700</v>
+        <v>6673789</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399644</v>
+        <v>122399632</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +803,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,7 +831,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650328</v>
+        <v>650256</v>
       </c>
       <c r="R3" t="n">
-        <v>6673703</v>
+        <v>6673700</v>
       </c>
       <c r="S3" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399667</v>
+        <v>122399652</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>90837</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650365</v>
+        <v>650328</v>
       </c>
       <c r="R4" t="n">
-        <v>6673701</v>
+        <v>6673703</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399626</v>
+        <v>122399633</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,34 +1042,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1092,13 +1082,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650382</v>
+        <v>650328</v>
       </c>
       <c r="R5" t="n">
-        <v>6673643</v>
+        <v>6673703</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399668</v>
+        <v>122399670</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,7 +1189,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1216,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650331</v>
+        <v>650313</v>
       </c>
       <c r="R6" t="n">
-        <v>6673701</v>
+        <v>6673680</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1251,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1261,12 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399630</v>
+        <v>122399644</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>57754</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,16 +1294,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1326,15 +1311,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1342,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650217</v>
+        <v>650328</v>
       </c>
       <c r="R7" t="n">
-        <v>6673709</v>
+        <v>6673703</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1377,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1387,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,7 +1401,7 @@
         <v>122399666</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1539,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399633</v>
+        <v>122399668</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,39 +1535,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1591,13 +1575,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650328</v>
+        <v>650331</v>
       </c>
       <c r="R9" t="n">
-        <v>6673703</v>
+        <v>6673701</v>
       </c>
       <c r="S9" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1626,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1636,7 +1620,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,10 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399652</v>
+        <v>122399667</v>
       </c>
       <c r="B10" t="n">
-        <v>90834</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,30 +1664,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1706,13 +1704,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650328</v>
+        <v>650365</v>
       </c>
       <c r="R10" t="n">
-        <v>6673703</v>
+        <v>6673701</v>
       </c>
       <c r="S10" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1741,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1751,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,7 +1776,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399628</v>
+        <v>122399627</v>
       </c>
       <c r="B11" t="n">
         <v>5193</v>
@@ -1827,10 +1825,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650379</v>
+        <v>650420</v>
       </c>
       <c r="R11" t="n">
-        <v>6673641</v>
+        <v>6673617</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1862,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1872,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,10 +1897,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399627</v>
+        <v>122399626</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1915,21 +1913,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1948,10 +1946,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650420</v>
+        <v>650382</v>
       </c>
       <c r="R12" t="n">
-        <v>6673617</v>
+        <v>6673643</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1983,7 +1981,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1993,7 +1991,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,10 +2018,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122399670</v>
+        <v>122399628</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,39 +2030,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2072,10 +2067,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650313</v>
+        <v>650379</v>
       </c>
       <c r="R13" t="n">
-        <v>6673680</v>
+        <v>6673641</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2107,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399671</v>
+        <v>122399630</v>
       </c>
       <c r="B14" t="n">
-        <v>100507</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,27 +2155,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650309</v>
+        <v>650217</v>
       </c>
       <c r="R14" t="n">
-        <v>6673789</v>
+        <v>6673709</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,7 +2263,7 @@
         <v>122399676</v>
       </c>
       <c r="B15" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384395</v>
+        <v>122384477</v>
       </c>
       <c r="B16" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,39 +2396,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650395</v>
+        <v>650415</v>
       </c>
       <c r="R16" t="n">
-        <v>6674254</v>
+        <v>6674216</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,10 +2508,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384369</v>
+        <v>122384454</v>
       </c>
       <c r="B17" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2524,35 +2524,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2560,10 +2551,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650395</v>
+        <v>650440</v>
       </c>
       <c r="R17" t="n">
-        <v>6674349</v>
+        <v>6674369</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2595,7 +2586,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2605,7 +2596,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2632,10 +2623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384437</v>
+        <v>122384373</v>
       </c>
       <c r="B18" t="n">
-        <v>80614</v>
+        <v>57400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2648,37 +2639,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650387</v>
+        <v>650373</v>
       </c>
       <c r="R18" t="n">
-        <v>6674259</v>
+        <v>6674389</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384440</v>
+        <v>122384369</v>
       </c>
       <c r="B19" t="n">
-        <v>80614</v>
+        <v>57400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2763,37 +2763,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650077</v>
+        <v>650395</v>
       </c>
       <c r="R19" t="n">
-        <v>6674268</v>
+        <v>6674349</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2825,7 +2834,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2835,7 +2844,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2862,10 +2871,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384366</v>
+        <v>122384417</v>
       </c>
       <c r="B20" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2878,21 +2887,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2904,7 +2913,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2914,13 +2923,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650419</v>
+        <v>650385</v>
       </c>
       <c r="R20" t="n">
-        <v>6674371</v>
+        <v>6674365</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2949,7 +2958,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2959,7 +2968,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2986,10 +3000,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384404</v>
+        <v>122384443</v>
       </c>
       <c r="B21" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3002,46 +3016,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650195</v>
+        <v>650438</v>
       </c>
       <c r="R21" t="n">
-        <v>6674100</v>
+        <v>6674347</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3073,7 +3078,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3083,7 +3088,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,10 +3115,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384439</v>
+        <v>122384465</v>
       </c>
       <c r="B22" t="n">
-        <v>80614</v>
+        <v>91128</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3126,21 +3131,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3149,14 +3154,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650238</v>
+        <v>650436</v>
       </c>
       <c r="R22" t="n">
-        <v>6674074</v>
+        <v>6674342</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3188,7 +3193,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3198,12 +3203,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3230,10 +3230,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384462</v>
+        <v>122384440</v>
       </c>
       <c r="B23" t="n">
-        <v>90834</v>
+        <v>80617</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3269,14 +3269,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650428</v>
+        <v>650077</v>
       </c>
       <c r="R23" t="n">
-        <v>6674388</v>
+        <v>6674268</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384403</v>
+        <v>122384476</v>
       </c>
       <c r="B24" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3357,39 +3357,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650237</v>
+        <v>650396</v>
       </c>
       <c r="R24" t="n">
-        <v>6674049</v>
+        <v>6674252</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3469,10 +3469,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384472</v>
+        <v>122384432</v>
       </c>
       <c r="B25" t="n">
-        <v>98241</v>
+        <v>74700</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3481,39 +3481,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3521,10 +3512,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650415</v>
+        <v>650422</v>
       </c>
       <c r="R25" t="n">
-        <v>6674360</v>
+        <v>6674376</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3556,7 +3547,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3566,7 +3557,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3575,8 +3566,24 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3593,10 +3600,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384411</v>
+        <v>122384434</v>
       </c>
       <c r="B26" t="n">
-        <v>57400</v>
+        <v>74700</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3605,50 +3612,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650415</v>
+        <v>650407</v>
       </c>
       <c r="R26" t="n">
-        <v>6674083</v>
+        <v>6674363</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3680,7 +3678,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3690,7 +3688,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3717,7 +3715,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384388</v>
+        <v>122384391</v>
       </c>
       <c r="B27" t="n">
         <v>57400</v>
@@ -3759,7 +3757,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3769,10 +3767,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650400</v>
+        <v>650364</v>
       </c>
       <c r="R27" t="n">
-        <v>6674425</v>
+        <v>6674383</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3804,7 +3802,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3814,7 +3812,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3841,10 +3839,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384436</v>
+        <v>122384483</v>
       </c>
       <c r="B28" t="n">
-        <v>80614</v>
+        <v>100510</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3853,41 +3851,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650363</v>
+        <v>650238</v>
       </c>
       <c r="R28" t="n">
-        <v>6674334</v>
+        <v>6674076</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3919,7 +3918,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3929,7 +3928,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3956,10 +3955,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384391</v>
+        <v>122384468</v>
       </c>
       <c r="B29" t="n">
-        <v>57400</v>
+        <v>91282</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3968,39 +3967,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4008,10 +3998,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650364</v>
+        <v>650436</v>
       </c>
       <c r="R29" t="n">
-        <v>6674383</v>
+        <v>6674345</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4043,7 +4033,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4053,7 +4043,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4062,8 +4057,24 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4080,10 +4091,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384397</v>
+        <v>122384438</v>
       </c>
       <c r="B30" t="n">
-        <v>57400</v>
+        <v>80617</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4096,35 +4107,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4132,10 +4134,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650406</v>
+        <v>650353</v>
       </c>
       <c r="R30" t="n">
-        <v>6674220</v>
+        <v>6674235</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4167,7 +4169,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4177,7 +4179,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4204,10 +4211,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384400</v>
+        <v>122384484</v>
       </c>
       <c r="B31" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4216,39 +4223,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4256,10 +4255,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650362</v>
+        <v>650407</v>
       </c>
       <c r="R31" t="n">
-        <v>6674082</v>
+        <v>6674068</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4291,7 +4290,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4301,7 +4300,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4328,10 +4327,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384417</v>
+        <v>122384403</v>
       </c>
       <c r="B32" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4344,21 +4343,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4370,23 +4369,23 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650385</v>
+        <v>650237</v>
       </c>
       <c r="R32" t="n">
-        <v>6674365</v>
+        <v>6674049</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4415,7 +4414,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4425,12 +4424,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4457,7 +4451,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384371</v>
+        <v>122384410</v>
       </c>
       <c r="B33" t="n">
         <v>57400</v>
@@ -4499,7 +4493,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4509,13 +4503,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650400</v>
+        <v>650147</v>
       </c>
       <c r="R33" t="n">
-        <v>6674206</v>
+        <v>6674088</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4544,7 +4538,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4554,7 +4548,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4581,10 +4575,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384443</v>
+        <v>122384481</v>
       </c>
       <c r="B34" t="n">
-        <v>90834</v>
+        <v>100510</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4593,41 +4587,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650438</v>
+        <v>650230</v>
       </c>
       <c r="R34" t="n">
-        <v>6674347</v>
+        <v>6674064</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4659,7 +4654,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4669,7 +4664,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4696,10 +4691,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384466</v>
+        <v>122384412</v>
       </c>
       <c r="B35" t="n">
-        <v>91235</v>
+        <v>57400</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4708,41 +4703,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650393</v>
+        <v>650399</v>
       </c>
       <c r="R35" t="n">
-        <v>6674366</v>
+        <v>6674181</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4774,7 +4778,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4784,7 +4788,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4793,24 +4797,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4827,7 +4815,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384394</v>
+        <v>122384402</v>
       </c>
       <c r="B36" t="n">
         <v>57400</v>
@@ -4879,10 +4867,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650394</v>
+        <v>650297</v>
       </c>
       <c r="R36" t="n">
-        <v>6674272</v>
+        <v>6674040</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4914,7 +4902,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4924,7 +4912,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4951,10 +4939,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384470</v>
+        <v>122384388</v>
       </c>
       <c r="B37" t="n">
-        <v>91279</v>
+        <v>57400</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4963,30 +4951,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4994,10 +4991,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650388</v>
+        <v>650400</v>
       </c>
       <c r="R37" t="n">
-        <v>6674308</v>
+        <v>6674425</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5029,7 +5026,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5039,7 +5036,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5066,10 +5063,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384476</v>
+        <v>122384406</v>
       </c>
       <c r="B38" t="n">
-        <v>98241</v>
+        <v>57400</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5078,39 +5075,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5118,10 +5115,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650396</v>
+        <v>650115</v>
       </c>
       <c r="R38" t="n">
-        <v>6674252</v>
+        <v>6674245</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5153,7 +5150,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5163,7 +5160,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5190,10 +5187,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384432</v>
+        <v>122384404</v>
       </c>
       <c r="B39" t="n">
-        <v>74697</v>
+        <v>57400</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5202,41 +5199,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650422</v>
+        <v>650195</v>
       </c>
       <c r="R39" t="n">
-        <v>6674376</v>
+        <v>6674100</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5268,7 +5274,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5278,7 +5284,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5287,24 +5293,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5321,7 +5311,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384410</v>
+        <v>122384371</v>
       </c>
       <c r="B40" t="n">
         <v>57400</v>
@@ -5363,7 +5353,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5373,13 +5363,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650147</v>
+        <v>650400</v>
       </c>
       <c r="R40" t="n">
-        <v>6674088</v>
+        <v>6674206</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5408,7 +5398,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5418,7 +5408,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5445,10 +5435,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384373</v>
+        <v>122384462</v>
       </c>
       <c r="B41" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5461,35 +5451,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5497,10 +5478,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650373</v>
+        <v>650428</v>
       </c>
       <c r="R41" t="n">
-        <v>6674389</v>
+        <v>6674388</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5532,7 +5513,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5542,7 +5523,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5569,10 +5550,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384481</v>
+        <v>122384395</v>
       </c>
       <c r="B42" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5581,31 +5562,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5613,10 +5602,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650230</v>
+        <v>650395</v>
       </c>
       <c r="R42" t="n">
-        <v>6674064</v>
+        <v>6674254</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5648,7 +5637,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5658,7 +5647,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5685,7 +5674,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384406</v>
+        <v>122384397</v>
       </c>
       <c r="B43" t="n">
         <v>57400</v>
@@ -5737,10 +5726,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650115</v>
+        <v>650406</v>
       </c>
       <c r="R43" t="n">
-        <v>6674245</v>
+        <v>6674220</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5772,7 +5761,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5782,7 +5771,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5809,10 +5798,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384407</v>
+        <v>122384487</v>
       </c>
       <c r="B44" t="n">
-        <v>57400</v>
+        <v>105350</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5821,50 +5810,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650101</v>
+        <v>650442</v>
       </c>
       <c r="R44" t="n">
-        <v>6674120</v>
+        <v>6674345</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5896,7 +5877,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5906,7 +5887,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5933,10 +5914,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384487</v>
+        <v>122384411</v>
       </c>
       <c r="B45" t="n">
-        <v>105347</v>
+        <v>57400</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5945,42 +5926,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650442</v>
+        <v>650415</v>
       </c>
       <c r="R45" t="n">
-        <v>6674345</v>
+        <v>6674083</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -6012,7 +6001,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6022,7 +6011,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6049,10 +6038,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384479</v>
+        <v>122384394</v>
       </c>
       <c r="B46" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6061,42 +6050,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650415</v>
+        <v>650394</v>
       </c>
       <c r="R46" t="n">
-        <v>6674370</v>
+        <v>6674272</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6128,7 +6125,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6138,7 +6135,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6165,10 +6162,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384465</v>
+        <v>122384472</v>
       </c>
       <c r="B47" t="n">
-        <v>91125</v>
+        <v>98244</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6177,30 +6174,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6208,10 +6214,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650436</v>
+        <v>650415</v>
       </c>
       <c r="R47" t="n">
-        <v>6674342</v>
+        <v>6674360</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6243,7 +6249,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6253,7 +6259,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6280,10 +6286,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384468</v>
+        <v>122384473</v>
       </c>
       <c r="B48" t="n">
-        <v>91279</v>
+        <v>98244</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6296,26 +6302,35 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6323,10 +6338,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650436</v>
+        <v>650400</v>
       </c>
       <c r="R48" t="n">
-        <v>6674345</v>
+        <v>6674415</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6358,7 +6373,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6368,12 +6383,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6382,24 +6392,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6416,10 +6410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384434</v>
+        <v>122384485</v>
       </c>
       <c r="B49" t="n">
-        <v>74697</v>
+        <v>100510</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6432,37 +6426,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650407</v>
+        <v>650432</v>
       </c>
       <c r="R49" t="n">
-        <v>6674363</v>
+        <v>6674247</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6494,7 +6489,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6504,7 +6499,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6531,10 +6526,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384485</v>
+        <v>122384407</v>
       </c>
       <c r="B50" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6543,31 +6538,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6575,10 +6578,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650432</v>
+        <v>650101</v>
       </c>
       <c r="R50" t="n">
-        <v>6674247</v>
+        <v>6674120</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6610,7 +6613,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6620,7 +6623,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6647,10 +6650,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384454</v>
+        <v>122384400</v>
       </c>
       <c r="B51" t="n">
-        <v>90834</v>
+        <v>57400</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6663,37 +6666,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650440</v>
+        <v>650362</v>
       </c>
       <c r="R51" t="n">
-        <v>6674369</v>
+        <v>6674082</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6725,7 +6737,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6735,7 +6747,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6762,10 +6774,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384464</v>
+        <v>122384366</v>
       </c>
       <c r="B52" t="n">
-        <v>90834</v>
+        <v>57400</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6778,37 +6790,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650429</v>
+        <v>650419</v>
       </c>
       <c r="R52" t="n">
-        <v>6674188</v>
+        <v>6674371</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6840,7 +6861,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6850,7 +6871,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6877,10 +6898,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384402</v>
+        <v>122384464</v>
       </c>
       <c r="B53" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6893,35 +6914,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6929,10 +6941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650297</v>
+        <v>650429</v>
       </c>
       <c r="R53" t="n">
-        <v>6674040</v>
+        <v>6674188</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6964,7 +6976,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6974,7 +6986,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7001,10 +7013,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384412</v>
+        <v>122384436</v>
       </c>
       <c r="B54" t="n">
-        <v>57400</v>
+        <v>80617</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7017,46 +7029,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650399</v>
+        <v>650363</v>
       </c>
       <c r="R54" t="n">
-        <v>6674181</v>
+        <v>6674334</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7088,7 +7091,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7098,7 +7101,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7125,10 +7128,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384442</v>
+        <v>122384439</v>
       </c>
       <c r="B55" t="n">
-        <v>90799</v>
+        <v>80617</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7137,25 +7140,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7168,10 +7171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650393</v>
+        <v>650238</v>
       </c>
       <c r="R55" t="n">
-        <v>6674157</v>
+        <v>6674074</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7203,7 +7206,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7213,7 +7216,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7240,10 +7248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384438</v>
+        <v>122384480</v>
       </c>
       <c r="B56" t="n">
-        <v>80614</v>
+        <v>100510</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7252,30 +7260,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7283,10 +7292,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650353</v>
+        <v>650316</v>
       </c>
       <c r="R56" t="n">
-        <v>6674235</v>
+        <v>6674034</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7318,7 +7327,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7328,12 +7337,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7360,10 +7364,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384483</v>
+        <v>122384437</v>
       </c>
       <c r="B57" t="n">
-        <v>100507</v>
+        <v>80617</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7372,31 +7376,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7404,10 +7407,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650238</v>
+        <v>650387</v>
       </c>
       <c r="R57" t="n">
-        <v>6674076</v>
+        <v>6674259</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7439,7 +7442,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7449,7 +7452,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7476,10 +7479,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384477</v>
+        <v>122384479</v>
       </c>
       <c r="B58" t="n">
-        <v>98241</v>
+        <v>100510</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7488,50 +7491,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
         <v>650415</v>
       </c>
       <c r="R58" t="n">
-        <v>6674216</v>
+        <v>6674370</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7563,7 +7558,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7573,7 +7568,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7600,10 +7595,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384484</v>
+        <v>122384466</v>
       </c>
       <c r="B59" t="n">
-        <v>100507</v>
+        <v>91238</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7616,38 +7611,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>4217</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>650407</v>
+        <v>650393</v>
       </c>
       <c r="R59" t="n">
-        <v>6674068</v>
+        <v>6674366</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7679,7 +7673,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7689,7 +7683,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7698,8 +7692,24 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7716,10 +7726,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384473</v>
+        <v>122384470</v>
       </c>
       <c r="B60" t="n">
-        <v>98241</v>
+        <v>91282</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7732,35 +7742,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7768,10 +7769,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650400</v>
+        <v>650388</v>
       </c>
       <c r="R60" t="n">
-        <v>6674415</v>
+        <v>6674308</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7803,7 +7804,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7813,7 +7814,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7840,10 +7841,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384480</v>
+        <v>122384442</v>
       </c>
       <c r="B61" t="n">
-        <v>100507</v>
+        <v>90802</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7856,27 +7857,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650316</v>
+        <v>650393</v>
       </c>
       <c r="R61" t="n">
-        <v>6674034</v>
+        <v>6674157</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7956,10 +7956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122399656</v>
+        <v>122399649</v>
       </c>
       <c r="B62" t="n">
-        <v>94762</v>
+        <v>80617</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7968,31 +7968,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2818</v>
+        <v>1049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8000,10 +7999,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649935</v>
+        <v>650383</v>
       </c>
       <c r="R62" t="n">
-        <v>6674249</v>
+        <v>6673928</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8035,7 +8034,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8045,7 +8044,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8072,10 +8071,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399637</v>
+        <v>122399656</v>
       </c>
       <c r="B63" t="n">
-        <v>57400</v>
+        <v>94765</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8084,39 +8083,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8124,10 +8115,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649994</v>
+        <v>649935</v>
       </c>
       <c r="R63" t="n">
-        <v>6674118</v>
+        <v>6674249</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8159,7 +8150,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8169,7 +8160,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8196,10 +8187,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399640</v>
+        <v>122399650</v>
       </c>
       <c r="B64" t="n">
-        <v>57400</v>
+        <v>90802</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8208,39 +8199,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8248,10 +8230,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650059</v>
+        <v>650386</v>
       </c>
       <c r="R64" t="n">
-        <v>6674144</v>
+        <v>6673912</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8283,7 +8265,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8293,7 +8275,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8320,10 +8302,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399639</v>
+        <v>122399675</v>
       </c>
       <c r="B65" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8332,39 +8314,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8372,10 +8346,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650031</v>
+        <v>650473</v>
       </c>
       <c r="R65" t="n">
-        <v>6674158</v>
+        <v>6673911</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8407,7 +8381,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8417,7 +8391,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8444,10 +8418,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399649</v>
+        <v>122399640</v>
       </c>
       <c r="B66" t="n">
-        <v>80614</v>
+        <v>57400</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8460,26 +8434,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8487,10 +8470,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>650383</v>
+        <v>650059</v>
       </c>
       <c r="R66" t="n">
-        <v>6673928</v>
+        <v>6674144</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8522,7 +8505,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8532,7 +8515,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8559,10 +8542,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399675</v>
+        <v>122399639</v>
       </c>
       <c r="B67" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8571,31 +8554,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8603,10 +8594,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>650473</v>
+        <v>650031</v>
       </c>
       <c r="R67" t="n">
-        <v>6673911</v>
+        <v>6674158</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8638,7 +8629,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8648,7 +8639,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8675,10 +8666,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399673</v>
+        <v>122399641</v>
       </c>
       <c r="B68" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8687,31 +8678,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8719,10 +8718,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650321</v>
+        <v>650092</v>
       </c>
       <c r="R68" t="n">
-        <v>6673981</v>
+        <v>6674138</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8754,7 +8753,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8764,7 +8763,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8791,10 +8790,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399672</v>
+        <v>122399642</v>
       </c>
       <c r="B69" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8803,31 +8802,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8835,10 +8842,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650329</v>
+        <v>650411</v>
       </c>
       <c r="R69" t="n">
-        <v>6673994</v>
+        <v>6674002</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8870,7 +8877,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8880,7 +8887,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8910,7 +8917,7 @@
         <v>122399658</v>
       </c>
       <c r="B70" t="n">
-        <v>94858</v>
+        <v>94861</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9023,10 +9030,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399642</v>
+        <v>122399673</v>
       </c>
       <c r="B71" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9035,39 +9042,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9075,10 +9074,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650411</v>
+        <v>650321</v>
       </c>
       <c r="R71" t="n">
-        <v>6674002</v>
+        <v>6673981</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9110,7 +9109,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9120,7 +9119,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9147,7 +9146,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122399641</v>
+        <v>122399637</v>
       </c>
       <c r="B72" t="n">
         <v>57400</v>
@@ -9189,7 +9188,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9199,10 +9198,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>650092</v>
+        <v>649994</v>
       </c>
       <c r="R72" t="n">
-        <v>6674138</v>
+        <v>6674118</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9234,7 +9233,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9244,7 +9243,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9271,10 +9270,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399650</v>
+        <v>122399672</v>
       </c>
       <c r="B73" t="n">
-        <v>90799</v>
+        <v>100510</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9287,26 +9286,27 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650386</v>
+        <v>650329</v>
       </c>
       <c r="R73" t="n">
-        <v>6673912</v>
+        <v>6673994</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9389,7 +9389,7 @@
         <v>122399660</v>
       </c>
       <c r="B74" t="n">
-        <v>94858</v>
+        <v>94861</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9502,10 +9502,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399657</v>
+        <v>122399655</v>
       </c>
       <c r="B75" t="n">
-        <v>94858</v>
+        <v>94765</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9518,21 +9518,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649950</v>
+        <v>649962</v>
       </c>
       <c r="R75" t="n">
-        <v>6674175</v>
+        <v>6674201</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9738,10 +9738,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122399655</v>
+        <v>122399657</v>
       </c>
       <c r="B77" t="n">
-        <v>94762</v>
+        <v>94861</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9782,10 +9782,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>649962</v>
+        <v>649950</v>
       </c>
       <c r="R77" t="n">
-        <v>6674201</v>
+        <v>6674175</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122399671</v>
+        <v>122399627</v>
       </c>
       <c r="B2" t="n">
-        <v>100510</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650309</v>
+        <v>650420</v>
       </c>
       <c r="R2" t="n">
-        <v>6673789</v>
+        <v>6673617</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122399632</v>
+        <v>122399667</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650256</v>
+        <v>650365</v>
       </c>
       <c r="R3" t="n">
-        <v>6673700</v>
+        <v>6673701</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399652</v>
+        <v>122399626</v>
       </c>
       <c r="B4" t="n">
-        <v>90837</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +932,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650328</v>
+        <v>650382</v>
       </c>
       <c r="R4" t="n">
-        <v>6673703</v>
+        <v>6673643</v>
       </c>
       <c r="S4" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1154,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122399670</v>
+        <v>122399630</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,39 +1177,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1206,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650313</v>
+        <v>650217</v>
       </c>
       <c r="R6" t="n">
-        <v>6673680</v>
+        <v>6673709</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1241,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1259,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122399644</v>
+        <v>122399671</v>
       </c>
       <c r="B7" t="n">
-        <v>57754</v>
+        <v>100510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,31 +1302,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1326,13 +1330,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650328</v>
+        <v>650309</v>
       </c>
       <c r="R7" t="n">
-        <v>6673703</v>
+        <v>6673789</v>
       </c>
       <c r="S7" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122399666</v>
+        <v>122399668</v>
       </c>
       <c r="B8" t="n">
         <v>98244</v>
@@ -1433,10 +1437,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1446,10 +1454,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650369</v>
+        <v>650331</v>
       </c>
       <c r="R8" t="n">
-        <v>6673665</v>
+        <v>6673701</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1481,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,12 +1499,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst!</t>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122399668</v>
+        <v>122399632</v>
       </c>
       <c r="B9" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,39 +1543,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1575,10 +1583,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650331</v>
+        <v>650256</v>
       </c>
       <c r="R9" t="n">
-        <v>6673701</v>
+        <v>6673700</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1610,7 +1618,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,12 +1628,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,10 +1655,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122399667</v>
+        <v>122399652</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>90837</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,39 +1667,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1704,13 +1698,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650365</v>
+        <v>650328</v>
       </c>
       <c r="R10" t="n">
-        <v>6673701</v>
+        <v>6673703</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,7 +1733,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1743,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,10 +1770,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122399627</v>
+        <v>122399670</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>98244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1788,36 +1782,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1825,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650420</v>
+        <v>650313</v>
       </c>
       <c r="R11" t="n">
-        <v>6673617</v>
+        <v>6673680</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1860,7 +1857,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1867,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122399626</v>
+        <v>122399644</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>57754</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1913,32 +1910,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1946,13 +1942,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650382</v>
+        <v>650328</v>
       </c>
       <c r="R12" t="n">
-        <v>6673643</v>
+        <v>6673703</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1981,7 +1977,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1991,7 +1987,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2139,10 +2135,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122399630</v>
+        <v>122399666</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>98244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,36 +2147,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650217</v>
+        <v>650369</v>
       </c>
       <c r="R14" t="n">
-        <v>6673709</v>
+        <v>6673665</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2223,7 +2218,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2228,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122384477</v>
+        <v>122384397</v>
       </c>
       <c r="B16" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,39 +2396,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650415</v>
+        <v>650406</v>
       </c>
       <c r="R16" t="n">
-        <v>6674216</v>
+        <v>6674220</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,10 +2508,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122384454</v>
+        <v>122384369</v>
       </c>
       <c r="B17" t="n">
-        <v>90837</v>
+        <v>57400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2524,26 +2524,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2551,10 +2560,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650440</v>
+        <v>650395</v>
       </c>
       <c r="R17" t="n">
-        <v>6674369</v>
+        <v>6674349</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2586,7 +2595,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2596,7 +2605,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2623,7 +2632,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122384373</v>
+        <v>122384403</v>
       </c>
       <c r="B18" t="n">
         <v>57400</v>
@@ -2665,20 +2674,20 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650373</v>
+        <v>650237</v>
       </c>
       <c r="R18" t="n">
-        <v>6674389</v>
+        <v>6674049</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2710,7 +2719,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2720,7 +2729,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2747,10 +2756,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122384369</v>
+        <v>122384481</v>
       </c>
       <c r="B19" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2759,50 +2768,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650395</v>
+        <v>650230</v>
       </c>
       <c r="R19" t="n">
-        <v>6674349</v>
+        <v>6674064</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2834,7 +2835,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2844,7 +2845,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2871,10 +2872,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122384417</v>
+        <v>122384394</v>
       </c>
       <c r="B20" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2887,21 +2888,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2913,23 +2914,23 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650385</v>
+        <v>650394</v>
       </c>
       <c r="R20" t="n">
-        <v>6674365</v>
+        <v>6674272</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2958,7 +2959,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2968,12 +2969,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Sjunger ihärdigt med båda sångtyperna.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3000,7 +2996,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122384443</v>
+        <v>122384462</v>
       </c>
       <c r="B21" t="n">
         <v>90837</v>
@@ -3043,10 +3039,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650438</v>
+        <v>650428</v>
       </c>
       <c r="R21" t="n">
-        <v>6674347</v>
+        <v>6674388</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3078,7 +3074,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3088,7 +3084,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3115,10 +3111,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122384465</v>
+        <v>122384373</v>
       </c>
       <c r="B22" t="n">
-        <v>91128</v>
+        <v>57400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3131,26 +3127,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3158,10 +3163,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650436</v>
+        <v>650373</v>
       </c>
       <c r="R22" t="n">
-        <v>6674342</v>
+        <v>6674389</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3193,7 +3198,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3203,7 +3208,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3230,10 +3235,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122384440</v>
+        <v>122384464</v>
       </c>
       <c r="B23" t="n">
-        <v>80617</v>
+        <v>90837</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3246,21 +3251,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3273,10 +3278,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650077</v>
+        <v>650429</v>
       </c>
       <c r="R23" t="n">
-        <v>6674268</v>
+        <v>6674188</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3308,7 +3313,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3318,7 +3323,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3345,10 +3350,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122384476</v>
+        <v>122384404</v>
       </c>
       <c r="B24" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3357,39 +3362,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3397,10 +3402,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650396</v>
+        <v>650195</v>
       </c>
       <c r="R24" t="n">
-        <v>6674252</v>
+        <v>6674100</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3432,7 +3437,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3442,7 +3447,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3469,10 +3474,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122384432</v>
+        <v>122384466</v>
       </c>
       <c r="B25" t="n">
-        <v>74700</v>
+        <v>91238</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3485,21 +3490,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>4217</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3512,10 +3517,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650422</v>
+        <v>650393</v>
       </c>
       <c r="R25" t="n">
-        <v>6674376</v>
+        <v>6674366</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3547,7 +3552,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3557,7 +3562,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3572,17 +3577,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3715,7 +3720,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384391</v>
+        <v>122384410</v>
       </c>
       <c r="B27" t="n">
         <v>57400</v>
@@ -3763,14 +3768,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650364</v>
+        <v>650147</v>
       </c>
       <c r="R27" t="n">
-        <v>6674383</v>
+        <v>6674088</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3802,7 +3807,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3812,7 +3817,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3839,10 +3844,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384483</v>
+        <v>122384473</v>
       </c>
       <c r="B28" t="n">
-        <v>100510</v>
+        <v>98244</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3851,42 +3856,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650238</v>
+        <v>650400</v>
       </c>
       <c r="R28" t="n">
-        <v>6674076</v>
+        <v>6674415</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3918,7 +3931,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3928,7 +3941,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3955,10 +3968,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384468</v>
+        <v>122384440</v>
       </c>
       <c r="B29" t="n">
-        <v>91282</v>
+        <v>80617</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3967,25 +3980,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3994,14 +4007,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650436</v>
+        <v>650077</v>
       </c>
       <c r="R29" t="n">
-        <v>6674345</v>
+        <v>6674268</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4033,7 +4046,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4043,12 +4056,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4057,24 +4065,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4091,7 +4083,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122384438</v>
+        <v>122384436</v>
       </c>
       <c r="B30" t="n">
         <v>80617</v>
@@ -4130,14 +4122,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650353</v>
+        <v>650363</v>
       </c>
       <c r="R30" t="n">
-        <v>6674235</v>
+        <v>6674334</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4169,7 +4161,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4179,12 +4171,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4211,10 +4198,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122384484</v>
+        <v>122384411</v>
       </c>
       <c r="B31" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4223,31 +4210,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4255,10 +4250,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>650407</v>
+        <v>650415</v>
       </c>
       <c r="R31" t="n">
-        <v>6674068</v>
+        <v>6674083</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4290,7 +4285,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4300,7 +4295,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4327,7 +4322,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122384403</v>
+        <v>122384366</v>
       </c>
       <c r="B32" t="n">
         <v>57400</v>
@@ -4375,14 +4370,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650237</v>
+        <v>650419</v>
       </c>
       <c r="R32" t="n">
-        <v>6674049</v>
+        <v>6674371</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4414,7 +4409,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4424,7 +4419,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4451,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122384410</v>
+        <v>122384402</v>
       </c>
       <c r="B33" t="n">
         <v>57400</v>
@@ -4493,7 +4488,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650147</v>
+        <v>650297</v>
       </c>
       <c r="R33" t="n">
-        <v>6674088</v>
+        <v>6674040</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4538,7 +4533,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4548,7 +4543,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4575,10 +4570,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122384481</v>
+        <v>122384412</v>
       </c>
       <c r="B34" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4587,31 +4582,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4619,10 +4622,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>650230</v>
+        <v>650399</v>
       </c>
       <c r="R34" t="n">
-        <v>6674064</v>
+        <v>6674181</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4654,7 +4657,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4664,7 +4667,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4691,10 +4694,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122384412</v>
+        <v>122384477</v>
       </c>
       <c r="B35" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4703,39 +4706,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4743,10 +4746,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650399</v>
+        <v>650415</v>
       </c>
       <c r="R35" t="n">
-        <v>6674181</v>
+        <v>6674216</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4778,7 +4781,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4788,7 +4791,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4815,10 +4818,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384402</v>
+        <v>122384476</v>
       </c>
       <c r="B36" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4827,39 +4830,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4867,10 +4870,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650297</v>
+        <v>650396</v>
       </c>
       <c r="R36" t="n">
-        <v>6674040</v>
+        <v>6674252</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4902,7 +4905,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4912,7 +4915,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4939,10 +4942,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384388</v>
+        <v>122384443</v>
       </c>
       <c r="B37" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4955,35 +4958,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4991,10 +4985,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650400</v>
+        <v>650438</v>
       </c>
       <c r="R37" t="n">
-        <v>6674425</v>
+        <v>6674347</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5026,7 +5020,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5036,7 +5030,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5063,10 +5057,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122384406</v>
+        <v>122384487</v>
       </c>
       <c r="B38" t="n">
-        <v>57400</v>
+        <v>105350</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5075,50 +5069,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650115</v>
+        <v>650442</v>
       </c>
       <c r="R38" t="n">
-        <v>6674245</v>
+        <v>6674345</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5150,7 +5136,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5160,7 +5146,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5187,10 +5173,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122384404</v>
+        <v>122384438</v>
       </c>
       <c r="B39" t="n">
-        <v>57400</v>
+        <v>80617</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5203,35 +5189,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5239,10 +5216,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>650195</v>
+        <v>650353</v>
       </c>
       <c r="R39" t="n">
-        <v>6674100</v>
+        <v>6674235</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5274,7 +5251,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5284,7 +5261,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5311,10 +5293,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122384371</v>
+        <v>122384439</v>
       </c>
       <c r="B40" t="n">
-        <v>57400</v>
+        <v>80617</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5327,35 +5309,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5363,13 +5336,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650400</v>
+        <v>650238</v>
       </c>
       <c r="R40" t="n">
-        <v>6674206</v>
+        <v>6674074</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5398,7 +5371,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5408,7 +5381,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5435,10 +5413,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122384462</v>
+        <v>122384468</v>
       </c>
       <c r="B41" t="n">
-        <v>90837</v>
+        <v>91282</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5447,25 +5425,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5478,10 +5456,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>650428</v>
+        <v>650436</v>
       </c>
       <c r="R41" t="n">
-        <v>6674388</v>
+        <v>6674345</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5513,7 +5491,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5523,7 +5501,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka och ullticka och även klibbticka (vid basen).</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5532,8 +5515,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5550,10 +5549,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122384395</v>
+        <v>122384480</v>
       </c>
       <c r="B42" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5562,39 +5561,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5602,10 +5593,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650395</v>
+        <v>650316</v>
       </c>
       <c r="R42" t="n">
-        <v>6674254</v>
+        <v>6674034</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5637,7 +5628,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5647,7 +5638,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5674,10 +5665,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122384397</v>
+        <v>122384432</v>
       </c>
       <c r="B43" t="n">
-        <v>57400</v>
+        <v>74700</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5686,50 +5677,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>650406</v>
+        <v>650422</v>
       </c>
       <c r="R43" t="n">
-        <v>6674220</v>
+        <v>6674376</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5761,7 +5743,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5771,7 +5753,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5780,8 +5762,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5798,10 +5796,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122384487</v>
+        <v>122384485</v>
       </c>
       <c r="B44" t="n">
-        <v>105350</v>
+        <v>100510</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5814,21 +5812,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5838,14 +5836,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>650442</v>
+        <v>650432</v>
       </c>
       <c r="R44" t="n">
-        <v>6674345</v>
+        <v>6674247</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5877,7 +5875,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5887,7 +5885,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5914,7 +5912,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122384411</v>
+        <v>122384395</v>
       </c>
       <c r="B45" t="n">
         <v>57400</v>
@@ -5966,10 +5964,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>650415</v>
+        <v>650395</v>
       </c>
       <c r="R45" t="n">
-        <v>6674083</v>
+        <v>6674254</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -6001,7 +5999,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6011,7 +6009,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6038,7 +6036,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122384394</v>
+        <v>122384400</v>
       </c>
       <c r="B46" t="n">
         <v>57400</v>
@@ -6090,10 +6088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>650394</v>
+        <v>650362</v>
       </c>
       <c r="R46" t="n">
-        <v>6674272</v>
+        <v>6674082</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6125,7 +6123,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6135,7 +6133,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6162,10 +6160,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122384472</v>
+        <v>122384417</v>
       </c>
       <c r="B47" t="n">
-        <v>98244</v>
+        <v>57537</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6174,39 +6172,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6214,13 +6212,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>650415</v>
+        <v>650385</v>
       </c>
       <c r="R47" t="n">
-        <v>6674360</v>
+        <v>6674365</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6249,7 +6247,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6259,7 +6257,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Sjunger ihärdigt med båda sångtyperna.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6286,10 +6289,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122384473</v>
+        <v>122384479</v>
       </c>
       <c r="B48" t="n">
-        <v>98244</v>
+        <v>100510</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6298,37 +6301,29 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -6338,10 +6333,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>650400</v>
+        <v>650415</v>
       </c>
       <c r="R48" t="n">
-        <v>6674415</v>
+        <v>6674370</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6373,7 +6368,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6383,7 +6378,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6410,10 +6405,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122384485</v>
+        <v>122384437</v>
       </c>
       <c r="B49" t="n">
-        <v>100510</v>
+        <v>80617</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6422,31 +6417,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6454,10 +6448,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>650432</v>
+        <v>650387</v>
       </c>
       <c r="R49" t="n">
-        <v>6674247</v>
+        <v>6674259</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6489,7 +6483,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6499,7 +6493,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6526,10 +6520,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122384407</v>
+        <v>122384472</v>
       </c>
       <c r="B50" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6538,50 +6532,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>650101</v>
+        <v>650415</v>
       </c>
       <c r="R50" t="n">
-        <v>6674120</v>
+        <v>6674360</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6613,7 +6607,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6623,7 +6617,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6650,10 +6644,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122384400</v>
+        <v>122384470</v>
       </c>
       <c r="B51" t="n">
-        <v>57400</v>
+        <v>91282</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6662,50 +6656,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>650362</v>
+        <v>650388</v>
       </c>
       <c r="R51" t="n">
-        <v>6674082</v>
+        <v>6674308</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6737,7 +6722,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6747,7 +6732,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6774,7 +6759,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122384366</v>
+        <v>122384406</v>
       </c>
       <c r="B52" t="n">
         <v>57400</v>
@@ -6816,20 +6801,20 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>650419</v>
+        <v>650115</v>
       </c>
       <c r="R52" t="n">
-        <v>6674371</v>
+        <v>6674245</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6861,7 +6846,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6871,7 +6856,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6898,10 +6883,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122384464</v>
+        <v>122384484</v>
       </c>
       <c r="B53" t="n">
-        <v>90837</v>
+        <v>100510</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6910,30 +6895,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6941,10 +6927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>650429</v>
+        <v>650407</v>
       </c>
       <c r="R53" t="n">
-        <v>6674188</v>
+        <v>6674068</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6976,7 +6962,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6986,7 +6972,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7013,10 +6999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122384436</v>
+        <v>122384465</v>
       </c>
       <c r="B54" t="n">
-        <v>80617</v>
+        <v>91128</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7029,21 +7015,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7056,10 +7042,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>650363</v>
+        <v>650436</v>
       </c>
       <c r="R54" t="n">
-        <v>6674334</v>
+        <v>6674342</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7091,7 +7077,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7101,7 +7087,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7128,10 +7114,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122384439</v>
+        <v>122384454</v>
       </c>
       <c r="B55" t="n">
-        <v>80617</v>
+        <v>90837</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7144,21 +7130,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7167,14 +7153,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>650238</v>
+        <v>650440</v>
       </c>
       <c r="R55" t="n">
-        <v>6674074</v>
+        <v>6674369</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7206,7 +7192,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7216,12 +7202,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>En ensam liten pajsare men kan säkert finnas fler.</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7248,10 +7229,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122384480</v>
+        <v>122384388</v>
       </c>
       <c r="B56" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7260,42 +7241,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>650316</v>
+        <v>650400</v>
       </c>
       <c r="R56" t="n">
-        <v>6674034</v>
+        <v>6674425</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7327,7 +7316,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7337,7 +7326,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7364,10 +7353,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122384437</v>
+        <v>122384407</v>
       </c>
       <c r="B57" t="n">
-        <v>80617</v>
+        <v>57400</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7380,26 +7369,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7407,10 +7405,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>650387</v>
+        <v>650101</v>
       </c>
       <c r="R57" t="n">
-        <v>6674259</v>
+        <v>6674120</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7442,7 +7440,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7452,7 +7450,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7479,7 +7477,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122384479</v>
+        <v>122384483</v>
       </c>
       <c r="B58" t="n">
         <v>100510</v>
@@ -7519,14 +7517,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>650415</v>
+        <v>650238</v>
       </c>
       <c r="R58" t="n">
-        <v>6674370</v>
+        <v>6674076</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7558,7 +7556,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7568,7 +7566,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7595,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122384466</v>
+        <v>122384442</v>
       </c>
       <c r="B59" t="n">
-        <v>91238</v>
+        <v>90802</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7611,21 +7609,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7634,14 +7632,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
         <v>650393</v>
       </c>
       <c r="R59" t="n">
-        <v>6674366</v>
+        <v>6674157</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7673,7 +7671,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7683,7 +7681,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7692,24 +7690,8 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7726,10 +7708,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122384470</v>
+        <v>122384391</v>
       </c>
       <c r="B60" t="n">
-        <v>91282</v>
+        <v>57400</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7738,30 +7720,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7769,10 +7760,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650388</v>
+        <v>650364</v>
       </c>
       <c r="R60" t="n">
-        <v>6674308</v>
+        <v>6674383</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7804,7 +7795,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7814,7 +7805,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7841,10 +7832,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122384442</v>
+        <v>122384371</v>
       </c>
       <c r="B61" t="n">
-        <v>90802</v>
+        <v>57400</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7853,30 +7844,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7884,13 +7884,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>650393</v>
+        <v>650400</v>
       </c>
       <c r="R61" t="n">
-        <v>6674157</v>
+        <v>6674206</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8071,10 +8071,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122399656</v>
+        <v>122399675</v>
       </c>
       <c r="B63" t="n">
-        <v>94765</v>
+        <v>100510</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649935</v>
+        <v>650473</v>
       </c>
       <c r="R63" t="n">
-        <v>6674249</v>
+        <v>6673911</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8187,10 +8187,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122399650</v>
+        <v>122399641</v>
       </c>
       <c r="B64" t="n">
-        <v>90802</v>
+        <v>57400</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8199,30 +8199,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8230,10 +8239,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650386</v>
+        <v>650092</v>
       </c>
       <c r="R64" t="n">
-        <v>6673912</v>
+        <v>6674138</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8265,7 +8274,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8275,7 +8284,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8302,10 +8311,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122399675</v>
+        <v>122399658</v>
       </c>
       <c r="B65" t="n">
-        <v>100510</v>
+        <v>94861</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8318,21 +8327,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8346,10 +8355,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650473</v>
+        <v>649956</v>
       </c>
       <c r="R65" t="n">
-        <v>6673911</v>
+        <v>6674194</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8381,7 +8390,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8391,7 +8400,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8418,10 +8427,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122399640</v>
+        <v>122399673</v>
       </c>
       <c r="B66" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8430,39 +8439,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8470,10 +8471,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>650059</v>
+        <v>650321</v>
       </c>
       <c r="R66" t="n">
-        <v>6674144</v>
+        <v>6673981</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8505,7 +8506,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8515,7 +8516,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8542,10 +8543,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122399639</v>
+        <v>122399656</v>
       </c>
       <c r="B67" t="n">
-        <v>57400</v>
+        <v>94765</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8554,39 +8555,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8594,10 +8587,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>650031</v>
+        <v>649935</v>
       </c>
       <c r="R67" t="n">
-        <v>6674158</v>
+        <v>6674249</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8629,7 +8622,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8639,7 +8632,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8666,7 +8659,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122399641</v>
+        <v>122399640</v>
       </c>
       <c r="B68" t="n">
         <v>57400</v>
@@ -8708,7 +8701,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8718,10 +8711,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650092</v>
+        <v>650059</v>
       </c>
       <c r="R68" t="n">
-        <v>6674138</v>
+        <v>6674144</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8753,7 +8746,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8763,7 +8756,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8790,10 +8783,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122399642</v>
+        <v>122399672</v>
       </c>
       <c r="B69" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8802,39 +8795,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8842,10 +8827,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>650411</v>
+        <v>650329</v>
       </c>
       <c r="R69" t="n">
-        <v>6674002</v>
+        <v>6673994</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8877,7 +8862,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8887,7 +8872,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8914,10 +8899,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122399658</v>
+        <v>122399639</v>
       </c>
       <c r="B70" t="n">
-        <v>94861</v>
+        <v>57400</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8926,31 +8911,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8958,10 +8951,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>649956</v>
+        <v>650031</v>
       </c>
       <c r="R70" t="n">
-        <v>6674194</v>
+        <v>6674158</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8993,7 +8986,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9003,7 +8996,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9030,10 +9023,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122399673</v>
+        <v>122399650</v>
       </c>
       <c r="B71" t="n">
-        <v>100510</v>
+        <v>90802</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9046,27 +9039,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9074,10 +9066,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>650321</v>
+        <v>650386</v>
       </c>
       <c r="R71" t="n">
-        <v>6673981</v>
+        <v>6673912</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9109,7 +9101,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9119,7 +9111,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9270,10 +9262,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122399672</v>
+        <v>122399642</v>
       </c>
       <c r="B73" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9282,31 +9274,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>650329</v>
+        <v>650411</v>
       </c>
       <c r="R73" t="n">
-        <v>6673994</v>
+        <v>6674002</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9502,14 +9502,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122399655</v>
+        <v>122399645</v>
       </c>
       <c r="B75" t="n">
-        <v>94765</v>
+        <v>57754</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9518,27 +9518,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2818</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649962</v>
+        <v>649902</v>
       </c>
       <c r="R75" t="n">
-        <v>6674201</v>
+        <v>6674271</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9614,18 +9614,22 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122399645</v>
+        <v>122399657</v>
       </c>
       <c r="B76" t="n">
-        <v>57754</v>
+        <v>94861</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9634,27 +9638,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>210</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9662,10 +9666,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>649902</v>
+        <v>649950</v>
       </c>
       <c r="R76" t="n">
-        <v>6674271</v>
+        <v>6674175</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9697,7 +9701,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9707,7 +9711,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9730,18 +9734,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122399657</v>
+        <v>122399655</v>
       </c>
       <c r="B77" t="n">
-        <v>94861</v>
+        <v>94765</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9782,10 +9782,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>649950</v>
+        <v>649962</v>
       </c>
       <c r="R77" t="n">
-        <v>6674175</v>
+        <v>6674201</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122399626</v>
+        <v>122399633</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,34 +932,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -969,13 +972,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650382</v>
+        <v>650328</v>
       </c>
       <c r="R4" t="n">
-        <v>6673643</v>
+        <v>6673703</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122399633</v>
+        <v>122399626</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,37 +1056,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650328</v>
+        <v>650382</v>
       </c>
       <c r="R5" t="n">
-        <v>6673703</v>
+        <v>6673643</v>
       </c>
       <c r="S5" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3605,10 +3605,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122384434</v>
+        <v>122384440</v>
       </c>
       <c r="B26" t="n">
-        <v>74700</v>
+        <v>80617</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3617,25 +3617,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3644,14 +3644,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650407</v>
+        <v>650077</v>
       </c>
       <c r="R26" t="n">
-        <v>6674363</v>
+        <v>6674268</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3720,10 +3720,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122384410</v>
+        <v>122384434</v>
       </c>
       <c r="B27" t="n">
-        <v>57400</v>
+        <v>74700</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3732,50 +3732,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>650147</v>
+        <v>650407</v>
       </c>
       <c r="R27" t="n">
-        <v>6674088</v>
+        <v>6674363</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3807,7 +3798,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3817,7 +3808,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3844,10 +3835,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122384473</v>
+        <v>122384410</v>
       </c>
       <c r="B28" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3856,50 +3847,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>650400</v>
+        <v>650147</v>
       </c>
       <c r="R28" t="n">
-        <v>6674415</v>
+        <v>6674088</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3931,7 +3922,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3941,7 +3932,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3968,10 +3959,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122384440</v>
+        <v>122384473</v>
       </c>
       <c r="B29" t="n">
-        <v>80617</v>
+        <v>98244</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3980,41 +3971,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650077</v>
+        <v>650400</v>
       </c>
       <c r="R29" t="n">
-        <v>6674268</v>
+        <v>6674415</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4818,10 +4818,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122384476</v>
+        <v>122384443</v>
       </c>
       <c r="B36" t="n">
-        <v>98244</v>
+        <v>90837</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4830,50 +4830,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650396</v>
+        <v>650438</v>
       </c>
       <c r="R36" t="n">
-        <v>6674252</v>
+        <v>6674347</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4905,7 +4896,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4915,7 +4906,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4942,10 +4933,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122384443</v>
+        <v>122384476</v>
       </c>
       <c r="B37" t="n">
-        <v>90837</v>
+        <v>98244</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4954,41 +4945,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>650438</v>
+        <v>650396</v>
       </c>
       <c r="R37" t="n">
-        <v>6674347</v>
+        <v>6674252</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:56</t>
+       